--- a/100_Beal_Street_Master_File_Inventory_v1.xlsx
+++ b/100_Beal_Street_Master_File_Inventory_v1.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard &amp; Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Files Master Catalog" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Downloaded Sources" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent Deliverables" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repository Index &amp; Governance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Dashboard &amp; Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All Files Master Catalog" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Downloaded Sources" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Agent Deliverables" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Repository Index &amp; Governance" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Files Master Catalog'!$A$4:$N$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Files Master Catalog'!$A$4:$N$176</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Downloaded Sources'!$A$4:$N$75</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Agent Deliverables'!$A$4:$N$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Agent Deliverables'!$A$4:$N$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Repository Index &amp; Governance'!$A$4:$N$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -625,7 +625,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Report Date: September 17, 2026  •  Location: Hingham, Plymouth County, MA  •  Zero Web Scrapes</t>
+          <t>Report Date: September 18, 2026  •  Location: Hingham, Plymouth County, MA  •  Zero Web Scrapes</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total Files Cataloged
-170</t>
+172</t>
         </is>
       </c>
       <c r="C6" s="5" t="n"/>
@@ -647,7 +647,7 @@
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Agent Deliverables
-84</t>
+86</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>503.2 MB (527,694,223 bytes across 170 active verified files)</t>
+          <t>503.3 MB (527,780,597 bytes across 172 active verified files)</t>
         </is>
       </c>
       <c r="D25" s="9" t="n"/>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>867.8 KB</t>
+          <t>952.2 KB</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -1435,7 +1435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N174"/>
+  <dimension ref="A1:N176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1464,7 +1464,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: September 17, 2026 • Total Records: 170 • Zero Web Scrapes</t>
+          <t>Generated: September 18, 2026 • Total Records: 172 • Zero Web Scrapes</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="D99" s="16" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.md</t>
+          <t>100_Beal_Street_The_True_Story_and_Evidence_v1.md</t>
         </is>
       </c>
       <c r="E99" s="15" t="inlineStr">
@@ -8147,11 +8147,11 @@
         </is>
       </c>
       <c r="F99" s="17" t="n">
-        <v>19343</v>
+        <v>12031</v>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>18.9 KB</t>
+          <t>11.7 KB</t>
         </is>
       </c>
       <c r="H99" s="15" t="inlineStr">
@@ -8161,32 +8161,32 @@
       </c>
       <c r="I99" s="16" t="inlineStr">
         <is>
-          <t>Hingham Board of Selectmen / HHA / Mass. DHCD</t>
+          <t>Primary Municipal Records &amp; Educational Architecture</t>
         </is>
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>M.G.L. c. 184A, § 3; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
+          <t>M.G.L. c. 121B; M.G.L. c. 184A; M.G.L. c. 44, § 7; Plymouth Registry Instruments</t>
         </is>
       </c>
       <c r="K99" s="18" t="inlineStr">
         <is>
-          <t>Primary source legal chronology detailing the 1989 deed, 2001 MOU, Feb 26, 2019 Select Board litigation vote (3-0), state DHCD letters, and Sept 7, 2021 HHA rescission vote.</t>
+          <t>Dedicated 2-page educational guide and evidence ledger for family and community members. Page 1 provides a 1-page unspun narrative essay; Page 2 provides the companion Works Cited mapping every point to primary documents with repository file names.</t>
         </is>
       </c>
       <c r="L99" s="15" t="inlineStr">
         <is>
-          <t>Prior Version (Superseded by v2)</t>
+          <t>Community Educational Guide &amp; Evidence Ledger (Verified)</t>
         </is>
       </c>
       <c r="M99" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17 06:59</t>
+          <t>2026-09-18 10:27</t>
         </is>
       </c>
       <c r="N99" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.md</t>
+          <t>agent_created_deliverables/executive_reports/100_Beal_Street_The_True_Story_and_Evidence_v1.md</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.pdf</t>
+          <t>100_Beal_Street_The_True_Story_and_Evidence_v1.pdf</t>
         </is>
       </c>
       <c r="E100" s="19" t="inlineStr">
@@ -8217,11 +8217,11 @@
         </is>
       </c>
       <c r="F100" s="21" t="n">
-        <v>108868</v>
+        <v>74343</v>
       </c>
       <c r="G100" s="22" t="inlineStr">
         <is>
-          <t>106.3 KB</t>
+          <t>72.6 KB</t>
         </is>
       </c>
       <c r="H100" s="19" t="inlineStr">
@@ -8231,32 +8231,32 @@
       </c>
       <c r="I100" s="20" t="inlineStr">
         <is>
-          <t>Hingham Board of Selectmen / HHA / Mass. DHCD</t>
+          <t>Primary Municipal Records &amp; Educational Architecture</t>
         </is>
       </c>
       <c r="J100" s="20" t="inlineStr">
         <is>
-          <t>M.G.L. c. 184A, § 3; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
+          <t>M.G.L. c. 121B; M.G.L. c. 184A; M.G.L. c. 44, § 7; Plymouth Registry Instruments</t>
         </is>
       </c>
       <c r="K100" s="23" t="inlineStr">
         <is>
-          <t>Primary source legal chronology detailing the 1989 deed, 2001 MOU, Feb 26, 2019 Select Board litigation vote (3-0), state DHCD letters, and Sept 7, 2021 HHA rescission vote.</t>
+          <t>Dedicated 2-page educational guide and evidence ledger for family and community members. Page 1 provides a 1-page unspun narrative essay; Page 2 provides the companion Works Cited mapping every point to primary documents with repository file names.</t>
         </is>
       </c>
       <c r="L100" s="19" t="inlineStr">
         <is>
-          <t>Prior Version (Superseded by v2)</t>
+          <t>Community Educational Guide &amp; Evidence Ledger (Verified)</t>
         </is>
       </c>
       <c r="M100" s="19" t="inlineStr">
         <is>
-          <t>2026-09-17 06:59</t>
+          <t>2026-09-18 10:27</t>
         </is>
       </c>
       <c r="N100" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.pdf</t>
+          <t>agent_created_deliverables/executive_reports/100_Beal_Street_The_True_Story_and_Evidence_v1.pdf</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="D101" s="16" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.md</t>
+          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.md</t>
         </is>
       </c>
       <c r="E101" s="15" t="inlineStr">
@@ -8287,46 +8287,46 @@
         </is>
       </c>
       <c r="F101" s="17" t="n">
-        <v>31676</v>
+        <v>19343</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>30.9 KB</t>
+          <t>18.9 KB</t>
         </is>
       </c>
       <c r="H101" s="15" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I101" s="16" t="inlineStr">
         <is>
-          <t>Primary Municipal Records / Mass. Registry of Deeds</t>
+          <t>Hingham Board of Selectmen / HHA / Mass. DHCD</t>
         </is>
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>Historical M.G.L. c. 184A, § 3; M.G.L. c. 184, § 23; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
+          <t>M.G.L. c. 184A, § 3; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
         </is>
       </c>
       <c r="K101" s="18" t="inlineStr">
         <is>
-          <t>Preliminary primary-source research chronology and record index; strictly neutral factual reporting; segregates verified facts, factual inferences, and open legal questions; includes missing documents inventory and disclaimer. Not a title opinion.</t>
+          <t>Primary source legal chronology detailing the 1989 deed, 2001 MOU, Feb 26, 2019 Select Board litigation vote (3-0), state DHCD letters, and Sept 7, 2021 HHA rescission vote.</t>
         </is>
       </c>
       <c r="L101" s="15" t="inlineStr">
         <is>
-          <t>Neutral Primary Source Research Index &amp; Inventory (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M101" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17 09:44</t>
+          <t>2026-09-17 06:59</t>
         </is>
       </c>
       <c r="N101" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.md</t>
+          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.md</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="D102" s="20" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.pdf</t>
+          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.pdf</t>
         </is>
       </c>
       <c r="E102" s="19" t="inlineStr">
@@ -8357,46 +8357,46 @@
         </is>
       </c>
       <c r="F102" s="21" t="n">
-        <v>119536</v>
+        <v>108868</v>
       </c>
       <c r="G102" s="22" t="inlineStr">
         <is>
-          <t>116.7 KB</t>
+          <t>106.3 KB</t>
         </is>
       </c>
       <c r="H102" s="19" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I102" s="20" t="inlineStr">
         <is>
-          <t>Primary Municipal Records / Mass. Registry of Deeds</t>
+          <t>Hingham Board of Selectmen / HHA / Mass. DHCD</t>
         </is>
       </c>
       <c r="J102" s="20" t="inlineStr">
         <is>
-          <t>Historical M.G.L. c. 184A, § 3; M.G.L. c. 184, § 23; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
+          <t>M.G.L. c. 184A, § 3; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
         </is>
       </c>
       <c r="K102" s="23" t="inlineStr">
         <is>
-          <t>Preliminary primary-source research chronology and record index; strictly neutral factual reporting; segregates verified facts, factual inferences, and open legal questions; includes missing documents inventory and disclaimer. Not a title opinion.</t>
+          <t>Primary source legal chronology detailing the 1989 deed, 2001 MOU, Feb 26, 2019 Select Board litigation vote (3-0), state DHCD letters, and Sept 7, 2021 HHA rescission vote.</t>
         </is>
       </c>
       <c r="L102" s="19" t="inlineStr">
         <is>
-          <t>Neutral Primary Source Research Index &amp; Inventory (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M102" s="19" t="inlineStr">
         <is>
-          <t>2026-09-17 09:44</t>
+          <t>2026-09-17 06:59</t>
         </is>
       </c>
       <c r="N102" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.pdf</t>
+          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.pdf</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="D103" s="16" t="inlineStr">
         <is>
-          <t>Center_for_Active_Living_CAL_Comprehensive_Report_v1.md</t>
+          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.md</t>
         </is>
       </c>
       <c r="E103" s="15" t="inlineStr">
@@ -8427,46 +8427,46 @@
         </is>
       </c>
       <c r="F103" s="17" t="n">
-        <v>32670</v>
+        <v>31676</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>31.9 KB</t>
+          <t>30.9 KB</t>
         </is>
       </c>
       <c r="H103" s="15" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="I103" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham / CALBC / EDM Studio</t>
+          <t>Primary Municipal Records / Mass. Registry of Deeds</t>
         </is>
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
-          <t>M.G.L. c. 44, § 7; Mass. Const. Amend. Art. 97; 2026 ATM Art. 12</t>
+          <t>Historical M.G.L. c. 184A, § 3; M.G.L. c. 184, § 23; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
         </is>
       </c>
       <c r="K103" s="18" t="inlineStr">
         <is>
-          <t>Comprehensive 12-section investigation of the Center for Active Living at Bare Cove Park Drive and its April 27, 2026 Town Meeting defeat (510 Yes to 470 No; failed 2/3 debt supermajority).</t>
+          <t>Preliminary primary-source research chronology and record index; strictly neutral factual reporting; segregates verified facts, factual inferences, and open legal questions; includes missing documents inventory and disclaimer. Not a title opinion.</t>
         </is>
       </c>
       <c r="L103" s="15" t="inlineStr">
         <is>
-          <t>Complete Analytical Report (Verified)</t>
+          <t>Neutral Primary Source Research Index &amp; Inventory (Verified)</t>
         </is>
       </c>
       <c r="M103" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 16:19</t>
+          <t>2026-09-17 09:44</t>
         </is>
       </c>
       <c r="N103" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/executive_reports/Center_for_Active_Living_CAL_Comprehensive_Report_v1.md</t>
+          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.md</t>
         </is>
       </c>
     </row>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>Center_for_Active_Living_CAL_Comprehensive_Report_v1.pdf</t>
+          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.pdf</t>
         </is>
       </c>
       <c r="E104" s="19" t="inlineStr">
@@ -8497,46 +8497,46 @@
         </is>
       </c>
       <c r="F104" s="21" t="n">
-        <v>93076</v>
+        <v>119536</v>
       </c>
       <c r="G104" s="22" t="inlineStr">
         <is>
-          <t>90.9 KB</t>
+          <t>116.7 KB</t>
         </is>
       </c>
       <c r="H104" s="19" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="I104" s="20" t="inlineStr">
         <is>
-          <t>Town of Hingham / CALBC / EDM Studio</t>
+          <t>Primary Municipal Records / Mass. Registry of Deeds</t>
         </is>
       </c>
       <c r="J104" s="20" t="inlineStr">
         <is>
-          <t>M.G.L. c. 44, § 7; Mass. Const. Amend. Art. 97; 2026 ATM Art. 12</t>
+          <t>Historical M.G.L. c. 184A, § 3; M.G.L. c. 184, § 23; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
         </is>
       </c>
       <c r="K104" s="23" t="inlineStr">
         <is>
-          <t>Comprehensive 12-section investigation of the Center for Active Living at Bare Cove Park Drive and its April 27, 2026 Town Meeting defeat (510 Yes to 470 No; failed 2/3 debt supermajority).</t>
+          <t>Preliminary primary-source research chronology and record index; strictly neutral factual reporting; segregates verified facts, factual inferences, and open legal questions; includes missing documents inventory and disclaimer. Not a title opinion.</t>
         </is>
       </c>
       <c r="L104" s="19" t="inlineStr">
         <is>
-          <t>Complete Analytical Report (Verified)</t>
+          <t>Neutral Primary Source Research Index &amp; Inventory (Verified)</t>
         </is>
       </c>
       <c r="M104" s="19" t="inlineStr">
         <is>
-          <t>2026-09-16 16:19</t>
+          <t>2026-09-17 09:44</t>
         </is>
       </c>
       <c r="N104" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/executive_reports/Center_for_Active_Living_CAL_Comprehensive_Report_v1.pdf</t>
+          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.pdf</t>
         </is>
       </c>
     </row>
@@ -8553,25 +8553,25 @@
       </c>
       <c r="C105" s="16" t="inlineStr">
         <is>
-          <t>Master Chronological Compendiums</t>
+          <t>Executive Reports &amp; Briefings</t>
         </is>
       </c>
       <c r="D105" s="16" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Comprehensive_Chronological_Master_Archive_v1.pdf</t>
+          <t>Center_for_Active_Living_CAL_Comprehensive_Report_v1.md</t>
         </is>
       </c>
       <c r="E105" s="15" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F105" s="17" t="n">
-        <v>105271962</v>
+        <v>32670</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>100.4 MB</t>
+          <t>31.9 KB</t>
         </is>
       </c>
       <c r="H105" s="15" t="inlineStr">
@@ -8581,32 +8581,32 @@
       </c>
       <c r="I105" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>Town of Hingham / CALBC / EDM Studio</t>
         </is>
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>M.G.L. c. 44, § 7; Mass. Const. Amend. Art. 97; 2026 ATM Art. 12</t>
         </is>
       </c>
       <c r="K105" s="18" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Comprehensive 12-section investigation of the Center for Active Living at Bare Cove Park Drive and its April 27, 2026 Town Meeting defeat (510 Yes to 470 No; failed 2/3 debt supermajority).</t>
         </is>
       </c>
       <c r="L105" s="15" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Complete Analytical Report (Verified)</t>
         </is>
       </c>
       <c r="M105" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 09:11</t>
+          <t>2026-09-16 16:19</t>
         </is>
       </c>
       <c r="N105" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/master_compendiums/100_Beal_Street_Comprehensive_Chronological_Master_Archive_v1.pdf</t>
+          <t>agent_created_deliverables/executive_reports/Center_for_Active_Living_CAL_Comprehensive_Report_v1.md</t>
         </is>
       </c>
     </row>
@@ -8623,25 +8623,25 @@
       </c>
       <c r="C106" s="20" t="inlineStr">
         <is>
-          <t>Master Chronological Compendiums</t>
+          <t>Executive Reports &amp; Briefings</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Master_Compendium_v1.md</t>
+          <t>Center_for_Active_Living_CAL_Comprehensive_Report_v1.pdf</t>
         </is>
       </c>
       <c r="E106" s="19" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="F106" s="21" t="n">
-        <v>34240</v>
+        <v>93076</v>
       </c>
       <c r="G106" s="22" t="inlineStr">
         <is>
-          <t>33.4 KB</t>
+          <t>90.9 KB</t>
         </is>
       </c>
       <c r="H106" s="19" t="inlineStr">
@@ -8651,32 +8651,32 @@
       </c>
       <c r="I106" s="20" t="inlineStr">
         <is>
-          <t>AI Research Team &amp; Quality Control</t>
+          <t>Town of Hingham / CALBC / EDM Studio</t>
         </is>
       </c>
       <c r="J106" s="20" t="inlineStr">
         <is>
-          <t>Complete Municipal &amp; State Statutory Compilation</t>
+          <t>M.G.L. c. 44, § 7; Mass. Const. Amend. Art. 97; 2026 ATM Art. 12</t>
         </is>
       </c>
       <c r="K106" s="23" t="inlineStr">
         <is>
-          <t>Comprehensive multi-megabyte compendium transcribing and synthesizing all historical warrants, board minutes, registry deeds, and environmental filings.</t>
+          <t>Comprehensive 12-section investigation of the Center for Active Living at Bare Cove Park Drive and its April 27, 2026 Town Meeting defeat (510 Yes to 470 No; failed 2/3 debt supermajority).</t>
         </is>
       </c>
       <c r="L106" s="19" t="inlineStr">
         <is>
-          <t>Master Synthesis (Verified)</t>
+          <t>Complete Analytical Report (Verified)</t>
         </is>
       </c>
       <c r="M106" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 10:22</t>
+          <t>2026-09-16 16:19</t>
         </is>
       </c>
       <c r="N106" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/master_compendiums/100_Beal_Street_Master_Compendium_v1.md</t>
+          <t>agent_created_deliverables/executive_reports/Center_for_Active_Living_CAL_Comprehensive_Report_v1.pdf</t>
         </is>
       </c>
     </row>
@@ -8698,55 +8698,55 @@
       </c>
       <c r="D107" s="16" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Master_Compendium_v2.md</t>
+          <t>100_Beal_Street_Comprehensive_Chronological_Master_Archive_v1.pdf</t>
         </is>
       </c>
       <c r="E107" s="15" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="F107" s="17" t="n">
-        <v>4225700</v>
+        <v>105271962</v>
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>4.0 MB</t>
+          <t>100.4 MB</t>
         </is>
       </c>
       <c r="H107" s="15" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I107" s="16" t="inlineStr">
         <is>
-          <t>AI Research Team &amp; Quality Control</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>Complete Municipal &amp; State Statutory Compilation</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K107" s="18" t="inlineStr">
         <is>
-          <t>Comprehensive multi-megabyte compendium transcribing and synthesizing all historical warrants, board minutes, registry deeds, and environmental filings.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L107" s="15" t="inlineStr">
         <is>
-          <t>Master Synthesis (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M107" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 16:02</t>
+          <t>2026-09-16 09:11</t>
         </is>
       </c>
       <c r="N107" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/master_compendiums/100_Beal_Street_Master_Compendium_v2.md</t>
+          <t>agent_created_deliverables/master_compendiums/100_Beal_Street_Comprehensive_Chronological_Master_Archive_v1.pdf</t>
         </is>
       </c>
     </row>
@@ -8763,12 +8763,12 @@
       </c>
       <c r="C108" s="20" t="inlineStr">
         <is>
-          <t>Companion Markdown Transcriptions</t>
+          <t>Master Chronological Compendiums</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>100-Beal-Street-ANRAD-Application_v1.md</t>
+          <t>100_Beal_Street_Master_Compendium_v1.md</t>
         </is>
       </c>
       <c r="E108" s="19" t="inlineStr">
@@ -8777,11 +8777,11 @@
         </is>
       </c>
       <c r="F108" s="21" t="n">
-        <v>66942</v>
+        <v>34240</v>
       </c>
       <c r="G108" s="22" t="inlineStr">
         <is>
-          <t>65.4 KB</t>
+          <t>33.4 KB</t>
         </is>
       </c>
       <c r="H108" s="19" t="inlineStr">
@@ -8791,32 +8791,32 @@
       </c>
       <c r="I108" s="20" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>AI Research Team &amp; Quality Control</t>
         </is>
       </c>
       <c r="J108" s="20" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>Complete Municipal &amp; State Statutory Compilation</t>
         </is>
       </c>
       <c r="K108" s="23" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Comprehensive multi-megabyte compendium transcribing and synthesizing all historical warrants, board minutes, registry deeds, and environmental filings.</t>
         </is>
       </c>
       <c r="L108" s="19" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Master Synthesis (Verified)</t>
         </is>
       </c>
       <c r="M108" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 10:23</t>
+          <t>2026-09-14 10:22</t>
         </is>
       </c>
       <c r="N108" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/100-Beal-Street-ANRAD-Application_v1.md</t>
+          <t>agent_created_deliverables/master_compendiums/100_Beal_Street_Master_Compendium_v1.md</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="C109" s="16" t="inlineStr">
         <is>
-          <t>Companion Markdown Transcriptions</t>
+          <t>Master Chronological Compendiums</t>
         </is>
       </c>
       <c r="D109" s="16" t="inlineStr">
         <is>
-          <t>100-Beal-Street-ANRAD-Plans_v1.md</t>
+          <t>100_Beal_Street_Master_Compendium_v2.md</t>
         </is>
       </c>
       <c r="E109" s="15" t="inlineStr">
@@ -8847,46 +8847,46 @@
         </is>
       </c>
       <c r="F109" s="17" t="n">
-        <v>21350</v>
+        <v>4225700</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>20.8 KB</t>
+          <t>4.0 MB</t>
         </is>
       </c>
       <c r="H109" s="15" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="I109" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>AI Research Team &amp; Quality Control</t>
         </is>
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>Complete Municipal &amp; State Statutory Compilation</t>
         </is>
       </c>
       <c r="K109" s="18" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Comprehensive multi-megabyte compendium transcribing and synthesizing all historical warrants, board minutes, registry deeds, and environmental filings.</t>
         </is>
       </c>
       <c r="L109" s="15" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Master Synthesis (Verified)</t>
         </is>
       </c>
       <c r="M109" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14 10:23</t>
+          <t>2026-09-16 16:02</t>
         </is>
       </c>
       <c r="N109" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/100-Beal-Street-ANRAD-Plans_v1.md</t>
+          <t>agent_created_deliverables/master_compendiums/100_Beal_Street_Master_Compendium_v2.md</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="D110" s="20" t="inlineStr">
         <is>
-          <t>25-Bare-Cove-Park-Drive-Public-Comments-Combined-100-Beal-Mention_v1.md</t>
+          <t>100-Beal-Street-ANRAD-Application_v1.md</t>
         </is>
       </c>
       <c r="E110" s="19" t="inlineStr">
@@ -8917,11 +8917,11 @@
         </is>
       </c>
       <c r="F110" s="21" t="n">
-        <v>41086</v>
+        <v>66942</v>
       </c>
       <c r="G110" s="22" t="inlineStr">
         <is>
-          <t>40.1 KB</t>
+          <t>65.4 KB</t>
         </is>
       </c>
       <c r="H110" s="19" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="N110" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/25-Bare-Cove-Park-Drive-Public-Comments-Combined-100-Beal-Mention_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/100-Beal-Street-ANRAD-Application_v1.md</t>
         </is>
       </c>
     </row>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="D111" s="16" t="inlineStr">
         <is>
-          <t>25-Bare-Cove-Park-Drive-Supplemental-Information-Letter-ORAD-034-1509_v1.md</t>
+          <t>100-Beal-Street-ANRAD-Plans_v1.md</t>
         </is>
       </c>
       <c r="E111" s="15" t="inlineStr">
@@ -8987,11 +8987,11 @@
         </is>
       </c>
       <c r="F111" s="17" t="n">
-        <v>27469</v>
+        <v>21350</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>26.8 KB</t>
+          <t>20.8 KB</t>
         </is>
       </c>
       <c r="H111" s="15" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="N111" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/25-Bare-Cove-Park-Drive-Supplemental-Information-Letter-ORAD-034-1509_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/100-Beal-Street-ANRAD-Plans_v1.md</t>
         </is>
       </c>
     </row>
@@ -9048,7 +9048,7 @@
       </c>
       <c r="D112" s="20" t="inlineStr">
         <is>
-          <t>Bare-Cove-Park-Drive-HCAL-Peer-Review-Report-ORAD-034-1509-Citation_v1.md</t>
+          <t>25-Bare-Cove-Park-Drive-Public-Comments-Combined-100-Beal-Mention_v1.md</t>
         </is>
       </c>
       <c r="E112" s="19" t="inlineStr">
@@ -9057,11 +9057,11 @@
         </is>
       </c>
       <c r="F112" s="21" t="n">
-        <v>20900</v>
+        <v>41086</v>
       </c>
       <c r="G112" s="22" t="inlineStr">
         <is>
-          <t>20.4 KB</t>
+          <t>40.1 KB</t>
         </is>
       </c>
       <c r="H112" s="19" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="N112" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Bare-Cove-Park-Drive-HCAL-Peer-Review-Report-ORAD-034-1509-Citation_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/25-Bare-Cove-Park-Drive-Public-Comments-Combined-100-Beal-Mention_v1.md</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="D113" s="16" t="inlineStr">
         <is>
-          <t>Bohler_Due_Diligence_Feasibility_Report_and_Lucas_Wetlands_v1.md</t>
+          <t>25-Bare-Cove-Park-Drive-Supplemental-Information-Letter-ORAD-034-1509_v1.md</t>
         </is>
       </c>
       <c r="E113" s="15" t="inlineStr">
@@ -9127,11 +9127,11 @@
         </is>
       </c>
       <c r="F113" s="17" t="n">
-        <v>100475</v>
+        <v>27469</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>98.1 KB</t>
+          <t>26.8 KB</t>
         </is>
       </c>
       <c r="H113" s="15" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="N113" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Bohler_Due_Diligence_Feasibility_Report_and_Lucas_Wetlands_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/25-Bare-Cove-Park-Drive-Supplemental-Information-Letter-ORAD-034-1509_v1.md</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Agenda_2024-11-04_DEP_034-1509_v1.md</t>
+          <t>Bare-Cove-Park-Drive-HCAL-Peer-Review-Report-ORAD-034-1509-Citation_v1.md</t>
         </is>
       </c>
       <c r="E114" s="19" t="inlineStr">
@@ -9197,11 +9197,11 @@
         </is>
       </c>
       <c r="F114" s="21" t="n">
-        <v>3569</v>
+        <v>20900</v>
       </c>
       <c r="G114" s="22" t="inlineStr">
         <is>
-          <t>3.5 KB</t>
+          <t>20.4 KB</t>
         </is>
       </c>
       <c r="H114" s="19" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="N114" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-11-04_DEP_034-1509_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Bare-Cove-Park-Drive-HCAL-Peer-Review-Report-ORAD-034-1509-Citation_v1.md</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="D115" s="16" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Agenda_2024-11-18_v1.md</t>
+          <t>Bohler_Due_Diligence_Feasibility_Report_and_Lucas_Wetlands_v1.md</t>
         </is>
       </c>
       <c r="E115" s="15" t="inlineStr">
@@ -9267,11 +9267,11 @@
         </is>
       </c>
       <c r="F115" s="17" t="n">
-        <v>3922</v>
+        <v>100475</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>3.8 KB</t>
+          <t>98.1 KB</t>
         </is>
       </c>
       <c r="H115" s="15" t="inlineStr">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="N115" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-11-18_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Bohler_Due_Diligence_Feasibility_Report_and_Lucas_Wetlands_v1.md</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Agenda_2024-12-02_v1.md</t>
+          <t>Conservation_Commission_Agenda_2024-11-04_DEP_034-1509_v1.md</t>
         </is>
       </c>
       <c r="E116" s="19" t="inlineStr">
@@ -9337,11 +9337,11 @@
         </is>
       </c>
       <c r="F116" s="21" t="n">
-        <v>3922</v>
+        <v>3569</v>
       </c>
       <c r="G116" s="22" t="inlineStr">
         <is>
-          <t>3.8 KB</t>
+          <t>3.5 KB</t>
         </is>
       </c>
       <c r="H116" s="19" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-12-02_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-11-04_DEP_034-1509_v1.md</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D117" s="16" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Agenda_2024-12-16_v1.md</t>
+          <t>Conservation_Commission_Agenda_2024-11-18_v1.md</t>
         </is>
       </c>
       <c r="E117" s="15" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="N117" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-12-16_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-11-18_v1.md</t>
         </is>
       </c>
     </row>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Minutes_2024-11-04_DEP_034-1509_v1.md</t>
+          <t>Conservation_Commission_Agenda_2024-12-02_v1.md</t>
         </is>
       </c>
       <c r="E118" s="19" t="inlineStr">
@@ -9477,11 +9477,11 @@
         </is>
       </c>
       <c r="F118" s="21" t="n">
-        <v>29843</v>
+        <v>3922</v>
       </c>
       <c r="G118" s="22" t="inlineStr">
         <is>
-          <t>29.1 KB</t>
+          <t>3.8 KB</t>
         </is>
       </c>
       <c r="H118" s="19" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="N118" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-11-04_DEP_034-1509_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-12-02_v1.md</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="D119" s="16" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Minutes_2024-11-18_v1.md</t>
+          <t>Conservation_Commission_Agenda_2024-12-16_v1.md</t>
         </is>
       </c>
       <c r="E119" s="15" t="inlineStr">
@@ -9547,11 +9547,11 @@
         </is>
       </c>
       <c r="F119" s="17" t="n">
-        <v>46813</v>
+        <v>3922</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>45.7 KB</t>
+          <t>3.8 KB</t>
         </is>
       </c>
       <c r="H119" s="15" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="N119" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-11-18_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-12-16_v1.md</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="D120" s="20" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Minutes_2024-12-02_v1.md</t>
+          <t>Conservation_Commission_Minutes_2024-11-04_DEP_034-1509_v1.md</t>
         </is>
       </c>
       <c r="E120" s="19" t="inlineStr">
@@ -9617,11 +9617,11 @@
         </is>
       </c>
       <c r="F120" s="21" t="n">
-        <v>46813</v>
+        <v>29843</v>
       </c>
       <c r="G120" s="22" t="inlineStr">
         <is>
-          <t>45.7 KB</t>
+          <t>29.1 KB</t>
         </is>
       </c>
       <c r="H120" s="19" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-12-02_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-11-04_DEP_034-1509_v1.md</t>
         </is>
       </c>
     </row>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="D121" s="16" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Minutes_2024-12-16_v1.md</t>
+          <t>Conservation_Commission_Minutes_2024-11-18_v1.md</t>
         </is>
       </c>
       <c r="E121" s="15" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="N121" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-12-16_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-11-18_v1.md</t>
         </is>
       </c>
     </row>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="D122" s="20" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2024-02-13_Beal_Surplus_MHP_RFP_v1.md</t>
+          <t>Conservation_Commission_Minutes_2024-12-02_v1.md</t>
         </is>
       </c>
       <c r="E122" s="19" t="inlineStr">
@@ -9757,11 +9757,11 @@
         </is>
       </c>
       <c r="F122" s="21" t="n">
-        <v>1567</v>
+        <v>46813</v>
       </c>
       <c r="G122" s="22" t="inlineStr">
         <is>
-          <t>1.5 KB</t>
+          <t>45.7 KB</t>
         </is>
       </c>
       <c r="H122" s="19" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="N122" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2024-02-13_Beal_Surplus_MHP_RFP_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-12-02_v1.md</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="D123" s="16" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2024-09-10_Beal_Excess_Declaration_RFP_Release_v1.md</t>
+          <t>Conservation_Commission_Minutes_2024-12-16_v1.md</t>
         </is>
       </c>
       <c r="E123" s="15" t="inlineStr">
@@ -9827,11 +9827,11 @@
         </is>
       </c>
       <c r="F123" s="17" t="n">
-        <v>2036</v>
+        <v>46813</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>2.0 KB</t>
+          <t>45.7 KB</t>
         </is>
       </c>
       <c r="H123" s="15" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="N123" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2024-09-10_Beal_Excess_Declaration_RFP_Release_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-12-16_v1.md</t>
         </is>
       </c>
     </row>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="D124" s="20" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2025-08-12_Peabody_Award_LDDA_v1.md</t>
+          <t>HHA_Agenda_2024-02-13_Beal_Surplus_MHP_RFP_v1.md</t>
         </is>
       </c>
       <c r="E124" s="19" t="inlineStr">
@@ -9897,11 +9897,11 @@
         </is>
       </c>
       <c r="F124" s="21" t="n">
-        <v>2180</v>
+        <v>1567</v>
       </c>
       <c r="G124" s="22" t="inlineStr">
         <is>
-          <t>2.1 KB</t>
+          <t>1.5 KB</t>
         </is>
       </c>
       <c r="H124" s="19" t="inlineStr">
@@ -9911,22 +9911,22 @@
       </c>
       <c r="I124" s="20" t="inlineStr">
         <is>
-          <t>Hingham Housing Authority Board of Commissioners</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J124" s="20" t="inlineStr">
         <is>
-          <t>M.G.L. c. 30B, § 16</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K124" s="23" t="inlineStr">
         <is>
-          <t>Official meeting minutes of August 12, 2025 recording 4-0 vote designating Peabody Properties / AHSC as developer for 100 Beal Street.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L124" s="19" t="inlineStr">
         <is>
-          <t>Official Board Minutes (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M124" s="19" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="N124" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2025-08-12_Peabody_Award_LDDA_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2024-02-13_Beal_Surplus_MHP_RFP_v1.md</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="D125" s="16" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2026-02-10_Meeting_v1.md</t>
+          <t>HHA_Agenda_2024-09-10_Beal_Excess_Declaration_RFP_Release_v1.md</t>
         </is>
       </c>
       <c r="E125" s="15" t="inlineStr">
@@ -9967,11 +9967,11 @@
         </is>
       </c>
       <c r="F125" s="17" t="n">
-        <v>2668</v>
+        <v>2036</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>2.6 KB</t>
+          <t>2.0 KB</t>
         </is>
       </c>
       <c r="H125" s="15" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="N125" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-02-10_Meeting_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2024-09-10_Beal_Excess_Declaration_RFP_Release_v1.md</t>
         </is>
       </c>
     </row>
@@ -10028,7 +10028,7 @@
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2026-04-14_Beal_Sprinkler_Bids_v1.md</t>
+          <t>HHA_Agenda_2025-08-12_Peabody_Award_LDDA_v1.md</t>
         </is>
       </c>
       <c r="E126" s="19" t="inlineStr">
@@ -10037,11 +10037,11 @@
         </is>
       </c>
       <c r="F126" s="21" t="n">
-        <v>2983</v>
+        <v>2180</v>
       </c>
       <c r="G126" s="22" t="inlineStr">
         <is>
-          <t>2.9 KB</t>
+          <t>2.1 KB</t>
         </is>
       </c>
       <c r="H126" s="19" t="inlineStr">
@@ -10051,22 +10051,22 @@
       </c>
       <c r="I126" s="20" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>Hingham Housing Authority Board of Commissioners</t>
         </is>
       </c>
       <c r="J126" s="20" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>M.G.L. c. 30B, § 16</t>
         </is>
       </c>
       <c r="K126" s="23" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Official meeting minutes of August 12, 2025 recording 4-0 vote designating Peabody Properties / AHSC as developer for 100 Beal Street.</t>
         </is>
       </c>
       <c r="L126" s="19" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Official Board Minutes (Verified)</t>
         </is>
       </c>
       <c r="M126" s="19" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="N126" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-04-14_Beal_Sprinkler_Bids_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2025-08-12_Peabody_Award_LDDA_v1.md</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="D127" s="16" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2026-06-09_Annual_Plan_v1.md</t>
+          <t>HHA_Agenda_2026-02-10_Meeting_v1.md</t>
         </is>
       </c>
       <c r="E127" s="15" t="inlineStr">
@@ -10107,11 +10107,11 @@
         </is>
       </c>
       <c r="F127" s="17" t="n">
-        <v>1900</v>
+        <v>2668</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>1.9 KB</t>
+          <t>2.6 KB</t>
         </is>
       </c>
       <c r="H127" s="15" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="N127" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-06-09_Annual_Plan_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-02-10_Meeting_v1.md</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2026-07-14_Beal_St_Sprinklers_v1.md</t>
+          <t>HHA_Agenda_2026-04-14_Beal_Sprinkler_Bids_v1.md</t>
         </is>
       </c>
       <c r="E128" s="19" t="inlineStr">
@@ -10177,11 +10177,11 @@
         </is>
       </c>
       <c r="F128" s="21" t="n">
-        <v>3257</v>
+        <v>2983</v>
       </c>
       <c r="G128" s="22" t="inlineStr">
         <is>
-          <t>3.2 KB</t>
+          <t>2.9 KB</t>
         </is>
       </c>
       <c r="H128" s="19" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-07-14_Beal_St_Sprinklers_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-04-14_Beal_Sprinkler_Bids_v1.md</t>
         </is>
       </c>
     </row>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="D129" s="16" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2026-08-25_Land_Disposition_Peabody_v1.md</t>
+          <t>HHA_Agenda_2026-06-09_Annual_Plan_v1.md</t>
         </is>
       </c>
       <c r="E129" s="15" t="inlineStr">
@@ -10247,11 +10247,11 @@
         </is>
       </c>
       <c r="F129" s="17" t="n">
-        <v>1501</v>
+        <v>1900</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>1.5 KB</t>
+          <t>1.9 KB</t>
         </is>
       </c>
       <c r="H129" s="15" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="N129" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-08-25_Land_Disposition_Peabody_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-06-09_Annual_Plan_v1.md</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>HHA_Minutes_2019-07-09_100_Beal_School_Tract_II_v1.md</t>
+          <t>HHA_Agenda_2026-07-14_Beal_St_Sprinklers_v1.md</t>
         </is>
       </c>
       <c r="E130" s="19" t="inlineStr">
@@ -10317,11 +10317,11 @@
         </is>
       </c>
       <c r="F130" s="21" t="n">
-        <v>6627</v>
+        <v>3257</v>
       </c>
       <c r="G130" s="22" t="inlineStr">
         <is>
-          <t>6.5 KB</t>
+          <t>3.2 KB</t>
         </is>
       </c>
       <c r="H130" s="19" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="N130" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2019-07-09_100_Beal_School_Tract_II_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-07-14_Beal_St_Sprinklers_v1.md</t>
         </is>
       </c>
     </row>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D131" s="16" t="inlineStr">
         <is>
-          <t>HHA_Minutes_2021-09-07_Rescission_Vote_v1.md</t>
+          <t>HHA_Agenda_2026-08-25_Land_Disposition_Peabody_v1.md</t>
         </is>
       </c>
       <c r="E131" s="15" t="inlineStr">
@@ -10387,11 +10387,11 @@
         </is>
       </c>
       <c r="F131" s="17" t="n">
-        <v>9130</v>
+        <v>1501</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>8.9 KB</t>
+          <t>1.5 KB</t>
         </is>
       </c>
       <c r="H131" s="15" t="inlineStr">
@@ -10401,32 +10401,32 @@
       </c>
       <c r="I131" s="16" t="inlineStr">
         <is>
-          <t>Hingham Housing Authority (Dir. James Marathas)</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J131" s="16" t="inlineStr">
         <is>
-          <t>M.G.L. c. 121B, § 34; HHA By-Laws</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K131" s="18" t="inlineStr">
         <is>
-          <t>Official meeting minutes of Sept 7, 2021 recording 4-0 vote formally rescinding the June 5, 2019 transfer motion, keeping land in HHA ownership.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L131" s="15" t="inlineStr">
         <is>
-          <t>Official Board Minutes (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M131" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 16:46</t>
+          <t>2026-09-14 10:23</t>
         </is>
       </c>
       <c r="N131" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2021-09-07_Rescission_Vote_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-08-25_Land_Disposition_Peabody_v1.md</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="D132" s="20" t="inlineStr">
         <is>
-          <t>HHA_Minutes_2025-08-12_Peabody_Award_Authentic_v1.md</t>
+          <t>HHA_Minutes_2019-07-09_100_Beal_School_Tract_II_v1.md</t>
         </is>
       </c>
       <c r="E132" s="19" t="inlineStr">
@@ -10457,11 +10457,11 @@
         </is>
       </c>
       <c r="F132" s="21" t="n">
-        <v>4338</v>
+        <v>6627</v>
       </c>
       <c r="G132" s="22" t="inlineStr">
         <is>
-          <t>4.2 KB</t>
+          <t>6.5 KB</t>
         </is>
       </c>
       <c r="H132" s="19" t="inlineStr">
@@ -10471,32 +10471,32 @@
       </c>
       <c r="I132" s="20" t="inlineStr">
         <is>
-          <t>Hingham Housing Authority Board of Commissioners</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J132" s="20" t="inlineStr">
         <is>
-          <t>M.G.L. c. 30B, § 16</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K132" s="23" t="inlineStr">
         <is>
-          <t>Official meeting minutes of August 12, 2025 recording 4-0 vote designating Peabody Properties / AHSC as developer for 100 Beal Street.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L132" s="19" t="inlineStr">
         <is>
-          <t>Official Board Minutes (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M132" s="19" t="inlineStr">
         <is>
-          <t>2026-09-16 16:46</t>
+          <t>2026-09-14 10:23</t>
         </is>
       </c>
       <c r="N132" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2025-08-12_Peabody_Award_Authentic_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2019-07-09_100_Beal_School_Tract_II_v1.md</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="D133" s="16" t="inlineStr">
         <is>
-          <t>HHA_Minutes_2025-08-12_Peabody_Award_LDDA_v1.md</t>
+          <t>HHA_Minutes_2021-09-07_Rescission_Vote_v1.md</t>
         </is>
       </c>
       <c r="E133" s="15" t="inlineStr">
@@ -10527,11 +10527,11 @@
         </is>
       </c>
       <c r="F133" s="17" t="n">
-        <v>7292</v>
+        <v>9130</v>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>7.1 KB</t>
+          <t>8.9 KB</t>
         </is>
       </c>
       <c r="H133" s="15" t="inlineStr">
@@ -10541,17 +10541,17 @@
       </c>
       <c r="I133" s="16" t="inlineStr">
         <is>
-          <t>Hingham Housing Authority Board of Commissioners</t>
+          <t>Hingham Housing Authority (Dir. James Marathas)</t>
         </is>
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>M.G.L. c. 30B, § 16</t>
+          <t>M.G.L. c. 121B, § 34; HHA By-Laws</t>
         </is>
       </c>
       <c r="K133" s="18" t="inlineStr">
         <is>
-          <t>Official meeting minutes of August 12, 2025 recording 4-0 vote designating Peabody Properties / AHSC as developer for 100 Beal Street.</t>
+          <t>Official meeting minutes of Sept 7, 2021 recording 4-0 vote formally rescinding the June 5, 2019 transfer motion, keeping land in HHA ownership.</t>
         </is>
       </c>
       <c r="L133" s="15" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="M133" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14 10:23</t>
+          <t>2026-09-16 16:46</t>
         </is>
       </c>
       <c r="N133" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2025-08-12_Peabody_Award_LDDA_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2021-09-07_Rescission_Vote_v1.md</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="D134" s="20" t="inlineStr">
         <is>
-          <t>Hingham-HA-Beal-St-RFP-04-16-25_Final_all-attachments_v1.md</t>
+          <t>HHA_Minutes_2025-08-12_Peabody_Award_Authentic_v1.md</t>
         </is>
       </c>
       <c r="E134" s="19" t="inlineStr">
@@ -10597,11 +10597,11 @@
         </is>
       </c>
       <c r="F134" s="21" t="n">
-        <v>303658</v>
+        <v>4338</v>
       </c>
       <c r="G134" s="22" t="inlineStr">
         <is>
-          <t>296.5 KB</t>
+          <t>4.2 KB</t>
         </is>
       </c>
       <c r="H134" s="19" t="inlineStr">
@@ -10611,32 +10611,32 @@
       </c>
       <c r="I134" s="20" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>Hingham Housing Authority Board of Commissioners</t>
         </is>
       </c>
       <c r="J134" s="20" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>M.G.L. c. 30B, § 16</t>
         </is>
       </c>
       <c r="K134" s="23" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Official meeting minutes of August 12, 2025 recording 4-0 vote designating Peabody Properties / AHSC as developer for 100 Beal Street.</t>
         </is>
       </c>
       <c r="L134" s="19" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Official Board Minutes (Verified)</t>
         </is>
       </c>
       <c r="M134" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 10:23</t>
+          <t>2026-09-16 16:46</t>
         </is>
       </c>
       <c r="N134" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham-HA-Beal-St-RFP-04-16-25_Final_all-attachments_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2025-08-12_Peabody_Award_Authentic_v1.md</t>
         </is>
       </c>
     </row>
@@ -10658,7 +10658,7 @@
       </c>
       <c r="D135" s="16" t="inlineStr">
         <is>
-          <t>Hingham_100_Beal_ALTA_Survey_and_Subdivision_Plans_v1.md</t>
+          <t>HHA_Minutes_2025-08-12_Peabody_Award_LDDA_v1.md</t>
         </is>
       </c>
       <c r="E135" s="15" t="inlineStr">
@@ -10667,11 +10667,11 @@
         </is>
       </c>
       <c r="F135" s="17" t="n">
-        <v>33044</v>
+        <v>7292</v>
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>32.3 KB</t>
+          <t>7.1 KB</t>
         </is>
       </c>
       <c r="H135" s="15" t="inlineStr">
@@ -10681,22 +10681,22 @@
       </c>
       <c r="I135" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>Hingham Housing Authority Board of Commissioners</t>
         </is>
       </c>
       <c r="J135" s="16" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>M.G.L. c. 30B, § 16</t>
         </is>
       </c>
       <c r="K135" s="18" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Official meeting minutes of August 12, 2025 recording 4-0 vote designating Peabody Properties / AHSC as developer for 100 Beal Street.</t>
         </is>
       </c>
       <c r="L135" s="15" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Official Board Minutes (Verified)</t>
         </is>
       </c>
       <c r="M135" s="15" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="N135" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_100_Beal_ALTA_Survey_and_Subdivision_Plans_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2025-08-12_Peabody_Award_LDDA_v1.md</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="D136" s="20" t="inlineStr">
         <is>
-          <t>Hingham_Beal_Street_Deed_1989_and_ZBA_Decision_v1.md</t>
+          <t>Hingham-HA-Beal-St-RFP-04-16-25_Final_all-attachments_v1.md</t>
         </is>
       </c>
       <c r="E136" s="19" t="inlineStr">
@@ -10737,11 +10737,11 @@
         </is>
       </c>
       <c r="F136" s="21" t="n">
-        <v>11705</v>
+        <v>303658</v>
       </c>
       <c r="G136" s="22" t="inlineStr">
         <is>
-          <t>11.4 KB</t>
+          <t>296.5 KB</t>
         </is>
       </c>
       <c r="H136" s="19" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="N136" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Beal_Street_Deed_1989_and_ZBA_Decision_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham-HA-Beal-St-RFP-04-16-25_Final_all-attachments_v1.md</t>
         </is>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="D137" s="16" t="inlineStr">
         <is>
-          <t>Hingham_Housing_Authority_Draft_Ground_Lease_100_Beal_v1.md</t>
+          <t>Hingham_100_Beal_ALTA_Survey_and_Subdivision_Plans_v1.md</t>
         </is>
       </c>
       <c r="E137" s="15" t="inlineStr">
@@ -10807,11 +10807,11 @@
         </is>
       </c>
       <c r="F137" s="17" t="n">
-        <v>56917</v>
+        <v>33044</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>55.6 KB</t>
+          <t>32.3 KB</t>
         </is>
       </c>
       <c r="H137" s="15" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="N137" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Housing_Authority_Draft_Ground_Lease_100_Beal_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_100_Beal_ALTA_Survey_and_Subdivision_Plans_v1.md</t>
         </is>
       </c>
     </row>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="D138" s="20" t="inlineStr">
         <is>
-          <t>Hingham_Housing_Authority_Draft_LDA_100_Beal_v1.md</t>
+          <t>Hingham_Beal_Street_Deed_1989_and_ZBA_Decision_v1.md</t>
         </is>
       </c>
       <c r="E138" s="19" t="inlineStr">
@@ -10877,11 +10877,11 @@
         </is>
       </c>
       <c r="F138" s="21" t="n">
-        <v>68604</v>
+        <v>11705</v>
       </c>
       <c r="G138" s="22" t="inlineStr">
         <is>
-          <t>67.0 KB</t>
+          <t>11.4 KB</t>
         </is>
       </c>
       <c r="H138" s="19" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="N138" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Housing_Authority_Draft_LDA_100_Beal_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Beal_Street_Deed_1989_and_ZBA_Decision_v1.md</t>
         </is>
       </c>
     </row>
@@ -10938,7 +10938,7 @@
       </c>
       <c r="D139" s="16" t="inlineStr">
         <is>
-          <t>Hingham_Town_Charter_Bylaws_Excerpts_v1.md</t>
+          <t>Hingham_Housing_Authority_Draft_Ground_Lease_100_Beal_v1.md</t>
         </is>
       </c>
       <c r="E139" s="15" t="inlineStr">
@@ -10947,11 +10947,11 @@
         </is>
       </c>
       <c r="F139" s="17" t="n">
-        <v>11796</v>
+        <v>56917</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>11.5 KB</t>
+          <t>55.6 KB</t>
         </is>
       </c>
       <c r="H139" s="15" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="N139" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Charter_Bylaws_Excerpts_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Housing_Authority_Draft_Ground_Lease_100_Beal_v1.md</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="D140" s="20" t="inlineStr">
         <is>
-          <t>Hingham_Town_Meeting_2006_Beal_St_Amended_Deed_Vote_v1.md</t>
+          <t>Hingham_Housing_Authority_Draft_LDA_100_Beal_v1.md</t>
         </is>
       </c>
       <c r="E140" s="19" t="inlineStr">
@@ -11017,11 +11017,11 @@
         </is>
       </c>
       <c r="F140" s="21" t="n">
-        <v>11120</v>
+        <v>68604</v>
       </c>
       <c r="G140" s="22" t="inlineStr">
         <is>
-          <t>10.9 KB</t>
+          <t>67.0 KB</t>
         </is>
       </c>
       <c r="H140" s="19" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="N140" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_2006_Beal_St_Amended_Deed_Vote_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Housing_Authority_Draft_LDA_100_Beal_v1.md</t>
         </is>
       </c>
     </row>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="D141" s="16" t="inlineStr">
         <is>
-          <t>Hingham_Town_Meeting_Warrant_2006_Article_38_School_Tract_II_v1.md</t>
+          <t>Hingham_Town_Charter_Bylaws_Excerpts_v1.md</t>
         </is>
       </c>
       <c r="E141" s="15" t="inlineStr">
@@ -11087,11 +11087,11 @@
         </is>
       </c>
       <c r="F141" s="17" t="n">
-        <v>192413</v>
+        <v>11796</v>
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>187.9 KB</t>
+          <t>11.5 KB</t>
         </is>
       </c>
       <c r="H141" s="15" t="inlineStr">
@@ -11101,22 +11101,22 @@
       </c>
       <c r="I141" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham Select Board / Advisory Committee</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>M.G.L. c. 39, § 10 (Town Meeting Warrant)</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K141" s="18" t="inlineStr">
         <is>
-          <t>Official Town Meeting Warrant detailing capital budget requests, debt exclusion articles, and municipal bylaws.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L141" s="15" t="inlineStr">
         <is>
-          <t>Official Town Warrant (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M141" s="15" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="N141" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2006_Article_38_School_Tract_II_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Charter_Bylaws_Excerpts_v1.md</t>
         </is>
       </c>
     </row>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="D142" s="20" t="inlineStr">
         <is>
-          <t>Hingham_Town_Meeting_Warrant_2016_Article_24_100_Beal_Street_v1.md</t>
+          <t>Hingham_Town_Meeting_2006_Beal_St_Amended_Deed_Vote_v1.md</t>
         </is>
       </c>
       <c r="E142" s="19" t="inlineStr">
@@ -11157,11 +11157,11 @@
         </is>
       </c>
       <c r="F142" s="21" t="n">
-        <v>294256</v>
+        <v>11120</v>
       </c>
       <c r="G142" s="22" t="inlineStr">
         <is>
-          <t>287.4 KB</t>
+          <t>10.9 KB</t>
         </is>
       </c>
       <c r="H142" s="19" t="inlineStr">
@@ -11171,22 +11171,22 @@
       </c>
       <c r="I142" s="20" t="inlineStr">
         <is>
-          <t>Town of Hingham Select Board / Advisory Committee</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J142" s="20" t="inlineStr">
         <is>
-          <t>M.G.L. c. 39, § 10 (Town Meeting Warrant)</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K142" s="23" t="inlineStr">
         <is>
-          <t>Official Town Meeting Warrant detailing capital budget requests, debt exclusion articles, and municipal bylaws.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L142" s="19" t="inlineStr">
         <is>
-          <t>Official Town Warrant (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M142" s="19" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="N142" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2016_Article_24_100_Beal_Street_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_2006_Beal_St_Amended_Deed_Vote_v1.md</t>
         </is>
       </c>
     </row>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="D143" s="16" t="inlineStr">
         <is>
-          <t>Hingham_Town_Meeting_Warrant_2024_v1.md</t>
+          <t>Hingham_Town_Meeting_Warrant_2006_Article_38_School_Tract_II_v1.md</t>
         </is>
       </c>
       <c r="E143" s="15" t="inlineStr">
@@ -11227,11 +11227,11 @@
         </is>
       </c>
       <c r="F143" s="17" t="n">
-        <v>352751</v>
+        <v>192413</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>344.5 KB</t>
+          <t>187.9 KB</t>
         </is>
       </c>
       <c r="H143" s="15" t="inlineStr">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="N143" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2024_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2006_Article_38_School_Tract_II_v1.md</t>
         </is>
       </c>
     </row>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="D144" s="20" t="inlineStr">
         <is>
-          <t>Hingham_Town_Meeting_Warrant_2025_v1.md</t>
+          <t>Hingham_Town_Meeting_Warrant_2016_Article_24_100_Beal_Street_v1.md</t>
         </is>
       </c>
       <c r="E144" s="19" t="inlineStr">
@@ -11297,11 +11297,11 @@
         </is>
       </c>
       <c r="F144" s="21" t="n">
-        <v>291343</v>
+        <v>294256</v>
       </c>
       <c r="G144" s="22" t="inlineStr">
         <is>
-          <t>284.5 KB</t>
+          <t>287.4 KB</t>
         </is>
       </c>
       <c r="H144" s="19" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="N144" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2025_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2016_Article_24_100_Beal_Street_v1.md</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="D145" s="16" t="inlineStr">
         <is>
-          <t>Hingham_Town_Meeting_Warrant_2026_v1.md</t>
+          <t>Hingham_Town_Meeting_Warrant_2024_v1.md</t>
         </is>
       </c>
       <c r="E145" s="15" t="inlineStr">
@@ -11367,11 +11367,11 @@
         </is>
       </c>
       <c r="F145" s="17" t="n">
-        <v>281884</v>
+        <v>352751</v>
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>275.3 KB</t>
+          <t>344.5 KB</t>
         </is>
       </c>
       <c r="H145" s="15" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="N145" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2026_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2024_v1.md</t>
         </is>
       </c>
     </row>
@@ -11428,7 +11428,7 @@
       </c>
       <c r="D146" s="20" t="inlineStr">
         <is>
-          <t>SRP2020-South-Shore-Site-Readiness_v1.md</t>
+          <t>Hingham_Town_Meeting_Warrant_2025_v1.md</t>
         </is>
       </c>
       <c r="E146" s="19" t="inlineStr">
@@ -11437,11 +11437,11 @@
         </is>
       </c>
       <c r="F146" s="21" t="n">
-        <v>276120</v>
+        <v>291343</v>
       </c>
       <c r="G146" s="22" t="inlineStr">
         <is>
-          <t>269.6 KB</t>
+          <t>284.5 KB</t>
         </is>
       </c>
       <c r="H146" s="19" t="inlineStr">
@@ -11451,22 +11451,22 @@
       </c>
       <c r="I146" s="20" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>Town of Hingham Select Board / Advisory Committee</t>
         </is>
       </c>
       <c r="J146" s="20" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>M.G.L. c. 39, § 10 (Town Meeting Warrant)</t>
         </is>
       </c>
       <c r="K146" s="23" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Official Town Meeting Warrant detailing capital budget requests, debt exclusion articles, and municipal bylaws.</t>
         </is>
       </c>
       <c r="L146" s="19" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Official Town Warrant (Verified)</t>
         </is>
       </c>
       <c r="M146" s="19" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="N146" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/SRP2020-South-Shore-Site-Readiness_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2025_v1.md</t>
         </is>
       </c>
     </row>
@@ -11498,7 +11498,7 @@
       </c>
       <c r="D147" s="16" t="inlineStr">
         <is>
-          <t>Select_Board_Executive_Session_Minutes_2019-02-26_100_Beal_v1.md</t>
+          <t>Hingham_Town_Meeting_Warrant_2026_v1.md</t>
         </is>
       </c>
       <c r="E147" s="15" t="inlineStr">
@@ -11507,11 +11507,11 @@
         </is>
       </c>
       <c r="F147" s="17" t="n">
-        <v>10290</v>
+        <v>281884</v>
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>10.0 KB</t>
+          <t>275.3 KB</t>
         </is>
       </c>
       <c r="H147" s="15" t="inlineStr">
@@ -11521,22 +11521,22 @@
       </c>
       <c r="I147" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>Town of Hingham Select Board / Advisory Committee</t>
         </is>
       </c>
       <c r="J147" s="16" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>M.G.L. c. 39, § 10 (Town Meeting Warrant)</t>
         </is>
       </c>
       <c r="K147" s="18" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Official Town Meeting Warrant detailing capital budget requests, debt exclusion articles, and municipal bylaws.</t>
         </is>
       </c>
       <c r="L147" s="15" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Official Town Warrant (Verified)</t>
         </is>
       </c>
       <c r="M147" s="15" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="N147" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Select_Board_Executive_Session_Minutes_2019-02-26_100_Beal_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2026_v1.md</t>
         </is>
       </c>
     </row>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="D148" s="20" t="inlineStr">
         <is>
-          <t>Select_Board_Minutes_2017-09-20_100_Beal_v1.md</t>
+          <t>SRP2020-South-Shore-Site-Readiness_v1.md</t>
         </is>
       </c>
       <c r="E148" s="19" t="inlineStr">
@@ -11577,11 +11577,11 @@
         </is>
       </c>
       <c r="F148" s="21" t="n">
-        <v>7589</v>
+        <v>276120</v>
       </c>
       <c r="G148" s="22" t="inlineStr">
         <is>
-          <t>7.4 KB</t>
+          <t>269.6 KB</t>
         </is>
       </c>
       <c r="H148" s="19" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="N148" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Select_Board_Minutes_2017-09-20_100_Beal_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/SRP2020-South-Shore-Site-Readiness_v1.md</t>
         </is>
       </c>
     </row>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="D149" s="16" t="inlineStr">
         <is>
-          <t>Select_Board_Minutes_2018-02-08_100_Beal_v1.md</t>
+          <t>Select_Board_Executive_Session_Minutes_2019-02-26_100_Beal_v1.md</t>
         </is>
       </c>
       <c r="E149" s="15" t="inlineStr">
@@ -11647,11 +11647,11 @@
         </is>
       </c>
       <c r="F149" s="17" t="n">
-        <v>1511</v>
+        <v>10290</v>
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>1.5 KB</t>
+          <t>10.0 KB</t>
         </is>
       </c>
       <c r="H149" s="15" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="N149" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Select_Board_Minutes_2018-02-08_100_Beal_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Select_Board_Executive_Session_Minutes_2019-02-26_100_Beal_v1.md</t>
         </is>
       </c>
     </row>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>architectural_plans_summary_v1.md</t>
+          <t>Select_Board_Minutes_2017-09-20_100_Beal_v1.md</t>
         </is>
       </c>
       <c r="E150" s="19" t="inlineStr">
@@ -11717,11 +11717,11 @@
         </is>
       </c>
       <c r="F150" s="21" t="n">
-        <v>9439</v>
+        <v>7589</v>
       </c>
       <c r="G150" s="22" t="inlineStr">
         <is>
-          <t>9.2 KB</t>
+          <t>7.4 KB</t>
         </is>
       </c>
       <c r="H150" s="19" t="inlineStr">
@@ -11751,12 +11751,12 @@
       </c>
       <c r="M150" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 08:36</t>
+          <t>2026-09-14 10:23</t>
         </is>
       </c>
       <c r="N150" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/architectural_plans_summary_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Select_Board_Minutes_2017-09-20_100_Beal_v1.md</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="D151" s="16" t="inlineStr">
         <is>
-          <t>architectural_plans_summary_v2.md</t>
+          <t>Select_Board_Minutes_2018-02-08_100_Beal_v1.md</t>
         </is>
       </c>
       <c r="E151" s="15" t="inlineStr">
@@ -11787,16 +11787,16 @@
         </is>
       </c>
       <c r="F151" s="17" t="n">
-        <v>9321</v>
+        <v>1511</v>
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>9.1 KB</t>
+          <t>1.5 KB</t>
         </is>
       </c>
       <c r="H151" s="15" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I151" s="16" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="M151" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 16:08</t>
+          <t>2026-09-14 10:23</t>
         </is>
       </c>
       <c r="N151" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/architectural_plans_summary_v2.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Select_Board_Minutes_2018-02-08_100_Beal_v1.md</t>
         </is>
       </c>
     </row>
@@ -11848,7 +11848,7 @@
       </c>
       <c r="D152" s="20" t="inlineStr">
         <is>
-          <t>bare_cove_tuckers_swamp_commentary_v1.md</t>
+          <t>architectural_plans_summary_v1.md</t>
         </is>
       </c>
       <c r="E152" s="19" t="inlineStr">
@@ -11857,11 +11857,11 @@
         </is>
       </c>
       <c r="F152" s="21" t="n">
-        <v>11075</v>
+        <v>9439</v>
       </c>
       <c r="G152" s="22" t="inlineStr">
         <is>
-          <t>10.8 KB</t>
+          <t>9.2 KB</t>
         </is>
       </c>
       <c r="H152" s="19" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="M152" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 09:16</t>
+          <t>2026-09-14 08:36</t>
         </is>
       </c>
       <c r="N152" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/bare_cove_tuckers_swamp_commentary_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/architectural_plans_summary_v1.md</t>
         </is>
       </c>
     </row>
@@ -11918,7 +11918,7 @@
       </c>
       <c r="D153" s="16" t="inlineStr">
         <is>
-          <t>meeting_minutes_and_timeline_v1.md</t>
+          <t>architectural_plans_summary_v2.md</t>
         </is>
       </c>
       <c r="E153" s="15" t="inlineStr">
@@ -11927,16 +11927,16 @@
         </is>
       </c>
       <c r="F153" s="17" t="n">
-        <v>5578</v>
+        <v>9321</v>
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>5.4 KB</t>
+          <t>9.1 KB</t>
         </is>
       </c>
       <c r="H153" s="15" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="I153" s="16" t="inlineStr">
@@ -11961,12 +11961,12 @@
       </c>
       <c r="M153" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14 08:39</t>
+          <t>2026-09-16 16:08</t>
         </is>
       </c>
       <c r="N153" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/meeting_minutes_and_timeline_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/architectural_plans_summary_v2.md</t>
         </is>
       </c>
     </row>
@@ -11988,7 +11988,7 @@
       </c>
       <c r="D154" s="20" t="inlineStr">
         <is>
-          <t>meeting_minutes_and_timeline_v2.md</t>
+          <t>bare_cove_tuckers_swamp_commentary_v1.md</t>
         </is>
       </c>
       <c r="E154" s="19" t="inlineStr">
@@ -11997,16 +11997,16 @@
         </is>
       </c>
       <c r="F154" s="21" t="n">
-        <v>15405</v>
+        <v>11075</v>
       </c>
       <c r="G154" s="22" t="inlineStr">
         <is>
-          <t>15.0 KB</t>
+          <t>10.8 KB</t>
         </is>
       </c>
       <c r="H154" s="19" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I154" s="20" t="inlineStr">
@@ -12031,12 +12031,12 @@
       </c>
       <c r="M154" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 09:25</t>
+          <t>2026-09-14 09:16</t>
         </is>
       </c>
       <c r="N154" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/meeting_minutes_and_timeline_v2.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/bare_cove_tuckers_swamp_commentary_v1.md</t>
         </is>
       </c>
     </row>
@@ -12058,7 +12058,7 @@
       </c>
       <c r="D155" s="16" t="inlineStr">
         <is>
-          <t>state_housing_and_40B_filings_v1.md</t>
+          <t>meeting_minutes_and_timeline_v1.md</t>
         </is>
       </c>
       <c r="E155" s="15" t="inlineStr">
@@ -12067,11 +12067,11 @@
         </is>
       </c>
       <c r="F155" s="17" t="n">
-        <v>7856</v>
+        <v>5578</v>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>7.7 KB</t>
+          <t>5.4 KB</t>
         </is>
       </c>
       <c r="H155" s="15" t="inlineStr">
@@ -12101,12 +12101,12 @@
       </c>
       <c r="M155" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14 09:16</t>
+          <t>2026-09-14 08:39</t>
         </is>
       </c>
       <c r="N155" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/state_housing_and_40B_filings_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/meeting_minutes_and_timeline_v1.md</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="D156" s="20" t="inlineStr">
         <is>
-          <t>town_documents_and_legal_records_v1.md</t>
+          <t>meeting_minutes_and_timeline_v2.md</t>
         </is>
       </c>
       <c r="E156" s="19" t="inlineStr">
@@ -12137,16 +12137,16 @@
         </is>
       </c>
       <c r="F156" s="21" t="n">
-        <v>21860</v>
+        <v>15405</v>
       </c>
       <c r="G156" s="22" t="inlineStr">
         <is>
-          <t>21.3 KB</t>
+          <t>15.0 KB</t>
         </is>
       </c>
       <c r="H156" s="19" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="I156" s="20" t="inlineStr">
@@ -12171,12 +12171,12 @@
       </c>
       <c r="M156" s="19" t="inlineStr">
         <is>
-          <t>2026-09-17 06:59</t>
+          <t>2026-09-14 09:25</t>
         </is>
       </c>
       <c r="N156" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/town_documents_and_legal_records_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/meeting_minutes_and_timeline_v2.md</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12198,7 @@
       </c>
       <c r="D157" s="16" t="inlineStr">
         <is>
-          <t>town_documents_and_legal_records_v2.md</t>
+          <t>state_housing_and_40B_filings_v1.md</t>
         </is>
       </c>
       <c r="E157" s="15" t="inlineStr">
@@ -12207,16 +12207,16 @@
         </is>
       </c>
       <c r="F157" s="17" t="n">
-        <v>24370</v>
+        <v>7856</v>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>23.8 KB</t>
+          <t>7.7 KB</t>
         </is>
       </c>
       <c r="H157" s="15" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I157" s="16" t="inlineStr">
@@ -12241,12 +12241,12 @@
       </c>
       <c r="M157" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17</t>
+          <t>2026-09-14 09:16</t>
         </is>
       </c>
       <c r="N157" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/town_documents_and_legal_records_v2.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/state_housing_and_40B_filings_v1.md</t>
         </is>
       </c>
     </row>
@@ -12268,7 +12268,7 @@
       </c>
       <c r="D158" s="20" t="inlineStr">
         <is>
-          <t>town_documents_and_legal_records_v3.md</t>
+          <t>town_documents_and_legal_records_v1.md</t>
         </is>
       </c>
       <c r="E158" s="19" t="inlineStr">
@@ -12277,16 +12277,16 @@
         </is>
       </c>
       <c r="F158" s="21" t="n">
-        <v>24396</v>
+        <v>21860</v>
       </c>
       <c r="G158" s="22" t="inlineStr">
         <is>
-          <t>23.8 KB</t>
+          <t>21.3 KB</t>
         </is>
       </c>
       <c r="H158" s="19" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I158" s="20" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="M158" s="19" t="inlineStr">
         <is>
-          <t>2026-09-16 16:47</t>
+          <t>2026-09-17 06:59</t>
         </is>
       </c>
       <c r="N158" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/town_documents_and_legal_records_v3.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/town_documents_and_legal_records_v1.md</t>
         </is>
       </c>
     </row>
@@ -12333,60 +12333,60 @@
       </c>
       <c r="C159" s="16" t="inlineStr">
         <is>
-          <t>Speech-to-Text Meeting Transcripts</t>
+          <t>Companion Markdown Transcriptions</t>
         </is>
       </c>
       <c r="D159" s="16" t="inlineStr">
         <is>
-          <t>2018-01-30_Selectmen_KfiJSICX-mo_whisper_transcript.txt</t>
+          <t>town_documents_and_legal_records_v2.md</t>
         </is>
       </c>
       <c r="E159" s="15" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F159" s="17" t="n">
-        <v>130469</v>
+        <v>24370</v>
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>127.4 KB</t>
+          <t>23.8 KB</t>
         </is>
       </c>
       <c r="H159" s="15" t="inlineStr">
         <is>
-          <t>Original Public Record</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="I159" s="16" t="inlineStr">
         <is>
-          <t>OpenAI Whisper (Apple Silicon Metal GPU)</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J159" s="16" t="inlineStr">
         <is>
-          <t>Open Meeting Deliberations</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K159" s="18" t="inlineStr">
         <is>
-          <t>Full verbatim speech-to-text transcript generated directly from municipal broadcast audio.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L159" s="15" t="inlineStr">
         <is>
-          <t>Automated Verified Transcript</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M159" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15 17:35</t>
+          <t>2026-09-14 09:17</t>
         </is>
       </c>
       <c r="N159" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/meeting_transcripts/2018-01-30_Selectmen_KfiJSICX-mo_whisper_transcript.txt</t>
+          <t>agent_created_deliverables/companion_transcriptions/town_documents_and_legal_records_v2.md</t>
         </is>
       </c>
     </row>
@@ -12403,60 +12403,60 @@
       </c>
       <c r="C160" s="20" t="inlineStr">
         <is>
-          <t>Speech-to-Text Meeting Transcripts</t>
+          <t>Companion Markdown Transcriptions</t>
         </is>
       </c>
       <c r="D160" s="20" t="inlineStr">
         <is>
-          <t>2018-02-13_Selectmen_t4P0ZzzO0oY_whisper_transcript.txt</t>
+          <t>town_documents_and_legal_records_v3.md</t>
         </is>
       </c>
       <c r="E160" s="19" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F160" s="21" t="n">
-        <v>81155</v>
+        <v>24396</v>
       </c>
       <c r="G160" s="22" t="inlineStr">
         <is>
-          <t>79.3 KB</t>
+          <t>23.8 KB</t>
         </is>
       </c>
       <c r="H160" s="19" t="inlineStr">
         <is>
-          <t>Original Public Record</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="I160" s="20" t="inlineStr">
         <is>
-          <t>OpenAI Whisper (Apple Silicon Metal GPU)</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J160" s="20" t="inlineStr">
         <is>
-          <t>Open Meeting Deliberations</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K160" s="23" t="inlineStr">
         <is>
-          <t>Full verbatim speech-to-text transcript generated directly from municipal broadcast audio.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L160" s="19" t="inlineStr">
         <is>
-          <t>Automated Verified Transcript</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M160" s="19" t="inlineStr">
         <is>
-          <t>2026-09-15 17:35</t>
+          <t>2026-09-16 16:47</t>
         </is>
       </c>
       <c r="N160" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/meeting_transcripts/2018-02-13_Selectmen_t4P0ZzzO0oY_whisper_transcript.txt</t>
+          <t>agent_created_deliverables/companion_transcriptions/town_documents_and_legal_records_v3.md</t>
         </is>
       </c>
     </row>
@@ -12478,7 +12478,7 @@
       </c>
       <c r="D161" s="16" t="inlineStr">
         <is>
-          <t>2019-02-26_Selectmen_iSOkQlHX-5s_GeminiPro_transcript.txt</t>
+          <t>2018-01-30_Selectmen_KfiJSICX-mo_whisper_transcript.txt</t>
         </is>
       </c>
       <c r="E161" s="15" t="inlineStr">
@@ -12487,11 +12487,11 @@
         </is>
       </c>
       <c r="F161" s="17" t="n">
-        <v>75792</v>
+        <v>130469</v>
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>74.0 KB</t>
+          <t>127.4 KB</t>
         </is>
       </c>
       <c r="H161" s="15" t="inlineStr">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="I161" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>OpenAI Whisper (Apple Silicon Metal GPU)</t>
         </is>
       </c>
       <c r="J161" s="16" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>Open Meeting Deliberations</t>
         </is>
       </c>
       <c r="K161" s="18" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Full verbatim speech-to-text transcript generated directly from municipal broadcast audio.</t>
         </is>
       </c>
       <c r="L161" s="15" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Automated Verified Transcript</t>
         </is>
       </c>
       <c r="M161" s="15" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="N161" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/meeting_transcripts/2019-02-26_Selectmen_iSOkQlHX-5s_GeminiPro_transcript.txt</t>
+          <t>agent_created_deliverables/meeting_transcripts/2018-01-30_Selectmen_KfiJSICX-mo_whisper_transcript.txt</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>2019-10-29_Selectmen_COFl6DmOWAo_whisper_transcript.txt</t>
+          <t>2018-02-13_Selectmen_t4P0ZzzO0oY_whisper_transcript.txt</t>
         </is>
       </c>
       <c r="E162" s="19" t="inlineStr">
@@ -12557,11 +12557,11 @@
         </is>
       </c>
       <c r="F162" s="21" t="n">
-        <v>133848</v>
+        <v>81155</v>
       </c>
       <c r="G162" s="22" t="inlineStr">
         <is>
-          <t>130.7 KB</t>
+          <t>79.3 KB</t>
         </is>
       </c>
       <c r="H162" s="19" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="N162" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/meeting_transcripts/2019-10-29_Selectmen_COFl6DmOWAo_whisper_transcript.txt</t>
+          <t>agent_created_deliverables/meeting_transcripts/2018-02-13_Selectmen_t4P0ZzzO0oY_whisper_transcript.txt</t>
         </is>
       </c>
     </row>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="D163" s="16" t="inlineStr">
         <is>
-          <t>2026-08-25_SelectBoard_LLJSH5V2ngg_whisper_transcript.txt</t>
+          <t>2019-02-26_Selectmen_iSOkQlHX-5s_GeminiPro_transcript.txt</t>
         </is>
       </c>
       <c r="E163" s="15" t="inlineStr">
@@ -12627,11 +12627,11 @@
         </is>
       </c>
       <c r="F163" s="17" t="n">
-        <v>112574</v>
+        <v>75792</v>
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>109.9 KB</t>
+          <t>74.0 KB</t>
         </is>
       </c>
       <c r="H163" s="15" t="inlineStr">
@@ -12641,22 +12641,22 @@
       </c>
       <c r="I163" s="16" t="inlineStr">
         <is>
-          <t>OpenAI Whisper (Apple Silicon Metal GPU)</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J163" s="16" t="inlineStr">
         <is>
-          <t>Open Meeting Deliberations</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K163" s="18" t="inlineStr">
         <is>
-          <t>Full verbatim speech-to-text transcript generated directly from municipal broadcast audio.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L163" s="15" t="inlineStr">
         <is>
-          <t>Automated Verified Transcript</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M163" s="15" t="inlineStr">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="N163" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/meeting_transcripts/2026-08-25_SelectBoard_LLJSH5V2ngg_whisper_transcript.txt</t>
+          <t>agent_created_deliverables/meeting_transcripts/2019-02-26_Selectmen_iSOkQlHX-5s_GeminiPro_transcript.txt</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>README.txt</t>
+          <t>2019-10-29_Selectmen_COFl6DmOWAo_whisper_transcript.txt</t>
         </is>
       </c>
       <c r="E164" s="19" t="inlineStr">
@@ -12697,11 +12697,11 @@
         </is>
       </c>
       <c r="F164" s="21" t="n">
-        <v>1730</v>
+        <v>133848</v>
       </c>
       <c r="G164" s="22" t="inlineStr">
         <is>
-          <t>1.7 KB</t>
+          <t>130.7 KB</t>
         </is>
       </c>
       <c r="H164" s="19" t="inlineStr">
@@ -12711,22 +12711,22 @@
       </c>
       <c r="I164" s="20" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>OpenAI Whisper (Apple Silicon Metal GPU)</t>
         </is>
       </c>
       <c r="J164" s="20" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>Open Meeting Deliberations</t>
         </is>
       </c>
       <c r="K164" s="23" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Full verbatim speech-to-text transcript generated directly from municipal broadcast audio.</t>
         </is>
       </c>
       <c r="L164" s="19" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Automated Verified Transcript</t>
         </is>
       </c>
       <c r="M164" s="19" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="N164" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/meeting_transcripts/README.txt</t>
+          <t>agent_created_deliverables/meeting_transcripts/2019-10-29_Selectmen_COFl6DmOWAo_whisper_transcript.txt</t>
         </is>
       </c>
     </row>
@@ -12758,55 +12758,55 @@
       </c>
       <c r="D165" s="16" t="inlineStr">
         <is>
-          <t>video_recordings_index_v1.md</t>
+          <t>2026-08-25_SelectBoard_LLJSH5V2ngg_whisper_transcript.txt</t>
         </is>
       </c>
       <c r="E165" s="15" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="F165" s="17" t="n">
-        <v>16881</v>
+        <v>112574</v>
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>16.5 KB</t>
+          <t>109.9 KB</t>
         </is>
       </c>
       <c r="H165" s="15" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>Original Public Record</t>
         </is>
       </c>
       <c r="I165" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>OpenAI Whisper (Apple Silicon Metal GPU)</t>
         </is>
       </c>
       <c r="J165" s="16" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>Open Meeting Deliberations</t>
         </is>
       </c>
       <c r="K165" s="18" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Full verbatim speech-to-text transcript generated directly from municipal broadcast audio.</t>
         </is>
       </c>
       <c r="L165" s="15" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Automated Verified Transcript</t>
         </is>
       </c>
       <c r="M165" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17</t>
+          <t>2026-09-15 17:35</t>
         </is>
       </c>
       <c r="N165" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/meeting_transcripts/video_recordings_index_v1.md</t>
+          <t>agent_created_deliverables/meeting_transcripts/2026-08-25_SelectBoard_LLJSH5V2ngg_whisper_transcript.txt</t>
         </is>
       </c>
     </row>
@@ -12823,60 +12823,60 @@
       </c>
       <c r="C166" s="20" t="inlineStr">
         <is>
-          <t>Quality Control Audits</t>
+          <t>Speech-to-Text Meeting Transcripts</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>qc_audit_legal_and_plans_v1.md</t>
+          <t>README.txt</t>
         </is>
       </c>
       <c r="E166" s="19" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="F166" s="21" t="n">
-        <v>31728</v>
+        <v>1730</v>
       </c>
       <c r="G166" s="22" t="inlineStr">
         <is>
-          <t>31.0 KB</t>
+          <t>1.7 KB</t>
         </is>
       </c>
       <c r="H166" s="19" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>Original Public Record</t>
         </is>
       </c>
       <c r="I166" s="20" t="inlineStr">
         <is>
-          <t>Meticulous Quality Control Auditor</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J166" s="20" t="inlineStr">
         <is>
-          <t>Records Integrity &amp; Geodetic Verification Standard</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K166" s="23" t="inlineStr">
         <is>
-          <t>Forensic quality control audit verifying document textual fidelity, wetland flag coordinates, and compendium completeness.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L166" s="19" t="inlineStr">
         <is>
-          <t>Audited &amp; Verified (100% Fidelity)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M166" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 11:39</t>
+          <t>2026-09-15 17:35</t>
         </is>
       </c>
       <c r="N166" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/quality_control_audits/qc_audit_legal_and_plans_v1.md</t>
+          <t>agent_created_deliverables/meeting_transcripts/README.txt</t>
         </is>
       </c>
     </row>
@@ -12893,12 +12893,12 @@
       </c>
       <c r="C167" s="16" t="inlineStr">
         <is>
-          <t>Quality Control Audits</t>
+          <t>Speech-to-Text Meeting Transcripts</t>
         </is>
       </c>
       <c r="D167" s="16" t="inlineStr">
         <is>
-          <t>qc_audit_media_and_compendium_integrity_v1.md</t>
+          <t>video_recordings_index_v1.md</t>
         </is>
       </c>
       <c r="E167" s="15" t="inlineStr">
@@ -12907,11 +12907,11 @@
         </is>
       </c>
       <c r="F167" s="17" t="n">
-        <v>29635</v>
+        <v>16881</v>
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>28.9 KB</t>
+          <t>16.5 KB</t>
         </is>
       </c>
       <c r="H167" s="15" t="inlineStr">
@@ -12921,32 +12921,32 @@
       </c>
       <c r="I167" s="16" t="inlineStr">
         <is>
-          <t>Meticulous Quality Control Auditor</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J167" s="16" t="inlineStr">
         <is>
-          <t>Records Integrity &amp; Geodetic Verification Standard</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K167" s="18" t="inlineStr">
         <is>
-          <t>Forensic quality control audit verifying document textual fidelity, wetland flag coordinates, and compendium completeness.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L167" s="15" t="inlineStr">
         <is>
-          <t>Audited &amp; Verified (100% Fidelity)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M167" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14 11:40</t>
+          <t>2026-09-14 09:17</t>
         </is>
       </c>
       <c r="N167" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/quality_control_audits/qc_audit_media_and_compendium_integrity_v1.md</t>
+          <t>agent_created_deliverables/meeting_transcripts/video_recordings_index_v1.md</t>
         </is>
       </c>
     </row>
@@ -12968,7 +12968,7 @@
       </c>
       <c r="D168" s="20" t="inlineStr">
         <is>
-          <t>qc_audit_meetings_and_videos_v1.md</t>
+          <t>qc_audit_legal_and_plans_v1.md</t>
         </is>
       </c>
       <c r="E168" s="19" t="inlineStr">
@@ -12977,11 +12977,11 @@
         </is>
       </c>
       <c r="F168" s="21" t="n">
-        <v>42842</v>
+        <v>31728</v>
       </c>
       <c r="G168" s="22" t="inlineStr">
         <is>
-          <t>41.8 KB</t>
+          <t>31.0 KB</t>
         </is>
       </c>
       <c r="H168" s="19" t="inlineStr">
@@ -13011,12 +13011,12 @@
       </c>
       <c r="M168" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 11:56</t>
+          <t>2026-09-14 11:39</t>
         </is>
       </c>
       <c r="N168" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/quality_control_audits/qc_audit_meetings_and_videos_v1.md</t>
+          <t>agent_created_deliverables/quality_control_audits/qc_audit_legal_and_plans_v1.md</t>
         </is>
       </c>
     </row>
@@ -13033,25 +13033,25 @@
       </c>
       <c r="C169" s="16" t="inlineStr">
         <is>
-          <t>Visual Infographics &amp; Timelines</t>
+          <t>Quality Control Audits</t>
         </is>
       </c>
       <c r="D169" s="16" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Timeline_Infographic_9x16_v1.jpg</t>
+          <t>qc_audit_media_and_compendium_integrity_v1.md</t>
         </is>
       </c>
       <c r="E169" s="15" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F169" s="17" t="n">
-        <v>656090</v>
+        <v>29635</v>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>640.7 KB</t>
+          <t>28.9 KB</t>
         </is>
       </c>
       <c r="H169" s="15" t="inlineStr">
@@ -13061,32 +13061,32 @@
       </c>
       <c r="I169" s="16" t="inlineStr">
         <is>
-          <t>AI Creative Design / Municipal Standards</t>
+          <t>Meticulous Quality Control Auditor</t>
         </is>
       </c>
       <c r="J169" s="16" t="inlineStr">
         <is>
-          <t>M.G.L. c. 121B, § 34; M.G.L. c. 30B, § 16</t>
+          <t>Records Integrity &amp; Geodetic Verification Standard</t>
         </is>
       </c>
       <c r="K169" s="18" t="inlineStr">
         <is>
-          <t>9:16 vertical infographic formatted in official Hingham Crimson (#891024) and Gold (#D97706) featuring exactly 3 bullets per milestone year and 99-year lease covenants.</t>
+          <t>Forensic quality control audit verifying document textual fidelity, wetland flag coordinates, and compendium completeness.</t>
         </is>
       </c>
       <c r="L169" s="15" t="inlineStr">
         <is>
-          <t>Visual Deliverable (Verified)</t>
+          <t>Audited &amp; Verified (100% Fidelity)</t>
         </is>
       </c>
       <c r="M169" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 09:58</t>
+          <t>2026-09-14 11:40</t>
         </is>
       </c>
       <c r="N169" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_9x16_v1.jpg</t>
+          <t>agent_created_deliverables/quality_control_audits/qc_audit_media_and_compendium_integrity_v1.md</t>
         </is>
       </c>
     </row>
@@ -13103,25 +13103,25 @@
       </c>
       <c r="C170" s="20" t="inlineStr">
         <is>
-          <t>Visual Infographics &amp; Timelines</t>
+          <t>Quality Control Audits</t>
         </is>
       </c>
       <c r="D170" s="20" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Timeline_Infographic_9x16_v1.pdf</t>
+          <t>qc_audit_meetings_and_videos_v1.md</t>
         </is>
       </c>
       <c r="E170" s="19" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F170" s="21" t="n">
-        <v>657143</v>
+        <v>42842</v>
       </c>
       <c r="G170" s="22" t="inlineStr">
         <is>
-          <t>641.7 KB</t>
+          <t>41.8 KB</t>
         </is>
       </c>
       <c r="H170" s="19" t="inlineStr">
@@ -13131,32 +13131,32 @@
       </c>
       <c r="I170" s="20" t="inlineStr">
         <is>
-          <t>AI Creative Design / Municipal Standards</t>
+          <t>Meticulous Quality Control Auditor</t>
         </is>
       </c>
       <c r="J170" s="20" t="inlineStr">
         <is>
-          <t>M.G.L. c. 121B, § 34; M.G.L. c. 30B, § 16</t>
+          <t>Records Integrity &amp; Geodetic Verification Standard</t>
         </is>
       </c>
       <c r="K170" s="23" t="inlineStr">
         <is>
-          <t>9:16 vertical infographic formatted in official Hingham Crimson (#891024) and Gold (#D97706) featuring exactly 3 bullets per milestone year and 99-year lease covenants.</t>
+          <t>Forensic quality control audit verifying document textual fidelity, wetland flag coordinates, and compendium completeness.</t>
         </is>
       </c>
       <c r="L170" s="19" t="inlineStr">
         <is>
-          <t>Visual Deliverable (Verified)</t>
+          <t>Audited &amp; Verified (100% Fidelity)</t>
         </is>
       </c>
       <c r="M170" s="19" t="inlineStr">
         <is>
-          <t>2026-09-16 09:58</t>
+          <t>2026-09-14 11:56</t>
         </is>
       </c>
       <c r="N170" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_9x16_v1.pdf</t>
+          <t>agent_created_deliverables/quality_control_audits/qc_audit_meetings_and_videos_v1.md</t>
         </is>
       </c>
     </row>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="D171" s="16" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v1.jpg</t>
+          <t>100_Beal_Street_Timeline_Infographic_9x16_v1.jpg</t>
         </is>
       </c>
       <c r="E171" s="15" t="inlineStr">
@@ -13187,11 +13187,11 @@
         </is>
       </c>
       <c r="F171" s="17" t="n">
-        <v>585609</v>
+        <v>656090</v>
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>571.9 KB</t>
+          <t>640.7 KB</t>
         </is>
       </c>
       <c r="H171" s="15" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="M171" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 09:59</t>
+          <t>2026-09-16 09:58</t>
         </is>
       </c>
       <c r="N171" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v1.jpg</t>
+          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_9x16_v1.jpg</t>
         </is>
       </c>
     </row>
@@ -13248,25 +13248,25 @@
       </c>
       <c r="D172" s="20" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.jpg</t>
+          <t>100_Beal_Street_Timeline_Infographic_9x16_v1.pdf</t>
         </is>
       </c>
       <c r="E172" s="19" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="F172" s="21" t="n">
-        <v>690206</v>
+        <v>657143</v>
       </c>
       <c r="G172" s="22" t="inlineStr">
         <is>
-          <t>674.0 KB</t>
+          <t>641.7 KB</t>
         </is>
       </c>
       <c r="H172" s="19" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I172" s="20" t="inlineStr">
@@ -13291,12 +13291,12 @@
       </c>
       <c r="M172" s="19" t="inlineStr">
         <is>
-          <t>2026-09-16 10:04</t>
+          <t>2026-09-16 09:58</t>
         </is>
       </c>
       <c r="N172" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.jpg</t>
+          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_9x16_v1.pdf</t>
         </is>
       </c>
     </row>
@@ -13318,25 +13318,25 @@
       </c>
       <c r="D173" s="16" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.pdf</t>
+          <t>100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v1.jpg</t>
         </is>
       </c>
       <c r="E173" s="15" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="F173" s="17" t="n">
-        <v>327716</v>
+        <v>585609</v>
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>320.0 KB</t>
+          <t>571.9 KB</t>
         </is>
       </c>
       <c r="H173" s="15" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I173" s="16" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="M173" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 10:04</t>
+          <t>2026-09-16 09:59</t>
         </is>
       </c>
       <c r="N173" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.pdf</t>
+          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v1.jpg</t>
         </is>
       </c>
     </row>
@@ -13388,60 +13388,200 @@
       </c>
       <c r="D174" s="20" t="inlineStr">
         <is>
+          <t>100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.jpg</t>
+        </is>
+      </c>
+      <c r="E174" s="19" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="F174" s="21" t="n">
+        <v>690206</v>
+      </c>
+      <c r="G174" s="22" t="inlineStr">
+        <is>
+          <t>674.0 KB</t>
+        </is>
+      </c>
+      <c r="H174" s="19" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="I174" s="20" t="inlineStr">
+        <is>
+          <t>AI Creative Design / Municipal Standards</t>
+        </is>
+      </c>
+      <c r="J174" s="20" t="inlineStr">
+        <is>
+          <t>M.G.L. c. 121B, § 34; M.G.L. c. 30B, § 16</t>
+        </is>
+      </c>
+      <c r="K174" s="23" t="inlineStr">
+        <is>
+          <t>9:16 vertical infographic formatted in official Hingham Crimson (#891024) and Gold (#D97706) featuring exactly 3 bullets per milestone year and 99-year lease covenants.</t>
+        </is>
+      </c>
+      <c r="L174" s="19" t="inlineStr">
+        <is>
+          <t>Visual Deliverable (Verified)</t>
+        </is>
+      </c>
+      <c r="M174" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:04</t>
+        </is>
+      </c>
+      <c r="N174" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="15" t="inlineStr">
+        <is>
+          <t>FL-171</t>
+        </is>
+      </c>
+      <c r="B175" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C175" s="16" t="inlineStr">
+        <is>
+          <t>Visual Infographics &amp; Timelines</t>
+        </is>
+      </c>
+      <c r="D175" s="16" t="inlineStr">
+        <is>
+          <t>100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.pdf</t>
+        </is>
+      </c>
+      <c r="E175" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F175" s="17" t="n">
+        <v>327716</v>
+      </c>
+      <c r="G175" s="12" t="inlineStr">
+        <is>
+          <t>320.0 KB</t>
+        </is>
+      </c>
+      <c r="H175" s="15" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="I175" s="16" t="inlineStr">
+        <is>
+          <t>AI Creative Design / Municipal Standards</t>
+        </is>
+      </c>
+      <c r="J175" s="16" t="inlineStr">
+        <is>
+          <t>M.G.L. c. 121B, § 34; M.G.L. c. 30B, § 16</t>
+        </is>
+      </c>
+      <c r="K175" s="18" t="inlineStr">
+        <is>
+          <t>9:16 vertical infographic formatted in official Hingham Crimson (#891024) and Gold (#D97706) featuring exactly 3 bullets per milestone year and 99-year lease covenants.</t>
+        </is>
+      </c>
+      <c r="L175" s="15" t="inlineStr">
+        <is>
+          <t>Visual Deliverable (Verified)</t>
+        </is>
+      </c>
+      <c r="M175" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:04</t>
+        </is>
+      </c>
+      <c r="N175" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="19" t="inlineStr">
+        <is>
+          <t>FL-172</t>
+        </is>
+      </c>
+      <c r="B176" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C176" s="20" t="inlineStr">
+        <is>
+          <t>Visual Infographics &amp; Timelines</t>
+        </is>
+      </c>
+      <c r="D176" s="20" t="inlineStr">
+        <is>
           <t>100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.png</t>
         </is>
       </c>
-      <c r="E174" s="19" t="inlineStr">
+      <c r="E176" s="19" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
       </c>
-      <c r="F174" s="21" t="n">
+      <c r="F176" s="21" t="n">
         <v>799187</v>
       </c>
-      <c r="G174" s="22" t="inlineStr">
+      <c r="G176" s="22" t="inlineStr">
         <is>
           <t>780.5 KB</t>
         </is>
       </c>
-      <c r="H174" s="19" t="inlineStr">
+      <c r="H176" s="19" t="inlineStr">
         <is>
           <t>v2</t>
         </is>
       </c>
-      <c r="I174" s="20" t="inlineStr">
+      <c r="I176" s="20" t="inlineStr">
         <is>
           <t>AI Creative Design / Municipal Standards</t>
         </is>
       </c>
-      <c r="J174" s="20" t="inlineStr">
+      <c r="J176" s="20" t="inlineStr">
         <is>
           <t>M.G.L. c. 121B, § 34; M.G.L. c. 30B, § 16</t>
         </is>
       </c>
-      <c r="K174" s="23" t="inlineStr">
+      <c r="K176" s="23" t="inlineStr">
         <is>
           <t>9:16 vertical infographic formatted in official Hingham Crimson (#891024) and Gold (#D97706) featuring exactly 3 bullets per milestone year and 99-year lease covenants.</t>
         </is>
       </c>
-      <c r="L174" s="19" t="inlineStr">
+      <c r="L176" s="19" t="inlineStr">
         <is>
           <t>Visual Deliverable (Verified)</t>
         </is>
       </c>
-      <c r="M174" s="19" t="inlineStr">
+      <c r="M176" s="19" t="inlineStr">
         <is>
           <t>2026-09-16 10:04</t>
         </is>
       </c>
-      <c r="N174" s="20" t="inlineStr">
+      <c r="N176" s="20" t="inlineStr">
         <is>
           <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.png</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N174"/>
+  <autoFilter ref="A4:N176"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13481,7 +13621,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: September 17, 2026 • Total Records: 71 • Zero Web Scrapes</t>
+          <t>Generated: September 18, 2026 • Total Records: 71 • Zero Web Scrapes</t>
         </is>
       </c>
     </row>
@@ -18539,7 +18679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18568,7 +18708,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: September 17, 2026 • Total Records: 84 • Zero Web Scrapes</t>
+          <t>Generated: September 18, 2026 • Total Records: 86 • Zero Web Scrapes</t>
         </is>
       </c>
     </row>
@@ -19222,7 +19362,7 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.md</t>
+          <t>100_Beal_Street_The_True_Story_and_Evidence_v1.md</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -19231,11 +19371,11 @@
         </is>
       </c>
       <c r="F13" s="17" t="n">
-        <v>19343</v>
+        <v>12031</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>18.9 KB</t>
+          <t>11.7 KB</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
@@ -19245,32 +19385,32 @@
       </c>
       <c r="I13" s="16" t="inlineStr">
         <is>
-          <t>Hingham Board of Selectmen / HHA / Mass. DHCD</t>
+          <t>Primary Municipal Records &amp; Educational Architecture</t>
         </is>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>M.G.L. c. 184A, § 3; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
+          <t>M.G.L. c. 121B; M.G.L. c. 184A; M.G.L. c. 44, § 7; Plymouth Registry Instruments</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
         <is>
-          <t>Primary source legal chronology detailing the 1989 deed, 2001 MOU, Feb 26, 2019 Select Board litigation vote (3-0), state DHCD letters, and Sept 7, 2021 HHA rescission vote.</t>
+          <t>Dedicated 2-page educational guide and evidence ledger for family and community members. Page 1 provides a 1-page unspun narrative essay; Page 2 provides the companion Works Cited mapping every point to primary documents with repository file names.</t>
         </is>
       </c>
       <c r="L13" s="15" t="inlineStr">
         <is>
-          <t>Prior Version (Superseded by v2)</t>
+          <t>Community Educational Guide &amp; Evidence Ledger (Verified)</t>
         </is>
       </c>
       <c r="M13" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17 06:59</t>
+          <t>2026-09-18 10:27</t>
         </is>
       </c>
       <c r="N13" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.md</t>
+          <t>agent_created_deliverables/executive_reports/100_Beal_Street_The_True_Story_and_Evidence_v1.md</t>
         </is>
       </c>
     </row>
@@ -19292,7 +19432,7 @@
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.pdf</t>
+          <t>100_Beal_Street_The_True_Story_and_Evidence_v1.pdf</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
@@ -19301,11 +19441,11 @@
         </is>
       </c>
       <c r="F14" s="21" t="n">
-        <v>108868</v>
+        <v>74343</v>
       </c>
       <c r="G14" s="22" t="inlineStr">
         <is>
-          <t>106.3 KB</t>
+          <t>72.6 KB</t>
         </is>
       </c>
       <c r="H14" s="19" t="inlineStr">
@@ -19315,32 +19455,32 @@
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
-          <t>Hingham Board of Selectmen / HHA / Mass. DHCD</t>
+          <t>Primary Municipal Records &amp; Educational Architecture</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
         <is>
-          <t>M.G.L. c. 184A, § 3; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
+          <t>M.G.L. c. 121B; M.G.L. c. 184A; M.G.L. c. 44, § 7; Plymouth Registry Instruments</t>
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr">
         <is>
-          <t>Primary source legal chronology detailing the 1989 deed, 2001 MOU, Feb 26, 2019 Select Board litigation vote (3-0), state DHCD letters, and Sept 7, 2021 HHA rescission vote.</t>
+          <t>Dedicated 2-page educational guide and evidence ledger for family and community members. Page 1 provides a 1-page unspun narrative essay; Page 2 provides the companion Works Cited mapping every point to primary documents with repository file names.</t>
         </is>
       </c>
       <c r="L14" s="19" t="inlineStr">
         <is>
-          <t>Prior Version (Superseded by v2)</t>
+          <t>Community Educational Guide &amp; Evidence Ledger (Verified)</t>
         </is>
       </c>
       <c r="M14" s="19" t="inlineStr">
         <is>
-          <t>2026-09-17 06:59</t>
+          <t>2026-09-18 10:27</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.pdf</t>
+          <t>agent_created_deliverables/executive_reports/100_Beal_Street_The_True_Story_and_Evidence_v1.pdf</t>
         </is>
       </c>
     </row>
@@ -19362,7 +19502,7 @@
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.md</t>
+          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.md</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -19371,46 +19511,46 @@
         </is>
       </c>
       <c r="F15" s="17" t="n">
-        <v>31676</v>
+        <v>19343</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>30.9 KB</t>
+          <t>18.9 KB</t>
         </is>
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
-          <t>Primary Municipal Records / Mass. Registry of Deeds</t>
+          <t>Hingham Board of Selectmen / HHA / Mass. DHCD</t>
         </is>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>Historical M.G.L. c. 184A, § 3; M.G.L. c. 184, § 23; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
+          <t>M.G.L. c. 184A, § 3; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
         </is>
       </c>
       <c r="K15" s="18" t="inlineStr">
         <is>
-          <t>Preliminary primary-source research chronology and record index; strictly neutral factual reporting; segregates verified facts, factual inferences, and open legal questions; includes missing documents inventory and disclaimer. Not a title opinion.</t>
+          <t>Primary source legal chronology detailing the 1989 deed, 2001 MOU, Feb 26, 2019 Select Board litigation vote (3-0), state DHCD letters, and Sept 7, 2021 HHA rescission vote.</t>
         </is>
       </c>
       <c r="L15" s="15" t="inlineStr">
         <is>
-          <t>Neutral Primary Source Research Index &amp; Inventory (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M15" s="15" t="inlineStr">
         <is>
-          <t>2026-09-17 09:44</t>
+          <t>2026-09-17 06:59</t>
         </is>
       </c>
       <c r="N15" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.md</t>
+          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.md</t>
         </is>
       </c>
     </row>
@@ -19432,7 +19572,7 @@
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.pdf</t>
+          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.pdf</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -19441,46 +19581,46 @@
         </is>
       </c>
       <c r="F16" s="21" t="n">
-        <v>119536</v>
+        <v>108868</v>
       </c>
       <c r="G16" s="22" t="inlineStr">
         <is>
-          <t>116.7 KB</t>
+          <t>106.3 KB</t>
         </is>
       </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
-          <t>Primary Municipal Records / Mass. Registry of Deeds</t>
+          <t>Hingham Board of Selectmen / HHA / Mass. DHCD</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
         <is>
-          <t>Historical M.G.L. c. 184A, § 3; M.G.L. c. 184, § 23; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
+          <t>M.G.L. c. 184A, § 3; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr">
         <is>
-          <t>Preliminary primary-source research chronology and record index; strictly neutral factual reporting; segregates verified facts, factual inferences, and open legal questions; includes missing documents inventory and disclaimer. Not a title opinion.</t>
+          <t>Primary source legal chronology detailing the 1989 deed, 2001 MOU, Feb 26, 2019 Select Board litigation vote (3-0), state DHCD letters, and Sept 7, 2021 HHA rescission vote.</t>
         </is>
       </c>
       <c r="L16" s="19" t="inlineStr">
         <is>
-          <t>Neutral Primary Source Research Index &amp; Inventory (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M16" s="19" t="inlineStr">
         <is>
-          <t>2026-09-17 09:44</t>
+          <t>2026-09-17 06:59</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.pdf</t>
+          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v1.pdf</t>
         </is>
       </c>
     </row>
@@ -19502,7 +19642,7 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>Center_for_Active_Living_CAL_Comprehensive_Report_v1.md</t>
+          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.md</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -19511,46 +19651,46 @@
         </is>
       </c>
       <c r="F17" s="17" t="n">
-        <v>32670</v>
+        <v>31676</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>31.9 KB</t>
+          <t>30.9 KB</t>
         </is>
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham / CALBC / EDM Studio</t>
+          <t>Primary Municipal Records / Mass. Registry of Deeds</t>
         </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>M.G.L. c. 44, § 7; Mass. Const. Amend. Art. 97; 2026 ATM Art. 12</t>
+          <t>Historical M.G.L. c. 184A, § 3; M.G.L. c. 184, § 23; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
         </is>
       </c>
       <c r="K17" s="18" t="inlineStr">
         <is>
-          <t>Comprehensive 12-section investigation of the Center for Active Living at Bare Cove Park Drive and its April 27, 2026 Town Meeting defeat (510 Yes to 470 No; failed 2/3 debt supermajority).</t>
+          <t>Preliminary primary-source research chronology and record index; strictly neutral factual reporting; segregates verified facts, factual inferences, and open legal questions; includes missing documents inventory and disclaimer. Not a title opinion.</t>
         </is>
       </c>
       <c r="L17" s="15" t="inlineStr">
         <is>
-          <t>Complete Analytical Report (Verified)</t>
+          <t>Neutral Primary Source Research Index &amp; Inventory (Verified)</t>
         </is>
       </c>
       <c r="M17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 16:19</t>
+          <t>2026-09-17 09:44</t>
         </is>
       </c>
       <c r="N17" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/executive_reports/Center_for_Active_Living_CAL_Comprehensive_Report_v1.md</t>
+          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.md</t>
         </is>
       </c>
     </row>
@@ -19572,7 +19712,7 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Center_for_Active_Living_CAL_Comprehensive_Report_v1.pdf</t>
+          <t>100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.pdf</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
@@ -19581,46 +19721,46 @@
         </is>
       </c>
       <c r="F18" s="21" t="n">
-        <v>93076</v>
+        <v>119536</v>
       </c>
       <c r="G18" s="22" t="inlineStr">
         <is>
-          <t>90.9 KB</t>
+          <t>116.7 KB</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
-          <t>Town of Hingham / CALBC / EDM Studio</t>
+          <t>Primary Municipal Records / Mass. Registry of Deeds</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
         <is>
-          <t>M.G.L. c. 44, § 7; Mass. Const. Amend. Art. 97; 2026 ATM Art. 12</t>
+          <t>Historical M.G.L. c. 184A, § 3; M.G.L. c. 184, § 23; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr">
         <is>
-          <t>Comprehensive 12-section investigation of the Center for Active Living at Bare Cove Park Drive and its April 27, 2026 Town Meeting defeat (510 Yes to 470 No; failed 2/3 debt supermajority).</t>
+          <t>Preliminary primary-source research chronology and record index; strictly neutral factual reporting; segregates verified facts, factual inferences, and open legal questions; includes missing documents inventory and disclaimer. Not a title opinion.</t>
         </is>
       </c>
       <c r="L18" s="19" t="inlineStr">
         <is>
-          <t>Complete Analytical Report (Verified)</t>
+          <t>Neutral Primary Source Research Index &amp; Inventory (Verified)</t>
         </is>
       </c>
       <c r="M18" s="19" t="inlineStr">
         <is>
-          <t>2026-09-16 16:19</t>
+          <t>2026-09-17 09:44</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/executive_reports/Center_for_Active_Living_CAL_Comprehensive_Report_v1.pdf</t>
+          <t>agent_created_deliverables/executive_reports/100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.pdf</t>
         </is>
       </c>
     </row>
@@ -19637,25 +19777,25 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>Master Chronological Compendiums</t>
+          <t>Executive Reports &amp; Briefings</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Comprehensive_Chronological_Master_Archive_v1.pdf</t>
+          <t>Center_for_Active_Living_CAL_Comprehensive_Report_v1.md</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F19" s="17" t="n">
-        <v>105271962</v>
+        <v>32670</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>100.4 MB</t>
+          <t>31.9 KB</t>
         </is>
       </c>
       <c r="H19" s="15" t="inlineStr">
@@ -19665,32 +19805,32 @@
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>Town of Hingham / CALBC / EDM Studio</t>
         </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>M.G.L. c. 44, § 7; Mass. Const. Amend. Art. 97; 2026 ATM Art. 12</t>
         </is>
       </c>
       <c r="K19" s="18" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Comprehensive 12-section investigation of the Center for Active Living at Bare Cove Park Drive and its April 27, 2026 Town Meeting defeat (510 Yes to 470 No; failed 2/3 debt supermajority).</t>
         </is>
       </c>
       <c r="L19" s="15" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Complete Analytical Report (Verified)</t>
         </is>
       </c>
       <c r="M19" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 09:11</t>
+          <t>2026-09-16 16:19</t>
         </is>
       </c>
       <c r="N19" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/master_compendiums/100_Beal_Street_Comprehensive_Chronological_Master_Archive_v1.pdf</t>
+          <t>agent_created_deliverables/executive_reports/Center_for_Active_Living_CAL_Comprehensive_Report_v1.md</t>
         </is>
       </c>
     </row>
@@ -19707,25 +19847,25 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>Master Chronological Compendiums</t>
+          <t>Executive Reports &amp; Briefings</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Master_Compendium_v1.md</t>
+          <t>Center_for_Active_Living_CAL_Comprehensive_Report_v1.pdf</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="F20" s="21" t="n">
-        <v>34240</v>
+        <v>93076</v>
       </c>
       <c r="G20" s="22" t="inlineStr">
         <is>
-          <t>33.4 KB</t>
+          <t>90.9 KB</t>
         </is>
       </c>
       <c r="H20" s="19" t="inlineStr">
@@ -19735,32 +19875,32 @@
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
-          <t>AI Research Team &amp; Quality Control</t>
+          <t>Town of Hingham / CALBC / EDM Studio</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
         <is>
-          <t>Complete Municipal &amp; State Statutory Compilation</t>
+          <t>M.G.L. c. 44, § 7; Mass. Const. Amend. Art. 97; 2026 ATM Art. 12</t>
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr">
         <is>
-          <t>Comprehensive multi-megabyte compendium transcribing and synthesizing all historical warrants, board minutes, registry deeds, and environmental filings.</t>
+          <t>Comprehensive 12-section investigation of the Center for Active Living at Bare Cove Park Drive and its April 27, 2026 Town Meeting defeat (510 Yes to 470 No; failed 2/3 debt supermajority).</t>
         </is>
       </c>
       <c r="L20" s="19" t="inlineStr">
         <is>
-          <t>Master Synthesis (Verified)</t>
+          <t>Complete Analytical Report (Verified)</t>
         </is>
       </c>
       <c r="M20" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 10:22</t>
+          <t>2026-09-16 16:19</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/master_compendiums/100_Beal_Street_Master_Compendium_v1.md</t>
+          <t>agent_created_deliverables/executive_reports/Center_for_Active_Living_CAL_Comprehensive_Report_v1.pdf</t>
         </is>
       </c>
     </row>
@@ -19782,55 +19922,55 @@
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Master_Compendium_v2.md</t>
+          <t>100_Beal_Street_Comprehensive_Chronological_Master_Archive_v1.pdf</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="F21" s="17" t="n">
-        <v>4225700</v>
+        <v>105271962</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>4.0 MB</t>
+          <t>100.4 MB</t>
         </is>
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
-          <t>AI Research Team &amp; Quality Control</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>Complete Municipal &amp; State Statutory Compilation</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K21" s="18" t="inlineStr">
         <is>
-          <t>Comprehensive multi-megabyte compendium transcribing and synthesizing all historical warrants, board minutes, registry deeds, and environmental filings.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L21" s="15" t="inlineStr">
         <is>
-          <t>Master Synthesis (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M21" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 16:02</t>
+          <t>2026-09-16 09:11</t>
         </is>
       </c>
       <c r="N21" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/master_compendiums/100_Beal_Street_Master_Compendium_v2.md</t>
+          <t>agent_created_deliverables/master_compendiums/100_Beal_Street_Comprehensive_Chronological_Master_Archive_v1.pdf</t>
         </is>
       </c>
     </row>
@@ -19847,12 +19987,12 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>Companion Markdown Transcriptions</t>
+          <t>Master Chronological Compendiums</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>100-Beal-Street-ANRAD-Application_v1.md</t>
+          <t>100_Beal_Street_Master_Compendium_v1.md</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
@@ -19861,11 +20001,11 @@
         </is>
       </c>
       <c r="F22" s="21" t="n">
-        <v>66942</v>
+        <v>34240</v>
       </c>
       <c r="G22" s="22" t="inlineStr">
         <is>
-          <t>65.4 KB</t>
+          <t>33.4 KB</t>
         </is>
       </c>
       <c r="H22" s="19" t="inlineStr">
@@ -19875,32 +20015,32 @@
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>AI Research Team &amp; Quality Control</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>Complete Municipal &amp; State Statutory Compilation</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Comprehensive multi-megabyte compendium transcribing and synthesizing all historical warrants, board minutes, registry deeds, and environmental filings.</t>
         </is>
       </c>
       <c r="L22" s="19" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Master Synthesis (Verified)</t>
         </is>
       </c>
       <c r="M22" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 10:23</t>
+          <t>2026-09-14 10:22</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/100-Beal-Street-ANRAD-Application_v1.md</t>
+          <t>agent_created_deliverables/master_compendiums/100_Beal_Street_Master_Compendium_v1.md</t>
         </is>
       </c>
     </row>
@@ -19917,12 +20057,12 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>Companion Markdown Transcriptions</t>
+          <t>Master Chronological Compendiums</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>100-Beal-Street-ANRAD-Plans_v1.md</t>
+          <t>100_Beal_Street_Master_Compendium_v2.md</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -19931,46 +20071,46 @@
         </is>
       </c>
       <c r="F23" s="17" t="n">
-        <v>21350</v>
+        <v>4225700</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>20.8 KB</t>
+          <t>4.0 MB</t>
         </is>
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="I23" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>AI Research Team &amp; Quality Control</t>
         </is>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>Complete Municipal &amp; State Statutory Compilation</t>
         </is>
       </c>
       <c r="K23" s="18" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Comprehensive multi-megabyte compendium transcribing and synthesizing all historical warrants, board minutes, registry deeds, and environmental filings.</t>
         </is>
       </c>
       <c r="L23" s="15" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Master Synthesis (Verified)</t>
         </is>
       </c>
       <c r="M23" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14 10:23</t>
+          <t>2026-09-16 16:02</t>
         </is>
       </c>
       <c r="N23" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/100-Beal-Street-ANRAD-Plans_v1.md</t>
+          <t>agent_created_deliverables/master_compendiums/100_Beal_Street_Master_Compendium_v2.md</t>
         </is>
       </c>
     </row>
@@ -19992,7 +20132,7 @@
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>25-Bare-Cove-Park-Drive-Public-Comments-Combined-100-Beal-Mention_v1.md</t>
+          <t>100-Beal-Street-ANRAD-Application_v1.md</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
@@ -20001,11 +20141,11 @@
         </is>
       </c>
       <c r="F24" s="21" t="n">
-        <v>41086</v>
+        <v>66942</v>
       </c>
       <c r="G24" s="22" t="inlineStr">
         <is>
-          <t>40.1 KB</t>
+          <t>65.4 KB</t>
         </is>
       </c>
       <c r="H24" s="19" t="inlineStr">
@@ -20040,7 +20180,7 @@
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/25-Bare-Cove-Park-Drive-Public-Comments-Combined-100-Beal-Mention_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/100-Beal-Street-ANRAD-Application_v1.md</t>
         </is>
       </c>
     </row>
@@ -20062,7 +20202,7 @@
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>25-Bare-Cove-Park-Drive-Supplemental-Information-Letter-ORAD-034-1509_v1.md</t>
+          <t>100-Beal-Street-ANRAD-Plans_v1.md</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -20071,11 +20211,11 @@
         </is>
       </c>
       <c r="F25" s="17" t="n">
-        <v>27469</v>
+        <v>21350</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>26.8 KB</t>
+          <t>20.8 KB</t>
         </is>
       </c>
       <c r="H25" s="15" t="inlineStr">
@@ -20110,7 +20250,7 @@
       </c>
       <c r="N25" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/25-Bare-Cove-Park-Drive-Supplemental-Information-Letter-ORAD-034-1509_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/100-Beal-Street-ANRAD-Plans_v1.md</t>
         </is>
       </c>
     </row>
@@ -20132,7 +20272,7 @@
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Bare-Cove-Park-Drive-HCAL-Peer-Review-Report-ORAD-034-1509-Citation_v1.md</t>
+          <t>25-Bare-Cove-Park-Drive-Public-Comments-Combined-100-Beal-Mention_v1.md</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
@@ -20141,11 +20281,11 @@
         </is>
       </c>
       <c r="F26" s="21" t="n">
-        <v>20900</v>
+        <v>41086</v>
       </c>
       <c r="G26" s="22" t="inlineStr">
         <is>
-          <t>20.4 KB</t>
+          <t>40.1 KB</t>
         </is>
       </c>
       <c r="H26" s="19" t="inlineStr">
@@ -20180,7 +20320,7 @@
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Bare-Cove-Park-Drive-HCAL-Peer-Review-Report-ORAD-034-1509-Citation_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/25-Bare-Cove-Park-Drive-Public-Comments-Combined-100-Beal-Mention_v1.md</t>
         </is>
       </c>
     </row>
@@ -20202,7 +20342,7 @@
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>Bohler_Due_Diligence_Feasibility_Report_and_Lucas_Wetlands_v1.md</t>
+          <t>25-Bare-Cove-Park-Drive-Supplemental-Information-Letter-ORAD-034-1509_v1.md</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -20211,11 +20351,11 @@
         </is>
       </c>
       <c r="F27" s="17" t="n">
-        <v>100475</v>
+        <v>27469</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>98.1 KB</t>
+          <t>26.8 KB</t>
         </is>
       </c>
       <c r="H27" s="15" t="inlineStr">
@@ -20250,7 +20390,7 @@
       </c>
       <c r="N27" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Bohler_Due_Diligence_Feasibility_Report_and_Lucas_Wetlands_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/25-Bare-Cove-Park-Drive-Supplemental-Information-Letter-ORAD-034-1509_v1.md</t>
         </is>
       </c>
     </row>
@@ -20272,7 +20412,7 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Agenda_2024-11-04_DEP_034-1509_v1.md</t>
+          <t>Bare-Cove-Park-Drive-HCAL-Peer-Review-Report-ORAD-034-1509-Citation_v1.md</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -20281,11 +20421,11 @@
         </is>
       </c>
       <c r="F28" s="21" t="n">
-        <v>3569</v>
+        <v>20900</v>
       </c>
       <c r="G28" s="22" t="inlineStr">
         <is>
-          <t>3.5 KB</t>
+          <t>20.4 KB</t>
         </is>
       </c>
       <c r="H28" s="19" t="inlineStr">
@@ -20320,7 +20460,7 @@
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-11-04_DEP_034-1509_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Bare-Cove-Park-Drive-HCAL-Peer-Review-Report-ORAD-034-1509-Citation_v1.md</t>
         </is>
       </c>
     </row>
@@ -20342,7 +20482,7 @@
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Agenda_2024-11-18_v1.md</t>
+          <t>Bohler_Due_Diligence_Feasibility_Report_and_Lucas_Wetlands_v1.md</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
@@ -20351,11 +20491,11 @@
         </is>
       </c>
       <c r="F29" s="17" t="n">
-        <v>3922</v>
+        <v>100475</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>3.8 KB</t>
+          <t>98.1 KB</t>
         </is>
       </c>
       <c r="H29" s="15" t="inlineStr">
@@ -20390,7 +20530,7 @@
       </c>
       <c r="N29" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-11-18_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Bohler_Due_Diligence_Feasibility_Report_and_Lucas_Wetlands_v1.md</t>
         </is>
       </c>
     </row>
@@ -20412,7 +20552,7 @@
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Agenda_2024-12-02_v1.md</t>
+          <t>Conservation_Commission_Agenda_2024-11-04_DEP_034-1509_v1.md</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
@@ -20421,11 +20561,11 @@
         </is>
       </c>
       <c r="F30" s="21" t="n">
-        <v>3922</v>
+        <v>3569</v>
       </c>
       <c r="G30" s="22" t="inlineStr">
         <is>
-          <t>3.8 KB</t>
+          <t>3.5 KB</t>
         </is>
       </c>
       <c r="H30" s="19" t="inlineStr">
@@ -20460,7 +20600,7 @@
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-12-02_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-11-04_DEP_034-1509_v1.md</t>
         </is>
       </c>
     </row>
@@ -20482,7 +20622,7 @@
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Agenda_2024-12-16_v1.md</t>
+          <t>Conservation_Commission_Agenda_2024-11-18_v1.md</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -20530,7 +20670,7 @@
       </c>
       <c r="N31" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-12-16_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-11-18_v1.md</t>
         </is>
       </c>
     </row>
@@ -20552,7 +20692,7 @@
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Minutes_2024-11-04_DEP_034-1509_v1.md</t>
+          <t>Conservation_Commission_Agenda_2024-12-02_v1.md</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
@@ -20561,11 +20701,11 @@
         </is>
       </c>
       <c r="F32" s="21" t="n">
-        <v>29843</v>
+        <v>3922</v>
       </c>
       <c r="G32" s="22" t="inlineStr">
         <is>
-          <t>29.1 KB</t>
+          <t>3.8 KB</t>
         </is>
       </c>
       <c r="H32" s="19" t="inlineStr">
@@ -20600,7 +20740,7 @@
       </c>
       <c r="N32" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-11-04_DEP_034-1509_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-12-02_v1.md</t>
         </is>
       </c>
     </row>
@@ -20622,7 +20762,7 @@
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Minutes_2024-11-18_v1.md</t>
+          <t>Conservation_Commission_Agenda_2024-12-16_v1.md</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
@@ -20631,11 +20771,11 @@
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>46813</v>
+        <v>3922</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>45.7 KB</t>
+          <t>3.8 KB</t>
         </is>
       </c>
       <c r="H33" s="15" t="inlineStr">
@@ -20670,7 +20810,7 @@
       </c>
       <c r="N33" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-11-18_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Agenda_2024-12-16_v1.md</t>
         </is>
       </c>
     </row>
@@ -20692,7 +20832,7 @@
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Minutes_2024-12-02_v1.md</t>
+          <t>Conservation_Commission_Minutes_2024-11-04_DEP_034-1509_v1.md</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
@@ -20701,11 +20841,11 @@
         </is>
       </c>
       <c r="F34" s="21" t="n">
-        <v>46813</v>
+        <v>29843</v>
       </c>
       <c r="G34" s="22" t="inlineStr">
         <is>
-          <t>45.7 KB</t>
+          <t>29.1 KB</t>
         </is>
       </c>
       <c r="H34" s="19" t="inlineStr">
@@ -20740,7 +20880,7 @@
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-12-02_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-11-04_DEP_034-1509_v1.md</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20902,7 @@
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>Conservation_Commission_Minutes_2024-12-16_v1.md</t>
+          <t>Conservation_Commission_Minutes_2024-11-18_v1.md</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
@@ -20810,7 +20950,7 @@
       </c>
       <c r="N35" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-12-16_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-11-18_v1.md</t>
         </is>
       </c>
     </row>
@@ -20832,7 +20972,7 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2024-02-13_Beal_Surplus_MHP_RFP_v1.md</t>
+          <t>Conservation_Commission_Minutes_2024-12-02_v1.md</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr">
@@ -20841,11 +20981,11 @@
         </is>
       </c>
       <c r="F36" s="21" t="n">
-        <v>1567</v>
+        <v>46813</v>
       </c>
       <c r="G36" s="22" t="inlineStr">
         <is>
-          <t>1.5 KB</t>
+          <t>45.7 KB</t>
         </is>
       </c>
       <c r="H36" s="19" t="inlineStr">
@@ -20880,7 +21020,7 @@
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2024-02-13_Beal_Surplus_MHP_RFP_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-12-02_v1.md</t>
         </is>
       </c>
     </row>
@@ -20902,7 +21042,7 @@
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2024-09-10_Beal_Excess_Declaration_RFP_Release_v1.md</t>
+          <t>Conservation_Commission_Minutes_2024-12-16_v1.md</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
@@ -20911,11 +21051,11 @@
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>2036</v>
+        <v>46813</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>2.0 KB</t>
+          <t>45.7 KB</t>
         </is>
       </c>
       <c r="H37" s="15" t="inlineStr">
@@ -20950,7 +21090,7 @@
       </c>
       <c r="N37" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2024-09-10_Beal_Excess_Declaration_RFP_Release_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Conservation_Commission_Minutes_2024-12-16_v1.md</t>
         </is>
       </c>
     </row>
@@ -20972,7 +21112,7 @@
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2025-08-12_Peabody_Award_LDDA_v1.md</t>
+          <t>HHA_Agenda_2024-02-13_Beal_Surplus_MHP_RFP_v1.md</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr">
@@ -20981,11 +21121,11 @@
         </is>
       </c>
       <c r="F38" s="21" t="n">
-        <v>2180</v>
+        <v>1567</v>
       </c>
       <c r="G38" s="22" t="inlineStr">
         <is>
-          <t>2.1 KB</t>
+          <t>1.5 KB</t>
         </is>
       </c>
       <c r="H38" s="19" t="inlineStr">
@@ -20995,22 +21135,22 @@
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
-          <t>Hingham Housing Authority Board of Commissioners</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J38" s="20" t="inlineStr">
         <is>
-          <t>M.G.L. c. 30B, § 16</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
         <is>
-          <t>Official meeting minutes of August 12, 2025 recording 4-0 vote designating Peabody Properties / AHSC as developer for 100 Beal Street.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L38" s="19" t="inlineStr">
         <is>
-          <t>Official Board Minutes (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M38" s="19" t="inlineStr">
@@ -21020,7 +21160,7 @@
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2025-08-12_Peabody_Award_LDDA_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2024-02-13_Beal_Surplus_MHP_RFP_v1.md</t>
         </is>
       </c>
     </row>
@@ -21042,7 +21182,7 @@
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2026-02-10_Meeting_v1.md</t>
+          <t>HHA_Agenda_2024-09-10_Beal_Excess_Declaration_RFP_Release_v1.md</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr">
@@ -21051,11 +21191,11 @@
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>2668</v>
+        <v>2036</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>2.6 KB</t>
+          <t>2.0 KB</t>
         </is>
       </c>
       <c r="H39" s="15" t="inlineStr">
@@ -21090,7 +21230,7 @@
       </c>
       <c r="N39" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-02-10_Meeting_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2024-09-10_Beal_Excess_Declaration_RFP_Release_v1.md</t>
         </is>
       </c>
     </row>
@@ -21112,7 +21252,7 @@
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2026-04-14_Beal_Sprinkler_Bids_v1.md</t>
+          <t>HHA_Agenda_2025-08-12_Peabody_Award_LDDA_v1.md</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr">
@@ -21121,11 +21261,11 @@
         </is>
       </c>
       <c r="F40" s="21" t="n">
-        <v>2983</v>
+        <v>2180</v>
       </c>
       <c r="G40" s="22" t="inlineStr">
         <is>
-          <t>2.9 KB</t>
+          <t>2.1 KB</t>
         </is>
       </c>
       <c r="H40" s="19" t="inlineStr">
@@ -21135,22 +21275,22 @@
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>Hingham Housing Authority Board of Commissioners</t>
         </is>
       </c>
       <c r="J40" s="20" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>M.G.L. c. 30B, § 16</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Official meeting minutes of August 12, 2025 recording 4-0 vote designating Peabody Properties / AHSC as developer for 100 Beal Street.</t>
         </is>
       </c>
       <c r="L40" s="19" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Official Board Minutes (Verified)</t>
         </is>
       </c>
       <c r="M40" s="19" t="inlineStr">
@@ -21160,7 +21300,7 @@
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-04-14_Beal_Sprinkler_Bids_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2025-08-12_Peabody_Award_LDDA_v1.md</t>
         </is>
       </c>
     </row>
@@ -21182,7 +21322,7 @@
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2026-06-09_Annual_Plan_v1.md</t>
+          <t>HHA_Agenda_2026-02-10_Meeting_v1.md</t>
         </is>
       </c>
       <c r="E41" s="15" t="inlineStr">
@@ -21191,11 +21331,11 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>1900</v>
+        <v>2668</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>1.9 KB</t>
+          <t>2.6 KB</t>
         </is>
       </c>
       <c r="H41" s="15" t="inlineStr">
@@ -21230,7 +21370,7 @@
       </c>
       <c r="N41" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-06-09_Annual_Plan_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-02-10_Meeting_v1.md</t>
         </is>
       </c>
     </row>
@@ -21252,7 +21392,7 @@
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2026-07-14_Beal_St_Sprinklers_v1.md</t>
+          <t>HHA_Agenda_2026-04-14_Beal_Sprinkler_Bids_v1.md</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
@@ -21261,11 +21401,11 @@
         </is>
       </c>
       <c r="F42" s="21" t="n">
-        <v>3257</v>
+        <v>2983</v>
       </c>
       <c r="G42" s="22" t="inlineStr">
         <is>
-          <t>3.2 KB</t>
+          <t>2.9 KB</t>
         </is>
       </c>
       <c r="H42" s="19" t="inlineStr">
@@ -21300,7 +21440,7 @@
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-07-14_Beal_St_Sprinklers_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-04-14_Beal_Sprinkler_Bids_v1.md</t>
         </is>
       </c>
     </row>
@@ -21322,7 +21462,7 @@
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>HHA_Agenda_2026-08-25_Land_Disposition_Peabody_v1.md</t>
+          <t>HHA_Agenda_2026-06-09_Annual_Plan_v1.md</t>
         </is>
       </c>
       <c r="E43" s="15" t="inlineStr">
@@ -21331,11 +21471,11 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>1501</v>
+        <v>1900</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>1.5 KB</t>
+          <t>1.9 KB</t>
         </is>
       </c>
       <c r="H43" s="15" t="inlineStr">
@@ -21370,7 +21510,7 @@
       </c>
       <c r="N43" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-08-25_Land_Disposition_Peabody_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-06-09_Annual_Plan_v1.md</t>
         </is>
       </c>
     </row>
@@ -21392,7 +21532,7 @@
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>HHA_Minutes_2019-07-09_100_Beal_School_Tract_II_v1.md</t>
+          <t>HHA_Agenda_2026-07-14_Beal_St_Sprinklers_v1.md</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr">
@@ -21401,11 +21541,11 @@
         </is>
       </c>
       <c r="F44" s="21" t="n">
-        <v>6627</v>
+        <v>3257</v>
       </c>
       <c r="G44" s="22" t="inlineStr">
         <is>
-          <t>6.5 KB</t>
+          <t>3.2 KB</t>
         </is>
       </c>
       <c r="H44" s="19" t="inlineStr">
@@ -21440,7 +21580,7 @@
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2019-07-09_100_Beal_School_Tract_II_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-07-14_Beal_St_Sprinklers_v1.md</t>
         </is>
       </c>
     </row>
@@ -21462,7 +21602,7 @@
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>HHA_Minutes_2021-09-07_Rescission_Vote_v1.md</t>
+          <t>HHA_Agenda_2026-08-25_Land_Disposition_Peabody_v1.md</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
@@ -21471,11 +21611,11 @@
         </is>
       </c>
       <c r="F45" s="17" t="n">
-        <v>9130</v>
+        <v>1501</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>8.9 KB</t>
+          <t>1.5 KB</t>
         </is>
       </c>
       <c r="H45" s="15" t="inlineStr">
@@ -21485,32 +21625,32 @@
       </c>
       <c r="I45" s="16" t="inlineStr">
         <is>
-          <t>Hingham Housing Authority (Dir. James Marathas)</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>M.G.L. c. 121B, § 34; HHA By-Laws</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K45" s="18" t="inlineStr">
         <is>
-          <t>Official meeting minutes of Sept 7, 2021 recording 4-0 vote formally rescinding the June 5, 2019 transfer motion, keeping land in HHA ownership.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L45" s="15" t="inlineStr">
         <is>
-          <t>Official Board Minutes (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M45" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 16:46</t>
+          <t>2026-09-14 10:23</t>
         </is>
       </c>
       <c r="N45" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2021-09-07_Rescission_Vote_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Agenda_2026-08-25_Land_Disposition_Peabody_v1.md</t>
         </is>
       </c>
     </row>
@@ -21532,7 +21672,7 @@
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>HHA_Minutes_2025-08-12_Peabody_Award_Authentic_v1.md</t>
+          <t>HHA_Minutes_2019-07-09_100_Beal_School_Tract_II_v1.md</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
@@ -21541,11 +21681,11 @@
         </is>
       </c>
       <c r="F46" s="21" t="n">
-        <v>4338</v>
+        <v>6627</v>
       </c>
       <c r="G46" s="22" t="inlineStr">
         <is>
-          <t>4.2 KB</t>
+          <t>6.5 KB</t>
         </is>
       </c>
       <c r="H46" s="19" t="inlineStr">
@@ -21555,32 +21695,32 @@
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
-          <t>Hingham Housing Authority Board of Commissioners</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J46" s="20" t="inlineStr">
         <is>
-          <t>M.G.L. c. 30B, § 16</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K46" s="23" t="inlineStr">
         <is>
-          <t>Official meeting minutes of August 12, 2025 recording 4-0 vote designating Peabody Properties / AHSC as developer for 100 Beal Street.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L46" s="19" t="inlineStr">
         <is>
-          <t>Official Board Minutes (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M46" s="19" t="inlineStr">
         <is>
-          <t>2026-09-16 16:46</t>
+          <t>2026-09-14 10:23</t>
         </is>
       </c>
       <c r="N46" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2025-08-12_Peabody_Award_Authentic_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2019-07-09_100_Beal_School_Tract_II_v1.md</t>
         </is>
       </c>
     </row>
@@ -21602,7 +21742,7 @@
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>HHA_Minutes_2025-08-12_Peabody_Award_LDDA_v1.md</t>
+          <t>HHA_Minutes_2021-09-07_Rescission_Vote_v1.md</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
@@ -21611,11 +21751,11 @@
         </is>
       </c>
       <c r="F47" s="17" t="n">
-        <v>7292</v>
+        <v>9130</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>7.1 KB</t>
+          <t>8.9 KB</t>
         </is>
       </c>
       <c r="H47" s="15" t="inlineStr">
@@ -21625,17 +21765,17 @@
       </c>
       <c r="I47" s="16" t="inlineStr">
         <is>
-          <t>Hingham Housing Authority Board of Commissioners</t>
+          <t>Hingham Housing Authority (Dir. James Marathas)</t>
         </is>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>M.G.L. c. 30B, § 16</t>
+          <t>M.G.L. c. 121B, § 34; HHA By-Laws</t>
         </is>
       </c>
       <c r="K47" s="18" t="inlineStr">
         <is>
-          <t>Official meeting minutes of August 12, 2025 recording 4-0 vote designating Peabody Properties / AHSC as developer for 100 Beal Street.</t>
+          <t>Official meeting minutes of Sept 7, 2021 recording 4-0 vote formally rescinding the June 5, 2019 transfer motion, keeping land in HHA ownership.</t>
         </is>
       </c>
       <c r="L47" s="15" t="inlineStr">
@@ -21645,12 +21785,12 @@
       </c>
       <c r="M47" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14 10:23</t>
+          <t>2026-09-16 16:46</t>
         </is>
       </c>
       <c r="N47" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2025-08-12_Peabody_Award_LDDA_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2021-09-07_Rescission_Vote_v1.md</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21812,7 @@
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Hingham-HA-Beal-St-RFP-04-16-25_Final_all-attachments_v1.md</t>
+          <t>HHA_Minutes_2025-08-12_Peabody_Award_Authentic_v1.md</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
@@ -21681,11 +21821,11 @@
         </is>
       </c>
       <c r="F48" s="21" t="n">
-        <v>303658</v>
+        <v>4338</v>
       </c>
       <c r="G48" s="22" t="inlineStr">
         <is>
-          <t>296.5 KB</t>
+          <t>4.2 KB</t>
         </is>
       </c>
       <c r="H48" s="19" t="inlineStr">
@@ -21695,32 +21835,32 @@
       </c>
       <c r="I48" s="20" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>Hingham Housing Authority Board of Commissioners</t>
         </is>
       </c>
       <c r="J48" s="20" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>M.G.L. c. 30B, § 16</t>
         </is>
       </c>
       <c r="K48" s="23" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Official meeting minutes of August 12, 2025 recording 4-0 vote designating Peabody Properties / AHSC as developer for 100 Beal Street.</t>
         </is>
       </c>
       <c r="L48" s="19" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Official Board Minutes (Verified)</t>
         </is>
       </c>
       <c r="M48" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 10:23</t>
+          <t>2026-09-16 16:46</t>
         </is>
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham-HA-Beal-St-RFP-04-16-25_Final_all-attachments_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2025-08-12_Peabody_Award_Authentic_v1.md</t>
         </is>
       </c>
     </row>
@@ -21742,7 +21882,7 @@
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>Hingham_100_Beal_ALTA_Survey_and_Subdivision_Plans_v1.md</t>
+          <t>HHA_Minutes_2025-08-12_Peabody_Award_LDDA_v1.md</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
@@ -21751,11 +21891,11 @@
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>33044</v>
+        <v>7292</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>32.3 KB</t>
+          <t>7.1 KB</t>
         </is>
       </c>
       <c r="H49" s="15" t="inlineStr">
@@ -21765,22 +21905,22 @@
       </c>
       <c r="I49" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>Hingham Housing Authority Board of Commissioners</t>
         </is>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>M.G.L. c. 30B, § 16</t>
         </is>
       </c>
       <c r="K49" s="18" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Official meeting minutes of August 12, 2025 recording 4-0 vote designating Peabody Properties / AHSC as developer for 100 Beal Street.</t>
         </is>
       </c>
       <c r="L49" s="15" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Official Board Minutes (Verified)</t>
         </is>
       </c>
       <c r="M49" s="15" t="inlineStr">
@@ -21790,7 +21930,7 @@
       </c>
       <c r="N49" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_100_Beal_ALTA_Survey_and_Subdivision_Plans_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/HHA_Minutes_2025-08-12_Peabody_Award_LDDA_v1.md</t>
         </is>
       </c>
     </row>
@@ -21812,7 +21952,7 @@
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>Hingham_Beal_Street_Deed_1989_and_ZBA_Decision_v1.md</t>
+          <t>Hingham-HA-Beal-St-RFP-04-16-25_Final_all-attachments_v1.md</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
@@ -21821,11 +21961,11 @@
         </is>
       </c>
       <c r="F50" s="21" t="n">
-        <v>11705</v>
+        <v>303658</v>
       </c>
       <c r="G50" s="22" t="inlineStr">
         <is>
-          <t>11.4 KB</t>
+          <t>296.5 KB</t>
         </is>
       </c>
       <c r="H50" s="19" t="inlineStr">
@@ -21860,7 +22000,7 @@
       </c>
       <c r="N50" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Beal_Street_Deed_1989_and_ZBA_Decision_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham-HA-Beal-St-RFP-04-16-25_Final_all-attachments_v1.md</t>
         </is>
       </c>
     </row>
@@ -21882,7 +22022,7 @@
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>Hingham_Housing_Authority_Draft_Ground_Lease_100_Beal_v1.md</t>
+          <t>Hingham_100_Beal_ALTA_Survey_and_Subdivision_Plans_v1.md</t>
         </is>
       </c>
       <c r="E51" s="15" t="inlineStr">
@@ -21891,11 +22031,11 @@
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>56917</v>
+        <v>33044</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>55.6 KB</t>
+          <t>32.3 KB</t>
         </is>
       </c>
       <c r="H51" s="15" t="inlineStr">
@@ -21930,7 +22070,7 @@
       </c>
       <c r="N51" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Housing_Authority_Draft_Ground_Lease_100_Beal_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_100_Beal_ALTA_Survey_and_Subdivision_Plans_v1.md</t>
         </is>
       </c>
     </row>
@@ -21952,7 +22092,7 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Hingham_Housing_Authority_Draft_LDA_100_Beal_v1.md</t>
+          <t>Hingham_Beal_Street_Deed_1989_and_ZBA_Decision_v1.md</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
@@ -21961,11 +22101,11 @@
         </is>
       </c>
       <c r="F52" s="21" t="n">
-        <v>68604</v>
+        <v>11705</v>
       </c>
       <c r="G52" s="22" t="inlineStr">
         <is>
-          <t>67.0 KB</t>
+          <t>11.4 KB</t>
         </is>
       </c>
       <c r="H52" s="19" t="inlineStr">
@@ -22000,7 +22140,7 @@
       </c>
       <c r="N52" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Housing_Authority_Draft_LDA_100_Beal_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Beal_Street_Deed_1989_and_ZBA_Decision_v1.md</t>
         </is>
       </c>
     </row>
@@ -22022,7 +22162,7 @@
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>Hingham_Town_Charter_Bylaws_Excerpts_v1.md</t>
+          <t>Hingham_Housing_Authority_Draft_Ground_Lease_100_Beal_v1.md</t>
         </is>
       </c>
       <c r="E53" s="15" t="inlineStr">
@@ -22031,11 +22171,11 @@
         </is>
       </c>
       <c r="F53" s="17" t="n">
-        <v>11796</v>
+        <v>56917</v>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>11.5 KB</t>
+          <t>55.6 KB</t>
         </is>
       </c>
       <c r="H53" s="15" t="inlineStr">
@@ -22070,7 +22210,7 @@
       </c>
       <c r="N53" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Charter_Bylaws_Excerpts_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Housing_Authority_Draft_Ground_Lease_100_Beal_v1.md</t>
         </is>
       </c>
     </row>
@@ -22092,7 +22232,7 @@
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>Hingham_Town_Meeting_2006_Beal_St_Amended_Deed_Vote_v1.md</t>
+          <t>Hingham_Housing_Authority_Draft_LDA_100_Beal_v1.md</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
@@ -22101,11 +22241,11 @@
         </is>
       </c>
       <c r="F54" s="21" t="n">
-        <v>11120</v>
+        <v>68604</v>
       </c>
       <c r="G54" s="22" t="inlineStr">
         <is>
-          <t>10.9 KB</t>
+          <t>67.0 KB</t>
         </is>
       </c>
       <c r="H54" s="19" t="inlineStr">
@@ -22140,7 +22280,7 @@
       </c>
       <c r="N54" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_2006_Beal_St_Amended_Deed_Vote_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Housing_Authority_Draft_LDA_100_Beal_v1.md</t>
         </is>
       </c>
     </row>
@@ -22162,7 +22302,7 @@
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Hingham_Town_Meeting_Warrant_2006_Article_38_School_Tract_II_v1.md</t>
+          <t>Hingham_Town_Charter_Bylaws_Excerpts_v1.md</t>
         </is>
       </c>
       <c r="E55" s="15" t="inlineStr">
@@ -22171,11 +22311,11 @@
         </is>
       </c>
       <c r="F55" s="17" t="n">
-        <v>192413</v>
+        <v>11796</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>187.9 KB</t>
+          <t>11.5 KB</t>
         </is>
       </c>
       <c r="H55" s="15" t="inlineStr">
@@ -22185,22 +22325,22 @@
       </c>
       <c r="I55" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham Select Board / Advisory Committee</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>M.G.L. c. 39, § 10 (Town Meeting Warrant)</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K55" s="18" t="inlineStr">
         <is>
-          <t>Official Town Meeting Warrant detailing capital budget requests, debt exclusion articles, and municipal bylaws.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L55" s="15" t="inlineStr">
         <is>
-          <t>Official Town Warrant (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M55" s="15" t="inlineStr">
@@ -22210,7 +22350,7 @@
       </c>
       <c r="N55" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2006_Article_38_School_Tract_II_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Charter_Bylaws_Excerpts_v1.md</t>
         </is>
       </c>
     </row>
@@ -22232,7 +22372,7 @@
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>Hingham_Town_Meeting_Warrant_2016_Article_24_100_Beal_Street_v1.md</t>
+          <t>Hingham_Town_Meeting_2006_Beal_St_Amended_Deed_Vote_v1.md</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr">
@@ -22241,11 +22381,11 @@
         </is>
       </c>
       <c r="F56" s="21" t="n">
-        <v>294256</v>
+        <v>11120</v>
       </c>
       <c r="G56" s="22" t="inlineStr">
         <is>
-          <t>287.4 KB</t>
+          <t>10.9 KB</t>
         </is>
       </c>
       <c r="H56" s="19" t="inlineStr">
@@ -22255,22 +22395,22 @@
       </c>
       <c r="I56" s="20" t="inlineStr">
         <is>
-          <t>Town of Hingham Select Board / Advisory Committee</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J56" s="20" t="inlineStr">
         <is>
-          <t>M.G.L. c. 39, § 10 (Town Meeting Warrant)</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K56" s="23" t="inlineStr">
         <is>
-          <t>Official Town Meeting Warrant detailing capital budget requests, debt exclusion articles, and municipal bylaws.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L56" s="19" t="inlineStr">
         <is>
-          <t>Official Town Warrant (Verified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M56" s="19" t="inlineStr">
@@ -22280,7 +22420,7 @@
       </c>
       <c r="N56" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2016_Article_24_100_Beal_Street_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_2006_Beal_St_Amended_Deed_Vote_v1.md</t>
         </is>
       </c>
     </row>
@@ -22302,7 +22442,7 @@
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>Hingham_Town_Meeting_Warrant_2024_v1.md</t>
+          <t>Hingham_Town_Meeting_Warrant_2006_Article_38_School_Tract_II_v1.md</t>
         </is>
       </c>
       <c r="E57" s="15" t="inlineStr">
@@ -22311,11 +22451,11 @@
         </is>
       </c>
       <c r="F57" s="17" t="n">
-        <v>352751</v>
+        <v>192413</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>344.5 KB</t>
+          <t>187.9 KB</t>
         </is>
       </c>
       <c r="H57" s="15" t="inlineStr">
@@ -22350,7 +22490,7 @@
       </c>
       <c r="N57" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2024_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2006_Article_38_School_Tract_II_v1.md</t>
         </is>
       </c>
     </row>
@@ -22372,7 +22512,7 @@
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>Hingham_Town_Meeting_Warrant_2025_v1.md</t>
+          <t>Hingham_Town_Meeting_Warrant_2016_Article_24_100_Beal_Street_v1.md</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
@@ -22381,11 +22521,11 @@
         </is>
       </c>
       <c r="F58" s="21" t="n">
-        <v>291343</v>
+        <v>294256</v>
       </c>
       <c r="G58" s="22" t="inlineStr">
         <is>
-          <t>284.5 KB</t>
+          <t>287.4 KB</t>
         </is>
       </c>
       <c r="H58" s="19" t="inlineStr">
@@ -22420,7 +22560,7 @@
       </c>
       <c r="N58" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2025_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2016_Article_24_100_Beal_Street_v1.md</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22582,7 @@
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>Hingham_Town_Meeting_Warrant_2026_v1.md</t>
+          <t>Hingham_Town_Meeting_Warrant_2024_v1.md</t>
         </is>
       </c>
       <c r="E59" s="15" t="inlineStr">
@@ -22451,11 +22591,11 @@
         </is>
       </c>
       <c r="F59" s="17" t="n">
-        <v>281884</v>
+        <v>352751</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>275.3 KB</t>
+          <t>344.5 KB</t>
         </is>
       </c>
       <c r="H59" s="15" t="inlineStr">
@@ -22490,7 +22630,7 @@
       </c>
       <c r="N59" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2026_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2024_v1.md</t>
         </is>
       </c>
     </row>
@@ -22512,7 +22652,7 @@
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>SRP2020-South-Shore-Site-Readiness_v1.md</t>
+          <t>Hingham_Town_Meeting_Warrant_2025_v1.md</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
@@ -22521,11 +22661,11 @@
         </is>
       </c>
       <c r="F60" s="21" t="n">
-        <v>276120</v>
+        <v>291343</v>
       </c>
       <c r="G60" s="22" t="inlineStr">
         <is>
-          <t>269.6 KB</t>
+          <t>284.5 KB</t>
         </is>
       </c>
       <c r="H60" s="19" t="inlineStr">
@@ -22535,22 +22675,22 @@
       </c>
       <c r="I60" s="20" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>Town of Hingham Select Board / Advisory Committee</t>
         </is>
       </c>
       <c r="J60" s="20" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>M.G.L. c. 39, § 10 (Town Meeting Warrant)</t>
         </is>
       </c>
       <c r="K60" s="23" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Official Town Meeting Warrant detailing capital budget requests, debt exclusion articles, and municipal bylaws.</t>
         </is>
       </c>
       <c r="L60" s="19" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Official Town Warrant (Verified)</t>
         </is>
       </c>
       <c r="M60" s="19" t="inlineStr">
@@ -22560,7 +22700,7 @@
       </c>
       <c r="N60" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/SRP2020-South-Shore-Site-Readiness_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2025_v1.md</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22722,7 @@
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>Select_Board_Executive_Session_Minutes_2019-02-26_100_Beal_v1.md</t>
+          <t>Hingham_Town_Meeting_Warrant_2026_v1.md</t>
         </is>
       </c>
       <c r="E61" s="15" t="inlineStr">
@@ -22591,11 +22731,11 @@
         </is>
       </c>
       <c r="F61" s="17" t="n">
-        <v>10290</v>
+        <v>281884</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>10.0 KB</t>
+          <t>275.3 KB</t>
         </is>
       </c>
       <c r="H61" s="15" t="inlineStr">
@@ -22605,22 +22745,22 @@
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>Town of Hingham Select Board / Advisory Committee</t>
         </is>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>M.G.L. c. 39, § 10 (Town Meeting Warrant)</t>
         </is>
       </c>
       <c r="K61" s="18" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Official Town Meeting Warrant detailing capital budget requests, debt exclusion articles, and municipal bylaws.</t>
         </is>
       </c>
       <c r="L61" s="15" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Official Town Warrant (Verified)</t>
         </is>
       </c>
       <c r="M61" s="15" t="inlineStr">
@@ -22630,7 +22770,7 @@
       </c>
       <c r="N61" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Select_Board_Executive_Session_Minutes_2019-02-26_100_Beal_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Hingham_Town_Meeting_Warrant_2026_v1.md</t>
         </is>
       </c>
     </row>
@@ -22652,7 +22792,7 @@
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>Select_Board_Minutes_2017-09-20_100_Beal_v1.md</t>
+          <t>SRP2020-South-Shore-Site-Readiness_v1.md</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
@@ -22661,11 +22801,11 @@
         </is>
       </c>
       <c r="F62" s="21" t="n">
-        <v>7589</v>
+        <v>276120</v>
       </c>
       <c r="G62" s="22" t="inlineStr">
         <is>
-          <t>7.4 KB</t>
+          <t>269.6 KB</t>
         </is>
       </c>
       <c r="H62" s="19" t="inlineStr">
@@ -22700,7 +22840,7 @@
       </c>
       <c r="N62" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Select_Board_Minutes_2017-09-20_100_Beal_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/SRP2020-South-Shore-Site-Readiness_v1.md</t>
         </is>
       </c>
     </row>
@@ -22722,7 +22862,7 @@
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>Select_Board_Minutes_2018-02-08_100_Beal_v1.md</t>
+          <t>Select_Board_Executive_Session_Minutes_2019-02-26_100_Beal_v1.md</t>
         </is>
       </c>
       <c r="E63" s="15" t="inlineStr">
@@ -22731,11 +22871,11 @@
         </is>
       </c>
       <c r="F63" s="17" t="n">
-        <v>1511</v>
+        <v>10290</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>1.5 KB</t>
+          <t>10.0 KB</t>
         </is>
       </c>
       <c r="H63" s="15" t="inlineStr">
@@ -22770,7 +22910,7 @@
       </c>
       <c r="N63" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/Select_Board_Minutes_2018-02-08_100_Beal_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Select_Board_Executive_Session_Minutes_2019-02-26_100_Beal_v1.md</t>
         </is>
       </c>
     </row>
@@ -22792,7 +22932,7 @@
       </c>
       <c r="D64" s="20" t="inlineStr">
         <is>
-          <t>architectural_plans_summary_v1.md</t>
+          <t>Select_Board_Minutes_2017-09-20_100_Beal_v1.md</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
@@ -22801,11 +22941,11 @@
         </is>
       </c>
       <c r="F64" s="21" t="n">
-        <v>9439</v>
+        <v>7589</v>
       </c>
       <c r="G64" s="22" t="inlineStr">
         <is>
-          <t>9.2 KB</t>
+          <t>7.4 KB</t>
         </is>
       </c>
       <c r="H64" s="19" t="inlineStr">
@@ -22835,12 +22975,12 @@
       </c>
       <c r="M64" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 08:36</t>
+          <t>2026-09-14 10:23</t>
         </is>
       </c>
       <c r="N64" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/architectural_plans_summary_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Select_Board_Minutes_2017-09-20_100_Beal_v1.md</t>
         </is>
       </c>
     </row>
@@ -22862,7 +23002,7 @@
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>architectural_plans_summary_v2.md</t>
+          <t>Select_Board_Minutes_2018-02-08_100_Beal_v1.md</t>
         </is>
       </c>
       <c r="E65" s="15" t="inlineStr">
@@ -22871,16 +23011,16 @@
         </is>
       </c>
       <c r="F65" s="17" t="n">
-        <v>9321</v>
+        <v>1511</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>9.1 KB</t>
+          <t>1.5 KB</t>
         </is>
       </c>
       <c r="H65" s="15" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I65" s="16" t="inlineStr">
@@ -22905,12 +23045,12 @@
       </c>
       <c r="M65" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 16:08</t>
+          <t>2026-09-14 10:23</t>
         </is>
       </c>
       <c r="N65" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/architectural_plans_summary_v2.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/Select_Board_Minutes_2018-02-08_100_Beal_v1.md</t>
         </is>
       </c>
     </row>
@@ -22932,7 +23072,7 @@
       </c>
       <c r="D66" s="20" t="inlineStr">
         <is>
-          <t>bare_cove_tuckers_swamp_commentary_v1.md</t>
+          <t>architectural_plans_summary_v1.md</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr">
@@ -22941,11 +23081,11 @@
         </is>
       </c>
       <c r="F66" s="21" t="n">
-        <v>11075</v>
+        <v>9439</v>
       </c>
       <c r="G66" s="22" t="inlineStr">
         <is>
-          <t>10.8 KB</t>
+          <t>9.2 KB</t>
         </is>
       </c>
       <c r="H66" s="19" t="inlineStr">
@@ -22975,12 +23115,12 @@
       </c>
       <c r="M66" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 09:16</t>
+          <t>2026-09-14 08:36</t>
         </is>
       </c>
       <c r="N66" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/bare_cove_tuckers_swamp_commentary_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/architectural_plans_summary_v1.md</t>
         </is>
       </c>
     </row>
@@ -23002,7 +23142,7 @@
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>meeting_minutes_and_timeline_v1.md</t>
+          <t>architectural_plans_summary_v2.md</t>
         </is>
       </c>
       <c r="E67" s="15" t="inlineStr">
@@ -23011,16 +23151,16 @@
         </is>
       </c>
       <c r="F67" s="17" t="n">
-        <v>5578</v>
+        <v>9321</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>5.4 KB</t>
+          <t>9.1 KB</t>
         </is>
       </c>
       <c r="H67" s="15" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="I67" s="16" t="inlineStr">
@@ -23045,12 +23185,12 @@
       </c>
       <c r="M67" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14 08:39</t>
+          <t>2026-09-16 16:08</t>
         </is>
       </c>
       <c r="N67" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/meeting_minutes_and_timeline_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/architectural_plans_summary_v2.md</t>
         </is>
       </c>
     </row>
@@ -23072,7 +23212,7 @@
       </c>
       <c r="D68" s="20" t="inlineStr">
         <is>
-          <t>meeting_minutes_and_timeline_v2.md</t>
+          <t>bare_cove_tuckers_swamp_commentary_v1.md</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr">
@@ -23081,16 +23221,16 @@
         </is>
       </c>
       <c r="F68" s="21" t="n">
-        <v>15405</v>
+        <v>11075</v>
       </c>
       <c r="G68" s="22" t="inlineStr">
         <is>
-          <t>15.0 KB</t>
+          <t>10.8 KB</t>
         </is>
       </c>
       <c r="H68" s="19" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I68" s="20" t="inlineStr">
@@ -23115,12 +23255,12 @@
       </c>
       <c r="M68" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 09:25</t>
+          <t>2026-09-14 09:16</t>
         </is>
       </c>
       <c r="N68" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/meeting_minutes_and_timeline_v2.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/bare_cove_tuckers_swamp_commentary_v1.md</t>
         </is>
       </c>
     </row>
@@ -23142,7 +23282,7 @@
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>state_housing_and_40B_filings_v1.md</t>
+          <t>meeting_minutes_and_timeline_v1.md</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
@@ -23151,11 +23291,11 @@
         </is>
       </c>
       <c r="F69" s="17" t="n">
-        <v>7856</v>
+        <v>5578</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>7.7 KB</t>
+          <t>5.4 KB</t>
         </is>
       </c>
       <c r="H69" s="15" t="inlineStr">
@@ -23185,12 +23325,12 @@
       </c>
       <c r="M69" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14 09:16</t>
+          <t>2026-09-14 08:39</t>
         </is>
       </c>
       <c r="N69" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/state_housing_and_40B_filings_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/meeting_minutes_and_timeline_v1.md</t>
         </is>
       </c>
     </row>
@@ -23212,7 +23352,7 @@
       </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
-          <t>town_documents_and_legal_records_v1.md</t>
+          <t>meeting_minutes_and_timeline_v2.md</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr">
@@ -23221,16 +23361,16 @@
         </is>
       </c>
       <c r="F70" s="21" t="n">
-        <v>21860</v>
+        <v>15405</v>
       </c>
       <c r="G70" s="22" t="inlineStr">
         <is>
-          <t>21.3 KB</t>
+          <t>15.0 KB</t>
         </is>
       </c>
       <c r="H70" s="19" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="I70" s="20" t="inlineStr">
@@ -23255,12 +23395,12 @@
       </c>
       <c r="M70" s="19" t="inlineStr">
         <is>
-          <t>2026-09-17 06:59</t>
+          <t>2026-09-14 09:25</t>
         </is>
       </c>
       <c r="N70" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/town_documents_and_legal_records_v1.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/meeting_minutes_and_timeline_v2.md</t>
         </is>
       </c>
     </row>
@@ -23282,7 +23422,7 @@
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>town_documents_and_legal_records_v2.md</t>
+          <t>state_housing_and_40B_filings_v1.md</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
@@ -23291,16 +23431,16 @@
         </is>
       </c>
       <c r="F71" s="17" t="n">
-        <v>24370</v>
+        <v>7856</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>23.8 KB</t>
+          <t>7.7 KB</t>
         </is>
       </c>
       <c r="H71" s="15" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I71" s="16" t="inlineStr">
@@ -23325,12 +23465,12 @@
       </c>
       <c r="M71" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17</t>
+          <t>2026-09-14 09:16</t>
         </is>
       </c>
       <c r="N71" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/town_documents_and_legal_records_v2.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/state_housing_and_40B_filings_v1.md</t>
         </is>
       </c>
     </row>
@@ -23352,7 +23492,7 @@
       </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>town_documents_and_legal_records_v3.md</t>
+          <t>town_documents_and_legal_records_v1.md</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
@@ -23361,16 +23501,16 @@
         </is>
       </c>
       <c r="F72" s="21" t="n">
-        <v>24396</v>
+        <v>21860</v>
       </c>
       <c r="G72" s="22" t="inlineStr">
         <is>
-          <t>23.8 KB</t>
+          <t>21.3 KB</t>
         </is>
       </c>
       <c r="H72" s="19" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I72" s="20" t="inlineStr">
@@ -23395,12 +23535,12 @@
       </c>
       <c r="M72" s="19" t="inlineStr">
         <is>
-          <t>2026-09-16 16:47</t>
+          <t>2026-09-17 06:59</t>
         </is>
       </c>
       <c r="N72" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/companion_transcriptions/town_documents_and_legal_records_v3.md</t>
+          <t>agent_created_deliverables/companion_transcriptions/town_documents_and_legal_records_v1.md</t>
         </is>
       </c>
     </row>
@@ -23417,60 +23557,60 @@
       </c>
       <c r="C73" s="16" t="inlineStr">
         <is>
-          <t>Speech-to-Text Meeting Transcripts</t>
+          <t>Companion Markdown Transcriptions</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>2018-01-30_Selectmen_KfiJSICX-mo_whisper_transcript.txt</t>
+          <t>town_documents_and_legal_records_v2.md</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F73" s="17" t="n">
-        <v>130469</v>
+        <v>24370</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>127.4 KB</t>
+          <t>23.8 KB</t>
         </is>
       </c>
       <c r="H73" s="15" t="inlineStr">
         <is>
-          <t>Original Public Record</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
-          <t>OpenAI Whisper (Apple Silicon Metal GPU)</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>Open Meeting Deliberations</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K73" s="18" t="inlineStr">
         <is>
-          <t>Full verbatim speech-to-text transcript generated directly from municipal broadcast audio.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
         <is>
-          <t>Automated Verified Transcript</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M73" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15 17:35</t>
+          <t>2026-09-14 09:17</t>
         </is>
       </c>
       <c r="N73" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/meeting_transcripts/2018-01-30_Selectmen_KfiJSICX-mo_whisper_transcript.txt</t>
+          <t>agent_created_deliverables/companion_transcriptions/town_documents_and_legal_records_v2.md</t>
         </is>
       </c>
     </row>
@@ -23487,60 +23627,60 @@
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>Speech-to-Text Meeting Transcripts</t>
+          <t>Companion Markdown Transcriptions</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>2018-02-13_Selectmen_t4P0ZzzO0oY_whisper_transcript.txt</t>
+          <t>town_documents_and_legal_records_v3.md</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F74" s="21" t="n">
-        <v>81155</v>
+        <v>24396</v>
       </c>
       <c r="G74" s="22" t="inlineStr">
         <is>
-          <t>79.3 KB</t>
+          <t>23.8 KB</t>
         </is>
       </c>
       <c r="H74" s="19" t="inlineStr">
         <is>
-          <t>Original Public Record</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
-          <t>OpenAI Whisper (Apple Silicon Metal GPU)</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J74" s="20" t="inlineStr">
         <is>
-          <t>Open Meeting Deliberations</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K74" s="23" t="inlineStr">
         <is>
-          <t>Full verbatim speech-to-text transcript generated directly from municipal broadcast audio.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L74" s="19" t="inlineStr">
         <is>
-          <t>Automated Verified Transcript</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M74" s="19" t="inlineStr">
         <is>
-          <t>2026-09-15 17:35</t>
+          <t>2026-09-16 16:47</t>
         </is>
       </c>
       <c r="N74" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/meeting_transcripts/2018-02-13_Selectmen_t4P0ZzzO0oY_whisper_transcript.txt</t>
+          <t>agent_created_deliverables/companion_transcriptions/town_documents_and_legal_records_v3.md</t>
         </is>
       </c>
     </row>
@@ -23562,7 +23702,7 @@
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>2019-02-26_Selectmen_iSOkQlHX-5s_GeminiPro_transcript.txt</t>
+          <t>2018-01-30_Selectmen_KfiJSICX-mo_whisper_transcript.txt</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
@@ -23571,11 +23711,11 @@
         </is>
       </c>
       <c r="F75" s="17" t="n">
-        <v>75792</v>
+        <v>130469</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>74.0 KB</t>
+          <t>127.4 KB</t>
         </is>
       </c>
       <c r="H75" s="15" t="inlineStr">
@@ -23585,22 +23725,22 @@
       </c>
       <c r="I75" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>OpenAI Whisper (Apple Silicon Metal GPU)</t>
         </is>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>Open Meeting Deliberations</t>
         </is>
       </c>
       <c r="K75" s="18" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Full verbatim speech-to-text transcript generated directly from municipal broadcast audio.</t>
         </is>
       </c>
       <c r="L75" s="15" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Automated Verified Transcript</t>
         </is>
       </c>
       <c r="M75" s="15" t="inlineStr">
@@ -23610,7 +23750,7 @@
       </c>
       <c r="N75" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/meeting_transcripts/2019-02-26_Selectmen_iSOkQlHX-5s_GeminiPro_transcript.txt</t>
+          <t>agent_created_deliverables/meeting_transcripts/2018-01-30_Selectmen_KfiJSICX-mo_whisper_transcript.txt</t>
         </is>
       </c>
     </row>
@@ -23632,7 +23772,7 @@
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>2019-10-29_Selectmen_COFl6DmOWAo_whisper_transcript.txt</t>
+          <t>2018-02-13_Selectmen_t4P0ZzzO0oY_whisper_transcript.txt</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr">
@@ -23641,11 +23781,11 @@
         </is>
       </c>
       <c r="F76" s="21" t="n">
-        <v>133848</v>
+        <v>81155</v>
       </c>
       <c r="G76" s="22" t="inlineStr">
         <is>
-          <t>130.7 KB</t>
+          <t>79.3 KB</t>
         </is>
       </c>
       <c r="H76" s="19" t="inlineStr">
@@ -23680,7 +23820,7 @@
       </c>
       <c r="N76" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/meeting_transcripts/2019-10-29_Selectmen_COFl6DmOWAo_whisper_transcript.txt</t>
+          <t>agent_created_deliverables/meeting_transcripts/2018-02-13_Selectmen_t4P0ZzzO0oY_whisper_transcript.txt</t>
         </is>
       </c>
     </row>
@@ -23702,7 +23842,7 @@
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>2026-08-25_SelectBoard_LLJSH5V2ngg_whisper_transcript.txt</t>
+          <t>2019-02-26_Selectmen_iSOkQlHX-5s_GeminiPro_transcript.txt</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
@@ -23711,11 +23851,11 @@
         </is>
       </c>
       <c r="F77" s="17" t="n">
-        <v>112574</v>
+        <v>75792</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>109.9 KB</t>
+          <t>74.0 KB</t>
         </is>
       </c>
       <c r="H77" s="15" t="inlineStr">
@@ -23725,22 +23865,22 @@
       </c>
       <c r="I77" s="16" t="inlineStr">
         <is>
-          <t>OpenAI Whisper (Apple Silicon Metal GPU)</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>Open Meeting Deliberations</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K77" s="18" t="inlineStr">
         <is>
-          <t>Full verbatim speech-to-text transcript generated directly from municipal broadcast audio.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L77" s="15" t="inlineStr">
         <is>
-          <t>Automated Verified Transcript</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M77" s="15" t="inlineStr">
@@ -23750,7 +23890,7 @@
       </c>
       <c r="N77" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/meeting_transcripts/2026-08-25_SelectBoard_LLJSH5V2ngg_whisper_transcript.txt</t>
+          <t>agent_created_deliverables/meeting_transcripts/2019-02-26_Selectmen_iSOkQlHX-5s_GeminiPro_transcript.txt</t>
         </is>
       </c>
     </row>
@@ -23772,7 +23912,7 @@
       </c>
       <c r="D78" s="20" t="inlineStr">
         <is>
-          <t>README.txt</t>
+          <t>2019-10-29_Selectmen_COFl6DmOWAo_whisper_transcript.txt</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr">
@@ -23781,11 +23921,11 @@
         </is>
       </c>
       <c r="F78" s="21" t="n">
-        <v>1730</v>
+        <v>133848</v>
       </c>
       <c r="G78" s="22" t="inlineStr">
         <is>
-          <t>1.7 KB</t>
+          <t>130.7 KB</t>
         </is>
       </c>
       <c r="H78" s="19" t="inlineStr">
@@ -23795,22 +23935,22 @@
       </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>OpenAI Whisper (Apple Silicon Metal GPU)</t>
         </is>
       </c>
       <c r="J78" s="20" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>Open Meeting Deliberations</t>
         </is>
       </c>
       <c r="K78" s="23" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Full verbatim speech-to-text transcript generated directly from municipal broadcast audio.</t>
         </is>
       </c>
       <c r="L78" s="19" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Automated Verified Transcript</t>
         </is>
       </c>
       <c r="M78" s="19" t="inlineStr">
@@ -23820,7 +23960,7 @@
       </c>
       <c r="N78" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/meeting_transcripts/README.txt</t>
+          <t>agent_created_deliverables/meeting_transcripts/2019-10-29_Selectmen_COFl6DmOWAo_whisper_transcript.txt</t>
         </is>
       </c>
     </row>
@@ -23842,55 +23982,55 @@
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>video_recordings_index_v1.md</t>
+          <t>2026-08-25_SelectBoard_LLJSH5V2ngg_whisper_transcript.txt</t>
         </is>
       </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="F79" s="17" t="n">
-        <v>16881</v>
+        <v>112574</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>16.5 KB</t>
+          <t>109.9 KB</t>
         </is>
       </c>
       <c r="H79" s="15" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>Original Public Record</t>
         </is>
       </c>
       <c r="I79" s="16" t="inlineStr">
         <is>
-          <t>Town of Hingham / Housing Authority</t>
+          <t>OpenAI Whisper (Apple Silicon Metal GPU)</t>
         </is>
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>Massachusetts General Laws</t>
+          <t>Open Meeting Deliberations</t>
         </is>
       </c>
       <c r="K79" s="18" t="inlineStr">
         <is>
-          <t>Project documentation and archival record.</t>
+          <t>Full verbatim speech-to-text transcript generated directly from municipal broadcast audio.</t>
         </is>
       </c>
       <c r="L79" s="15" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Automated Verified Transcript</t>
         </is>
       </c>
       <c r="M79" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14 09:17</t>
+          <t>2026-09-15 17:35</t>
         </is>
       </c>
       <c r="N79" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/meeting_transcripts/video_recordings_index_v1.md</t>
+          <t>agent_created_deliverables/meeting_transcripts/2026-08-25_SelectBoard_LLJSH5V2ngg_whisper_transcript.txt</t>
         </is>
       </c>
     </row>
@@ -23907,60 +24047,60 @@
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>Quality Control Audits</t>
+          <t>Speech-to-Text Meeting Transcripts</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>qc_audit_legal_and_plans_v1.md</t>
+          <t>README.txt</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="F80" s="21" t="n">
-        <v>31728</v>
+        <v>1730</v>
       </c>
       <c r="G80" s="22" t="inlineStr">
         <is>
-          <t>31.0 KB</t>
+          <t>1.7 KB</t>
         </is>
       </c>
       <c r="H80" s="19" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>Original Public Record</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
-          <t>Meticulous Quality Control Auditor</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J80" s="20" t="inlineStr">
         <is>
-          <t>Records Integrity &amp; Geodetic Verification Standard</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K80" s="23" t="inlineStr">
         <is>
-          <t>Forensic quality control audit verifying document textual fidelity, wetland flag coordinates, and compendium completeness.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L80" s="19" t="inlineStr">
         <is>
-          <t>Audited &amp; Verified (100% Fidelity)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M80" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 11:39</t>
+          <t>2026-09-15 17:35</t>
         </is>
       </c>
       <c r="N80" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/quality_control_audits/qc_audit_legal_and_plans_v1.md</t>
+          <t>agent_created_deliverables/meeting_transcripts/README.txt</t>
         </is>
       </c>
     </row>
@@ -23977,12 +24117,12 @@
       </c>
       <c r="C81" s="16" t="inlineStr">
         <is>
-          <t>Quality Control Audits</t>
+          <t>Speech-to-Text Meeting Transcripts</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>qc_audit_media_and_compendium_integrity_v1.md</t>
+          <t>video_recordings_index_v1.md</t>
         </is>
       </c>
       <c r="E81" s="15" t="inlineStr">
@@ -23991,11 +24131,11 @@
         </is>
       </c>
       <c r="F81" s="17" t="n">
-        <v>29635</v>
+        <v>16881</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>28.9 KB</t>
+          <t>16.5 KB</t>
         </is>
       </c>
       <c r="H81" s="15" t="inlineStr">
@@ -24005,32 +24145,32 @@
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
-          <t>Meticulous Quality Control Auditor</t>
+          <t>Town of Hingham / Housing Authority</t>
         </is>
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>Records Integrity &amp; Geodetic Verification Standard</t>
+          <t>Massachusetts General Laws</t>
         </is>
       </c>
       <c r="K81" s="18" t="inlineStr">
         <is>
-          <t>Forensic quality control audit verifying document textual fidelity, wetland flag coordinates, and compendium completeness.</t>
+          <t>Project documentation and archival record.</t>
         </is>
       </c>
       <c r="L81" s="15" t="inlineStr">
         <is>
-          <t>Audited &amp; Verified (100% Fidelity)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M81" s="15" t="inlineStr">
         <is>
-          <t>2026-09-14 11:40</t>
+          <t>2026-09-14 09:17</t>
         </is>
       </c>
       <c r="N81" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/quality_control_audits/qc_audit_media_and_compendium_integrity_v1.md</t>
+          <t>agent_created_deliverables/meeting_transcripts/video_recordings_index_v1.md</t>
         </is>
       </c>
     </row>
@@ -24052,7 +24192,7 @@
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>qc_audit_meetings_and_videos_v1.md</t>
+          <t>qc_audit_legal_and_plans_v1.md</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr">
@@ -24061,11 +24201,11 @@
         </is>
       </c>
       <c r="F82" s="21" t="n">
-        <v>42842</v>
+        <v>31728</v>
       </c>
       <c r="G82" s="22" t="inlineStr">
         <is>
-          <t>41.8 KB</t>
+          <t>31.0 KB</t>
         </is>
       </c>
       <c r="H82" s="19" t="inlineStr">
@@ -24095,12 +24235,12 @@
       </c>
       <c r="M82" s="19" t="inlineStr">
         <is>
-          <t>2026-09-14 11:56</t>
+          <t>2026-09-14 11:39</t>
         </is>
       </c>
       <c r="N82" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/quality_control_audits/qc_audit_meetings_and_videos_v1.md</t>
+          <t>agent_created_deliverables/quality_control_audits/qc_audit_legal_and_plans_v1.md</t>
         </is>
       </c>
     </row>
@@ -24117,25 +24257,25 @@
       </c>
       <c r="C83" s="16" t="inlineStr">
         <is>
-          <t>Visual Infographics &amp; Timelines</t>
+          <t>Quality Control Audits</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Timeline_Infographic_9x16_v1.jpg</t>
+          <t>qc_audit_media_and_compendium_integrity_v1.md</t>
         </is>
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F83" s="17" t="n">
-        <v>656090</v>
+        <v>29635</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>640.7 KB</t>
+          <t>28.9 KB</t>
         </is>
       </c>
       <c r="H83" s="15" t="inlineStr">
@@ -24145,32 +24285,32 @@
       </c>
       <c r="I83" s="16" t="inlineStr">
         <is>
-          <t>AI Creative Design / Municipal Standards</t>
+          <t>Meticulous Quality Control Auditor</t>
         </is>
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>M.G.L. c. 121B, § 34; M.G.L. c. 30B, § 16</t>
+          <t>Records Integrity &amp; Geodetic Verification Standard</t>
         </is>
       </c>
       <c r="K83" s="18" t="inlineStr">
         <is>
-          <t>9:16 vertical infographic formatted in official Hingham Crimson (#891024) and Gold (#D97706) featuring exactly 3 bullets per milestone year and 99-year lease covenants.</t>
+          <t>Forensic quality control audit verifying document textual fidelity, wetland flag coordinates, and compendium completeness.</t>
         </is>
       </c>
       <c r="L83" s="15" t="inlineStr">
         <is>
-          <t>Visual Deliverable (Verified)</t>
+          <t>Audited &amp; Verified (100% Fidelity)</t>
         </is>
       </c>
       <c r="M83" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 09:58</t>
+          <t>2026-09-14 11:40</t>
         </is>
       </c>
       <c r="N83" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_9x16_v1.jpg</t>
+          <t>agent_created_deliverables/quality_control_audits/qc_audit_media_and_compendium_integrity_v1.md</t>
         </is>
       </c>
     </row>
@@ -24187,25 +24327,25 @@
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>Visual Infographics &amp; Timelines</t>
+          <t>Quality Control Audits</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Timeline_Infographic_9x16_v1.pdf</t>
+          <t>qc_audit_meetings_and_videos_v1.md</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="F84" s="21" t="n">
-        <v>657143</v>
+        <v>42842</v>
       </c>
       <c r="G84" s="22" t="inlineStr">
         <is>
-          <t>641.7 KB</t>
+          <t>41.8 KB</t>
         </is>
       </c>
       <c r="H84" s="19" t="inlineStr">
@@ -24215,32 +24355,32 @@
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
-          <t>AI Creative Design / Municipal Standards</t>
+          <t>Meticulous Quality Control Auditor</t>
         </is>
       </c>
       <c r="J84" s="20" t="inlineStr">
         <is>
-          <t>M.G.L. c. 121B, § 34; M.G.L. c. 30B, § 16</t>
+          <t>Records Integrity &amp; Geodetic Verification Standard</t>
         </is>
       </c>
       <c r="K84" s="23" t="inlineStr">
         <is>
-          <t>9:16 vertical infographic formatted in official Hingham Crimson (#891024) and Gold (#D97706) featuring exactly 3 bullets per milestone year and 99-year lease covenants.</t>
+          <t>Forensic quality control audit verifying document textual fidelity, wetland flag coordinates, and compendium completeness.</t>
         </is>
       </c>
       <c r="L84" s="19" t="inlineStr">
         <is>
-          <t>Visual Deliverable (Verified)</t>
+          <t>Audited &amp; Verified (100% Fidelity)</t>
         </is>
       </c>
       <c r="M84" s="19" t="inlineStr">
         <is>
-          <t>2026-09-16 09:58</t>
+          <t>2026-09-14 11:56</t>
         </is>
       </c>
       <c r="N84" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_9x16_v1.pdf</t>
+          <t>agent_created_deliverables/quality_control_audits/qc_audit_meetings_and_videos_v1.md</t>
         </is>
       </c>
     </row>
@@ -24262,7 +24402,7 @@
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v1.jpg</t>
+          <t>100_Beal_Street_Timeline_Infographic_9x16_v1.jpg</t>
         </is>
       </c>
       <c r="E85" s="15" t="inlineStr">
@@ -24271,11 +24411,11 @@
         </is>
       </c>
       <c r="F85" s="17" t="n">
-        <v>585609</v>
+        <v>656090</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>571.9 KB</t>
+          <t>640.7 KB</t>
         </is>
       </c>
       <c r="H85" s="15" t="inlineStr">
@@ -24305,12 +24445,12 @@
       </c>
       <c r="M85" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 09:59</t>
+          <t>2026-09-16 09:58</t>
         </is>
       </c>
       <c r="N85" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v1.jpg</t>
+          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_9x16_v1.jpg</t>
         </is>
       </c>
     </row>
@@ -24332,25 +24472,25 @@
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.jpg</t>
+          <t>100_Beal_Street_Timeline_Infographic_9x16_v1.pdf</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="F86" s="21" t="n">
-        <v>690206</v>
+        <v>657143</v>
       </c>
       <c r="G86" s="22" t="inlineStr">
         <is>
-          <t>674.0 KB</t>
+          <t>641.7 KB</t>
         </is>
       </c>
       <c r="H86" s="19" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
@@ -24375,12 +24515,12 @@
       </c>
       <c r="M86" s="19" t="inlineStr">
         <is>
-          <t>2026-09-16 10:04</t>
+          <t>2026-09-16 09:58</t>
         </is>
       </c>
       <c r="N86" s="20" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.jpg</t>
+          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_9x16_v1.pdf</t>
         </is>
       </c>
     </row>
@@ -24402,25 +24542,25 @@
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.pdf</t>
+          <t>100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v1.jpg</t>
         </is>
       </c>
       <c r="E87" s="15" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="F87" s="17" t="n">
-        <v>327716</v>
+        <v>585609</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>320.0 KB</t>
+          <t>571.9 KB</t>
         </is>
       </c>
       <c r="H87" s="15" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="I87" s="16" t="inlineStr">
@@ -24445,12 +24585,12 @@
       </c>
       <c r="M87" s="15" t="inlineStr">
         <is>
-          <t>2026-09-16 10:04</t>
+          <t>2026-09-16 09:59</t>
         </is>
       </c>
       <c r="N87" s="16" t="inlineStr">
         <is>
-          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.pdf</t>
+          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v1.jpg</t>
         </is>
       </c>
     </row>
@@ -24472,60 +24612,200 @@
       </c>
       <c r="D88" s="20" t="inlineStr">
         <is>
+          <t>100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.jpg</t>
+        </is>
+      </c>
+      <c r="E88" s="19" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="F88" s="21" t="n">
+        <v>690206</v>
+      </c>
+      <c r="G88" s="22" t="inlineStr">
+        <is>
+          <t>674.0 KB</t>
+        </is>
+      </c>
+      <c r="H88" s="19" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="I88" s="20" t="inlineStr">
+        <is>
+          <t>AI Creative Design / Municipal Standards</t>
+        </is>
+      </c>
+      <c r="J88" s="20" t="inlineStr">
+        <is>
+          <t>M.G.L. c. 121B, § 34; M.G.L. c. 30B, § 16</t>
+        </is>
+      </c>
+      <c r="K88" s="23" t="inlineStr">
+        <is>
+          <t>9:16 vertical infographic formatted in official Hingham Crimson (#891024) and Gold (#D97706) featuring exactly 3 bullets per milestone year and 99-year lease covenants.</t>
+        </is>
+      </c>
+      <c r="L88" s="19" t="inlineStr">
+        <is>
+          <t>Visual Deliverable (Verified)</t>
+        </is>
+      </c>
+      <c r="M88" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:04</t>
+        </is>
+      </c>
+      <c r="N88" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>FL-171</t>
+        </is>
+      </c>
+      <c r="B89" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C89" s="16" t="inlineStr">
+        <is>
+          <t>Visual Infographics &amp; Timelines</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="inlineStr">
+        <is>
+          <t>100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.pdf</t>
+        </is>
+      </c>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F89" s="17" t="n">
+        <v>327716</v>
+      </c>
+      <c r="G89" s="12" t="inlineStr">
+        <is>
+          <t>320.0 KB</t>
+        </is>
+      </c>
+      <c r="H89" s="15" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>AI Creative Design / Municipal Standards</t>
+        </is>
+      </c>
+      <c r="J89" s="16" t="inlineStr">
+        <is>
+          <t>M.G.L. c. 121B, § 34; M.G.L. c. 30B, § 16</t>
+        </is>
+      </c>
+      <c r="K89" s="18" t="inlineStr">
+        <is>
+          <t>9:16 vertical infographic formatted in official Hingham Crimson (#891024) and Gold (#D97706) featuring exactly 3 bullets per milestone year and 99-year lease covenants.</t>
+        </is>
+      </c>
+      <c r="L89" s="15" t="inlineStr">
+        <is>
+          <t>Visual Deliverable (Verified)</t>
+        </is>
+      </c>
+      <c r="M89" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-16 10:04</t>
+        </is>
+      </c>
+      <c r="N89" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="19" t="inlineStr">
+        <is>
+          <t>FL-172</t>
+        </is>
+      </c>
+      <c r="B90" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C90" s="20" t="inlineStr">
+        <is>
+          <t>Visual Infographics &amp; Timelines</t>
+        </is>
+      </c>
+      <c r="D90" s="20" t="inlineStr">
+        <is>
           <t>100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.png</t>
         </is>
       </c>
-      <c r="E88" s="19" t="inlineStr">
+      <c r="E90" s="19" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
       </c>
-      <c r="F88" s="21" t="n">
+      <c r="F90" s="21" t="n">
         <v>799187</v>
       </c>
-      <c r="G88" s="22" t="inlineStr">
+      <c r="G90" s="22" t="inlineStr">
         <is>
           <t>780.5 KB</t>
         </is>
       </c>
-      <c r="H88" s="19" t="inlineStr">
+      <c r="H90" s="19" t="inlineStr">
         <is>
           <t>v2</t>
         </is>
       </c>
-      <c r="I88" s="20" t="inlineStr">
+      <c r="I90" s="20" t="inlineStr">
         <is>
           <t>AI Creative Design / Municipal Standards</t>
         </is>
       </c>
-      <c r="J88" s="20" t="inlineStr">
+      <c r="J90" s="20" t="inlineStr">
         <is>
           <t>M.G.L. c. 121B, § 34; M.G.L. c. 30B, § 16</t>
         </is>
       </c>
-      <c r="K88" s="23" t="inlineStr">
+      <c r="K90" s="23" t="inlineStr">
         <is>
           <t>9:16 vertical infographic formatted in official Hingham Crimson (#891024) and Gold (#D97706) featuring exactly 3 bullets per milestone year and 99-year lease covenants.</t>
         </is>
       </c>
-      <c r="L88" s="19" t="inlineStr">
+      <c r="L90" s="19" t="inlineStr">
         <is>
           <t>Visual Deliverable (Verified)</t>
         </is>
       </c>
-      <c r="M88" s="19" t="inlineStr">
+      <c r="M90" s="19" t="inlineStr">
         <is>
           <t>2026-09-16 10:04</t>
         </is>
       </c>
-      <c r="N88" s="20" t="inlineStr">
+      <c r="N90" s="20" t="inlineStr">
         <is>
           <t>agent_created_deliverables/visual_assets/100_Beal_Street_Timeline_Infographic_Hingham_Colors_9x16_v2.png</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N88"/>
+  <autoFilter ref="A4:N90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24565,7 +24845,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: September 17, 2026 • Total Records: 15 • Zero Web Scrapes</t>
+          <t>Generated: September 18, 2026 • Total Records: 15 • Zero Web Scrapes</t>
         </is>
       </c>
     </row>

--- a/100_Beal_Street_Master_File_Inventory_v1.xlsx
+++ b/100_Beal_Street_Master_File_Inventory_v1.xlsx
@@ -625,7 +625,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Report Date: September 20, 2026  •  Location: Hingham, Plymouth County, MA  •  Zero Web Scrapes</t>
+          <t>Report Date: September 21, 2026  •  Location: Hingham, Plymouth County, MA  •  Zero Web Scrapes</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: September 20, 2026 • Total Records: 311 • Zero Web Scrapes</t>
+          <t>Generated: September 21, 2026 • Total Records: 311 • Zero Web Scrapes</t>
         </is>
       </c>
     </row>
@@ -23450,7 +23450,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: September 20, 2026 • Total Records: 71 • Zero Web Scrapes</t>
+          <t>Generated: September 21, 2026 • Total Records: 71 • Zero Web Scrapes</t>
         </is>
       </c>
     </row>
@@ -28537,7 +28537,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: September 20, 2026 • Total Records: 223 • Zero Web Scrapes</t>
+          <t>Generated: September 21, 2026 • Total Records: 223 • Zero Web Scrapes</t>
         </is>
       </c>
     </row>
@@ -44264,7 +44264,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: September 20, 2026 • Total Records: 16 • Zero Web Scrapes</t>
+          <t>Generated: September 21, 2026 • Total Records: 16 • Zero Web Scrapes</t>
         </is>
       </c>
     </row>

--- a/100_Beal_Street_Master_File_Inventory_v1.xlsx
+++ b/100_Beal_Street_Master_File_Inventory_v1.xlsx
@@ -14,9 +14,9 @@
     <sheet name="Repository Index &amp; Governance" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Files Master Catalog'!$A$4:$N$319</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Files Master Catalog'!$A$4:$N$339</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Downloaded Sources'!$A$4:$N$75</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Agent Deliverables'!$A$4:$N$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Agent Deliverables'!$A$4:$N$251</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Repository Index &amp; Governance'!$A$4:$N$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I44"/>
+  <dimension ref="B2:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -633,7 +633,7 @@
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total Files Cataloged
-315</t>
+335</t>
         </is>
       </c>
       <c r="C6" s="5" t="n"/>
@@ -647,7 +647,7 @@
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Agent Deliverables
-227</t>
+247</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>862.8 MB (904,748,272 bytes across 315 active verified files)</t>
+          <t>901.8 MB (945,600,477 bytes across 335 active verified files)</t>
         </is>
       </c>
       <c r="D25" s="9" t="n"/>
@@ -1013,20 +1013,20 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Companion Markdown Transcriptions</t>
+          <t>Agent Synthesized Work</t>
         </is>
       </c>
       <c r="D30" s="12" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>2.7 MB</t>
+          <t>39.0 MB</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MD, PDF, ZIP</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
@@ -1045,20 +1045,20 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Detailed Timeline &amp; Plain-English TLDR</t>
+          <t>Companion Markdown Transcriptions</t>
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>154.7 KB</t>
+          <t>2.7 MB</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>MD, PDF</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
@@ -1077,15 +1077,15 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Executive Reports &amp; Briefings</t>
+          <t>Detailed Timeline &amp; Plain-English TLDR</t>
         </is>
       </c>
       <c r="D32" s="12" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>1.2 MB</t>
+          <t>154.7 KB</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -1109,15 +1109,15 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Master Chronological Compendiums</t>
+          <t>Executive Reports &amp; Briefings</t>
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>104.5 MB</t>
+          <t>1.2 MB</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Quality Control Audits</t>
+          <t>Master Chronological Compendiums</t>
         </is>
       </c>
       <c r="D34" s="12" t="n">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>101.8 KB</t>
+          <t>104.5 MB</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MD, PDF</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -1173,20 +1173,20 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Speech-to-Text Meeting Transcripts</t>
+          <t>Quality Control Audits</t>
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>539.5 KB</t>
+          <t>101.8 KB</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>MD, TXT</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -1205,20 +1205,20 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Video Presentations &amp; Narration Decks</t>
+          <t>Speech-to-Text Meeting Transcripts</t>
         </is>
       </c>
       <c r="D36" s="12" t="n">
-        <v>134</v>
+        <v>7</v>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>358.6 MB</t>
+          <t>539.5 KB</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>HTML, JPG, MD, MP4, PDF, PNG, PPTX, TXT, VTT, WAV</t>
+          <t>MD, TXT</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -1237,20 +1237,20 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Visual Infographics &amp; Timelines</t>
+          <t>Video Presentations &amp; Narration Decks</t>
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>3.5 MB</t>
+          <t>358.6 MB</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>JPG, PDF, PNG</t>
+          <t>HTML, JPG, MD, MP4, PDF, PNG, PPTX, TXT, VTT, WAV</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -1264,30 +1264,30 @@
     <row r="38">
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Downloaded Primary Source</t>
+          <t>Agent-Created Deliverable</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Architectural &amp; Survey Plans</t>
+          <t>Visual Infographics &amp; Timelines</t>
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>67.0 MB</t>
+          <t>3.5 MB</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>JPG, PDF, WEBP</t>
+          <t>JPG, PDF, PNG</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Authentic primary municipal record</t>
+          <t>Synthesized briefing / report</t>
         </is>
       </c>
       <c r="H38" s="9" t="n"/>
@@ -1301,20 +1301,20 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Board Agendas &amp; Minutes (PDF)</t>
+          <t>Architectural &amp; Survey Plans</t>
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>3.1 MB</t>
+          <t>67.0 MB</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>JPG, PDF, WEBP</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -1333,20 +1333,20 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Meeting Broadcast Audio (MP3)</t>
+          <t>Board Agendas &amp; Minutes (PDF)</t>
         </is>
       </c>
       <c r="D40" s="12" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>275.0 MB</t>
+          <t>3.1 MB</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>MP3</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -1365,20 +1365,20 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Municipal Documents, Warrants &amp; Deeds</t>
+          <t>Meeting Broadcast Audio (MP3)</t>
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>43.9 MB</t>
+          <t>275.0 MB</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>MP3</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -1397,20 +1397,20 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Registry Scans &amp; Recorded ORAD</t>
+          <t>Municipal Documents, Warrants &amp; Deeds</t>
         </is>
       </c>
       <c r="D42" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>2.0 MB</t>
+          <t>43.9 MB</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>PDF, PNG, TXT</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
@@ -1424,30 +1424,30 @@
     <row r="43">
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Master Compendium &amp; Archive</t>
+          <t>Downloaded Primary Source</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Authoritative Single-File Code &amp; Document Compendium</t>
+          <t>Registry Scans &amp; Recorded ORAD</t>
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>511.4 KB</t>
+          <t>2.0 MB</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>PDF, PNG, TXT</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>Repository catalog</t>
+          <t>Authentic primary municipal record</t>
         </is>
       </c>
       <c r="H43" s="9" t="n"/>
@@ -1456,25 +1456,25 @@
     <row r="44">
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Repository Documentation &amp; Index</t>
+          <t>Master Compendium &amp; Archive</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Repository Index &amp; Governance</t>
+          <t>Authoritative Single-File Code &amp; Document Compendium</t>
         </is>
       </c>
       <c r="D44" s="12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>205.2 KB</t>
+          <t>511.4 KB</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>JSON, MD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
@@ -1485,8 +1485,40 @@
       <c r="H44" s="9" t="n"/>
       <c r="I44" s="10" t="n"/>
     </row>
+    <row r="45">
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Repository Documentation &amp; Index</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Repository Index &amp; Governance</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>205.2 KB</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>JSON, MD</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>Repository catalog</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="37">
     <mergeCell ref="G38:I38"/>
     <mergeCell ref="C23:I23"/>
     <mergeCell ref="C17:I17"/>
@@ -1498,6 +1530,7 @@
     <mergeCell ref="G33:I33"/>
     <mergeCell ref="C13:I13"/>
     <mergeCell ref="C18:I18"/>
+    <mergeCell ref="G45:I45"/>
     <mergeCell ref="G35:I35"/>
     <mergeCell ref="C24:I24"/>
     <mergeCell ref="C15:I15"/>
@@ -1534,7 +1567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N319"/>
+  <dimension ref="A1:N339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1563,7 +1596,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: September 22, 2026 • Total Records: 315 • Zero Web Scrapes</t>
+          <t>Generated: September 22, 2026 • Total Records: 335 • Zero Web Scrapes</t>
         </is>
       </c>
     </row>
@@ -23689,8 +23722,1408 @@
         </is>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" s="19" t="inlineStr">
+        <is>
+          <t>FL-316</t>
+        </is>
+      </c>
+      <c r="B320" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C320" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D320" s="20" t="inlineStr">
+        <is>
+          <t>100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1.zip</t>
+        </is>
+      </c>
+      <c r="E320" s="19" t="inlineStr">
+        <is>
+          <t>ZIP</t>
+        </is>
+      </c>
+      <c r="F320" s="21" t="n">
+        <v>19847898</v>
+      </c>
+      <c r="G320" s="22" t="inlineStr">
+        <is>
+          <t>18.9 MB</t>
+        </is>
+      </c>
+      <c r="H320" s="19" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I320" s="20" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J320" s="20" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K320" s="23" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L320" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M320" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:14</t>
+        </is>
+      </c>
+      <c r="N320" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="15" t="inlineStr">
+        <is>
+          <t>FL-317</t>
+        </is>
+      </c>
+      <c r="B321" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C321" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D321" s="16" t="inlineStr">
+        <is>
+          <t>README_PACKAGE_v1.md</t>
+        </is>
+      </c>
+      <c r="E321" s="15" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="F321" s="17" t="n">
+        <v>5931</v>
+      </c>
+      <c r="G321" s="12" t="inlineStr">
+        <is>
+          <t>5.8 KB</t>
+        </is>
+      </c>
+      <c r="H321" s="15" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I321" s="16" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J321" s="16" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K321" s="18" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L321" s="15" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M321" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:14</t>
+        </is>
+      </c>
+      <c r="N321" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/README_PACKAGE_v1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="19" t="inlineStr">
+        <is>
+          <t>FL-318</t>
+        </is>
+      </c>
+      <c r="B322" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C322" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D322" s="20" t="inlineStr">
+        <is>
+          <t>01_100_Beal_Street_Verifiable_Facts_and_Human_Document_v1.md</t>
+        </is>
+      </c>
+      <c r="E322" s="19" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="F322" s="21" t="n">
+        <v>22221</v>
+      </c>
+      <c r="G322" s="22" t="inlineStr">
+        <is>
+          <t>21.7 KB</t>
+        </is>
+      </c>
+      <c r="H322" s="19" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I322" s="20" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J322" s="20" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K322" s="23" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L322" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M322" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:10</t>
+        </is>
+      </c>
+      <c r="N322" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/01_100_Beal_Street_Verifiable_Facts_and_Human_Document_v1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="15" t="inlineStr">
+        <is>
+          <t>FL-319</t>
+        </is>
+      </c>
+      <c r="B323" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C323" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D323" s="16" t="inlineStr">
+        <is>
+          <t>01_100_Beal_Street_Verifiable_Facts_and_Human_Document_v1.pdf</t>
+        </is>
+      </c>
+      <c r="E323" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F323" s="17" t="n">
+        <v>103490</v>
+      </c>
+      <c r="G323" s="12" t="inlineStr">
+        <is>
+          <t>101.1 KB</t>
+        </is>
+      </c>
+      <c r="H323" s="15" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I323" s="16" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J323" s="16" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K323" s="18" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L323" s="15" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M323" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:10</t>
+        </is>
+      </c>
+      <c r="N323" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/01_100_Beal_Street_Verifiable_Facts_and_Human_Document_v1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="19" t="inlineStr">
+        <is>
+          <t>FL-320</t>
+        </is>
+      </c>
+      <c r="B324" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C324" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D324" s="20" t="inlineStr">
+        <is>
+          <t>02_100_Beal_Street_Records_Verification_Checklist_and_Audit_v1.md</t>
+        </is>
+      </c>
+      <c r="E324" s="19" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="F324" s="21" t="n">
+        <v>28047</v>
+      </c>
+      <c r="G324" s="22" t="inlineStr">
+        <is>
+          <t>27.4 KB</t>
+        </is>
+      </c>
+      <c r="H324" s="19" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I324" s="20" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J324" s="20" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K324" s="23" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L324" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M324" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:06</t>
+        </is>
+      </c>
+      <c r="N324" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/02_100_Beal_Street_Records_Verification_Checklist_and_Audit_v1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="15" t="inlineStr">
+        <is>
+          <t>FL-321</t>
+        </is>
+      </c>
+      <c r="B325" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C325" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D325" s="16" t="inlineStr">
+        <is>
+          <t>02_100_Beal_Street_Records_Verification_Checklist_and_Audit_v1.pdf</t>
+        </is>
+      </c>
+      <c r="E325" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F325" s="17" t="n">
+        <v>132623</v>
+      </c>
+      <c r="G325" s="12" t="inlineStr">
+        <is>
+          <t>129.5 KB</t>
+        </is>
+      </c>
+      <c r="H325" s="15" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I325" s="16" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J325" s="16" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K325" s="18" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L325" s="15" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M325" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:08</t>
+        </is>
+      </c>
+      <c r="N325" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/02_100_Beal_Street_Records_Verification_Checklist_and_Audit_v1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="19" t="inlineStr">
+        <is>
+          <t>FL-322</t>
+        </is>
+      </c>
+      <c r="B326" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C326" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D326" s="20" t="inlineStr">
+        <is>
+          <t>03_100_Beal_Street_The_True_Story_and_Evidence_v1.md</t>
+        </is>
+      </c>
+      <c r="E326" s="19" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="F326" s="21" t="n">
+        <v>12031</v>
+      </c>
+      <c r="G326" s="22" t="inlineStr">
+        <is>
+          <t>11.7 KB</t>
+        </is>
+      </c>
+      <c r="H326" s="19" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I326" s="20" t="inlineStr">
+        <is>
+          <t>Primary Municipal Records &amp; Educational Architecture</t>
+        </is>
+      </c>
+      <c r="J326" s="20" t="inlineStr">
+        <is>
+          <t>M.G.L. c. 121B; M.G.L. c. 184A; M.G.L. c. 44, § 7; Plymouth Registry Instruments</t>
+        </is>
+      </c>
+      <c r="K326" s="23" t="inlineStr">
+        <is>
+          <t>Dedicated 2-page educational guide and evidence ledger for family and community members. Page 1 provides a 1-page unspun narrative essay; Page 2 provides the companion Works Cited mapping every point to primary documents with repository file names.</t>
+        </is>
+      </c>
+      <c r="L326" s="19" t="inlineStr">
+        <is>
+          <t>Community Educational Guide &amp; Evidence Ledger (Verified)</t>
+        </is>
+      </c>
+      <c r="M326" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:27</t>
+        </is>
+      </c>
+      <c r="N326" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/03_100_Beal_Street_The_True_Story_and_Evidence_v1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="15" t="inlineStr">
+        <is>
+          <t>FL-323</t>
+        </is>
+      </c>
+      <c r="B327" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C327" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D327" s="16" t="inlineStr">
+        <is>
+          <t>03_100_Beal_Street_The_True_Story_and_Evidence_v1.pdf</t>
+        </is>
+      </c>
+      <c r="E327" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F327" s="17" t="n">
+        <v>74343</v>
+      </c>
+      <c r="G327" s="12" t="inlineStr">
+        <is>
+          <t>72.6 KB</t>
+        </is>
+      </c>
+      <c r="H327" s="15" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I327" s="16" t="inlineStr">
+        <is>
+          <t>Primary Municipal Records &amp; Educational Architecture</t>
+        </is>
+      </c>
+      <c r="J327" s="16" t="inlineStr">
+        <is>
+          <t>M.G.L. c. 121B; M.G.L. c. 184A; M.G.L. c. 44, § 7; Plymouth Registry Instruments</t>
+        </is>
+      </c>
+      <c r="K327" s="18" t="inlineStr">
+        <is>
+          <t>Dedicated 2-page educational guide and evidence ledger for family and community members. Page 1 provides a 1-page unspun narrative essay; Page 2 provides the companion Works Cited mapping every point to primary documents with repository file names.</t>
+        </is>
+      </c>
+      <c r="L327" s="15" t="inlineStr">
+        <is>
+          <t>Community Educational Guide &amp; Evidence Ledger (Verified)</t>
+        </is>
+      </c>
+      <c r="M327" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:27</t>
+        </is>
+      </c>
+      <c r="N327" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/03_100_Beal_Street_The_True_Story_and_Evidence_v1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="19" t="inlineStr">
+        <is>
+          <t>FL-324</t>
+        </is>
+      </c>
+      <c r="B328" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C328" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D328" s="20" t="inlineStr">
+        <is>
+          <t>04_100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.md</t>
+        </is>
+      </c>
+      <c r="E328" s="19" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="F328" s="21" t="n">
+        <v>31676</v>
+      </c>
+      <c r="G328" s="22" t="inlineStr">
+        <is>
+          <t>30.9 KB</t>
+        </is>
+      </c>
+      <c r="H328" s="19" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="I328" s="20" t="inlineStr">
+        <is>
+          <t>Primary Municipal Records / Mass. Registry of Deeds</t>
+        </is>
+      </c>
+      <c r="J328" s="20" t="inlineStr">
+        <is>
+          <t>Historical M.G.L. c. 184A, § 3; M.G.L. c. 184, § 23; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
+        </is>
+      </c>
+      <c r="K328" s="23" t="inlineStr">
+        <is>
+          <t>Preliminary primary-source research chronology and record index; strictly neutral factual reporting; segregates verified facts, factual inferences, and open legal questions; includes missing documents inventory and disclaimer. Not a title opinion.</t>
+        </is>
+      </c>
+      <c r="L328" s="19" t="inlineStr">
+        <is>
+          <t>Neutral Primary Source Research Index &amp; Inventory (Verified)</t>
+        </is>
+      </c>
+      <c r="M328" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:44</t>
+        </is>
+      </c>
+      <c r="N328" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/04_100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="15" t="inlineStr">
+        <is>
+          <t>FL-325</t>
+        </is>
+      </c>
+      <c r="B329" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C329" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D329" s="16" t="inlineStr">
+        <is>
+          <t>04_100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.pdf</t>
+        </is>
+      </c>
+      <c r="E329" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F329" s="17" t="n">
+        <v>119536</v>
+      </c>
+      <c r="G329" s="12" t="inlineStr">
+        <is>
+          <t>116.7 KB</t>
+        </is>
+      </c>
+      <c r="H329" s="15" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="I329" s="16" t="inlineStr">
+        <is>
+          <t>Primary Municipal Records / Mass. Registry of Deeds</t>
+        </is>
+      </c>
+      <c r="J329" s="16" t="inlineStr">
+        <is>
+          <t>Historical M.G.L. c. 184A, § 3; M.G.L. c. 184, § 23; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
+        </is>
+      </c>
+      <c r="K329" s="18" t="inlineStr">
+        <is>
+          <t>Preliminary primary-source research chronology and record index; strictly neutral factual reporting; segregates verified facts, factual inferences, and open legal questions; includes missing documents inventory and disclaimer. Not a title opinion.</t>
+        </is>
+      </c>
+      <c r="L329" s="15" t="inlineStr">
+        <is>
+          <t>Neutral Primary Source Research Index &amp; Inventory (Verified)</t>
+        </is>
+      </c>
+      <c r="M329" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:44</t>
+        </is>
+      </c>
+      <c r="N329" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/04_100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="19" t="inlineStr">
+        <is>
+          <t>FL-326</t>
+        </is>
+      </c>
+      <c r="B330" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C330" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D330" s="20" t="inlineStr">
+        <is>
+          <t>Exhibit_01_1989_Fee_Deed_and_ZBA_Decision_Bk09097_Pg158.pdf</t>
+        </is>
+      </c>
+      <c r="E330" s="19" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F330" s="21" t="n">
+        <v>228302</v>
+      </c>
+      <c r="G330" s="22" t="inlineStr">
+        <is>
+          <t>223.0 KB</t>
+        </is>
+      </c>
+      <c r="H330" s="19" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I330" s="20" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J330" s="20" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K330" s="23" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L330" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M330" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:24</t>
+        </is>
+      </c>
+      <c r="N330" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_01_1989_Fee_Deed_and_ZBA_Decision_Bk09097_Pg158.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="15" t="inlineStr">
+        <is>
+          <t>FL-327</t>
+        </is>
+      </c>
+      <c r="B331" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C331" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D331" s="16" t="inlineStr">
+        <is>
+          <t>Exhibit_02_2001_Gale_Subdivision_Plan_and_2024_ALTA_Survey.pdf</t>
+        </is>
+      </c>
+      <c r="E331" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F331" s="17" t="n">
+        <v>2390635</v>
+      </c>
+      <c r="G331" s="12" t="inlineStr">
+        <is>
+          <t>2.3 MB</t>
+        </is>
+      </c>
+      <c r="H331" s="15" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I331" s="16" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J331" s="16" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K331" s="18" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L331" s="15" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M331" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:24</t>
+        </is>
+      </c>
+      <c r="N331" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_02_2001_Gale_Subdivision_Plan_and_2024_ALTA_Survey.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="19" t="inlineStr">
+        <is>
+          <t>FL-328</t>
+        </is>
+      </c>
+      <c r="B332" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C332" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D332" s="20" t="inlineStr">
+        <is>
+          <t>Exhibit_03_2006_Town_Meeting_Article_38_Certified_Vote.pdf</t>
+        </is>
+      </c>
+      <c r="E332" s="19" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F332" s="21" t="n">
+        <v>217985</v>
+      </c>
+      <c r="G332" s="22" t="inlineStr">
+        <is>
+          <t>212.9 KB</t>
+        </is>
+      </c>
+      <c r="H332" s="19" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I332" s="20" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J332" s="20" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K332" s="23" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L332" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M332" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:24</t>
+        </is>
+      </c>
+      <c r="N332" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_03_2006_Town_Meeting_Article_38_Certified_Vote.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="15" t="inlineStr">
+        <is>
+          <t>FL-329</t>
+        </is>
+      </c>
+      <c r="B333" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C333" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D333" s="16" t="inlineStr">
+        <is>
+          <t>Exhibit_04_2019_Select_Board_Executive_Session_Minutes_Lawsuit_Vote.pdf</t>
+        </is>
+      </c>
+      <c r="E333" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F333" s="17" t="n">
+        <v>50677</v>
+      </c>
+      <c r="G333" s="12" t="inlineStr">
+        <is>
+          <t>49.5 KB</t>
+        </is>
+      </c>
+      <c r="H333" s="15" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I333" s="16" t="inlineStr">
+        <is>
+          <t>Hingham Board of Selectmen (Healey, Power, Johnson)</t>
+        </is>
+      </c>
+      <c r="J333" s="16" t="inlineStr">
+        <is>
+          <t>M.G.L. c. 30A, § 21(a)(3) (Executive Session Litigation)</t>
+        </is>
+      </c>
+      <c r="K333" s="18" t="inlineStr">
+        <is>
+          <t>Executive Session minutes of Feb 26, 2019 recording 3-0 vote to file litigation against HHA to enforce 2001 MOU 9 days before 30-yr reverter expiration.</t>
+        </is>
+      </c>
+      <c r="L333" s="15" t="inlineStr">
+        <is>
+          <t>Official Municipal Minutes (Verified)</t>
+        </is>
+      </c>
+      <c r="M333" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-14 08:38</t>
+        </is>
+      </c>
+      <c r="N333" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_04_2019_Select_Board_Executive_Session_Minutes_Lawsuit_Vote.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="19" t="inlineStr">
+        <is>
+          <t>FL-330</t>
+        </is>
+      </c>
+      <c r="B334" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C334" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D334" s="20" t="inlineStr">
+        <is>
+          <t>Exhibit_05_2019_HHA_Minutes_School_Tract_II_DHCD_Intervention.pdf</t>
+        </is>
+      </c>
+      <c r="E334" s="19" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F334" s="21" t="n">
+        <v>41327</v>
+      </c>
+      <c r="G334" s="22" t="inlineStr">
+        <is>
+          <t>40.4 KB</t>
+        </is>
+      </c>
+      <c r="H334" s="19" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I334" s="20" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J334" s="20" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K334" s="23" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L334" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M334" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:13</t>
+        </is>
+      </c>
+      <c r="N334" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_05_2019_HHA_Minutes_School_Tract_II_DHCD_Intervention.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="15" t="inlineStr">
+        <is>
+          <t>FL-331</t>
+        </is>
+      </c>
+      <c r="B335" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C335" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D335" s="16" t="inlineStr">
+        <is>
+          <t>Exhibit_06_2021_HHA_Minutes_4-0_Rescission_Vote.pdf</t>
+        </is>
+      </c>
+      <c r="E335" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F335" s="17" t="n">
+        <v>101165</v>
+      </c>
+      <c r="G335" s="12" t="inlineStr">
+        <is>
+          <t>98.8 KB</t>
+        </is>
+      </c>
+      <c r="H335" s="15" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I335" s="16" t="inlineStr">
+        <is>
+          <t>Hingham Housing Authority (Dir. James Marathas)</t>
+        </is>
+      </c>
+      <c r="J335" s="16" t="inlineStr">
+        <is>
+          <t>M.G.L. c. 121B, § 34; HHA By-Laws</t>
+        </is>
+      </c>
+      <c r="K335" s="18" t="inlineStr">
+        <is>
+          <t>Official meeting minutes of Sept 7, 2021 recording 4-0 vote formally rescinding the June 5, 2019 transfer motion, keeping land in HHA ownership.</t>
+        </is>
+      </c>
+      <c r="L335" s="15" t="inlineStr">
+        <is>
+          <t>Official Board Minutes (Verified)</t>
+        </is>
+      </c>
+      <c r="M335" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-16 16:46</t>
+        </is>
+      </c>
+      <c r="N335" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_06_2021_HHA_Minutes_4-0_Rescission_Vote.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="19" t="inlineStr">
+        <is>
+          <t>FL-332</t>
+        </is>
+      </c>
+      <c r="B336" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C336" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D336" s="20" t="inlineStr">
+        <is>
+          <t>Exhibit_07_2024_MassDEP_Recorded_ORAD_Bk59527_Pg273.pdf</t>
+        </is>
+      </c>
+      <c r="E336" s="19" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F336" s="21" t="n">
+        <v>468709</v>
+      </c>
+      <c r="G336" s="22" t="inlineStr">
+        <is>
+          <t>457.7 KB</t>
+        </is>
+      </c>
+      <c r="H336" s="19" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I336" s="20" t="inlineStr">
+        <is>
+          <t>Hingham Conservation Commission / MassDEP</t>
+        </is>
+      </c>
+      <c r="J336" s="20" t="inlineStr">
+        <is>
+          <t>Plymouth County Registry of Deeds Book 59527, Page 273 (Doc #78968)</t>
+        </is>
+      </c>
+      <c r="K336" s="23" t="inlineStr">
+        <is>
+          <t>Recorded Order of Resource Area Delineation (ORAD) WPA Form 4B officially approving wetland boundary lines on Dec 10, 2024.</t>
+        </is>
+      </c>
+      <c r="L336" s="19" t="inlineStr">
+        <is>
+          <t>Recorded Order (Verified)</t>
+        </is>
+      </c>
+      <c r="M336" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:26</t>
+        </is>
+      </c>
+      <c r="N336" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_07_2024_MassDEP_Recorded_ORAD_Bk59527_Pg273.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="15" t="inlineStr">
+        <is>
+          <t>FL-333</t>
+        </is>
+      </c>
+      <c r="B337" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C337" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D337" s="16" t="inlineStr">
+        <is>
+          <t>Exhibit_08_2025_HHA_Developer_RFP_155_Pages.pdf</t>
+        </is>
+      </c>
+      <c r="E337" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F337" s="17" t="n">
+        <v>13909202</v>
+      </c>
+      <c r="G337" s="12" t="inlineStr">
+        <is>
+          <t>13.3 MB</t>
+        </is>
+      </c>
+      <c r="H337" s="15" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I337" s="16" t="inlineStr">
+        <is>
+          <t>Hingham Housing Authority (James Marathas, ED)</t>
+        </is>
+      </c>
+      <c r="J337" s="16" t="inlineStr">
+        <is>
+          <t>M.G.L. c. 30B, § 16; M.G.L. c. 121B</t>
+        </is>
+      </c>
+      <c r="K337" s="18" t="inlineStr">
+        <is>
+          <t>Official 155-page Developer RFP package including Bohler engineering study, Lucas wetlands report, Control Point boundary survey, and draft 99-year ground lease.</t>
+        </is>
+      </c>
+      <c r="L337" s="15" t="inlineStr">
+        <is>
+          <t>Authentic Public RFP (Verified)</t>
+        </is>
+      </c>
+      <c r="M337" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:20</t>
+        </is>
+      </c>
+      <c r="N337" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_08_2025_HHA_Developer_RFP_155_Pages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="19" t="inlineStr">
+        <is>
+          <t>FL-334</t>
+        </is>
+      </c>
+      <c r="B338" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C338" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D338" s="20" t="inlineStr">
+        <is>
+          <t>Exhibit_09_2025_HHA_Minutes_Peabody_Developer_Award_Vote.pdf</t>
+        </is>
+      </c>
+      <c r="E338" s="19" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F338" s="21" t="n">
+        <v>107708</v>
+      </c>
+      <c r="G338" s="22" t="inlineStr">
+        <is>
+          <t>105.2 KB</t>
+        </is>
+      </c>
+      <c r="H338" s="19" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I338" s="20" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J338" s="20" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K338" s="23" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L338" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M338" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-16 16:46</t>
+        </is>
+      </c>
+      <c r="N338" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_09_2025_HHA_Minutes_Peabody_Developer_Award_Vote.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="15" t="inlineStr">
+        <is>
+          <t>FL-335</t>
+        </is>
+      </c>
+      <c r="B339" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C339" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D339" s="16" t="inlineStr">
+        <is>
+          <t>Exhibit_10_2026_Town_Meeting_Warrant_Article_12_CAL_Debt_Defeat.pdf</t>
+        </is>
+      </c>
+      <c r="E339" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F339" s="17" t="n">
+        <v>2958699</v>
+      </c>
+      <c r="G339" s="12" t="inlineStr">
+        <is>
+          <t>2.8 MB</t>
+        </is>
+      </c>
+      <c r="H339" s="15" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I339" s="16" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J339" s="16" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K339" s="18" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L339" s="15" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M339" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:19</t>
+        </is>
+      </c>
+      <c r="N339" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_10_2026_Town_Meeting_Warrant_Article_12_CAL_Debt_Defeat.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:N319"/>
+  <autoFilter ref="A4:N339"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28788,7 +30221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N231"/>
+  <dimension ref="A1:N251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28817,7 +30250,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: September 22, 2026 • Total Records: 227 • Zero Web Scrapes</t>
+          <t>Generated: September 22, 2026 • Total Records: 247 • Zero Web Scrapes</t>
         </is>
       </c>
     </row>
@@ -44783,8 +46216,1408 @@
         </is>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" s="19" t="inlineStr">
+        <is>
+          <t>FL-316</t>
+        </is>
+      </c>
+      <c r="B232" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C232" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D232" s="20" t="inlineStr">
+        <is>
+          <t>100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1.zip</t>
+        </is>
+      </c>
+      <c r="E232" s="19" t="inlineStr">
+        <is>
+          <t>ZIP</t>
+        </is>
+      </c>
+      <c r="F232" s="21" t="n">
+        <v>19847898</v>
+      </c>
+      <c r="G232" s="22" t="inlineStr">
+        <is>
+          <t>18.9 MB</t>
+        </is>
+      </c>
+      <c r="H232" s="19" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I232" s="20" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J232" s="20" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K232" s="23" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L232" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M232" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:14</t>
+        </is>
+      </c>
+      <c r="N232" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="15" t="inlineStr">
+        <is>
+          <t>FL-317</t>
+        </is>
+      </c>
+      <c r="B233" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C233" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D233" s="16" t="inlineStr">
+        <is>
+          <t>README_PACKAGE_v1.md</t>
+        </is>
+      </c>
+      <c r="E233" s="15" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="F233" s="17" t="n">
+        <v>5931</v>
+      </c>
+      <c r="G233" s="12" t="inlineStr">
+        <is>
+          <t>5.8 KB</t>
+        </is>
+      </c>
+      <c r="H233" s="15" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I233" s="16" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J233" s="16" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K233" s="18" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L233" s="15" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M233" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:14</t>
+        </is>
+      </c>
+      <c r="N233" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/README_PACKAGE_v1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="19" t="inlineStr">
+        <is>
+          <t>FL-318</t>
+        </is>
+      </c>
+      <c r="B234" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C234" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D234" s="20" t="inlineStr">
+        <is>
+          <t>01_100_Beal_Street_Verifiable_Facts_and_Human_Document_v1.md</t>
+        </is>
+      </c>
+      <c r="E234" s="19" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="F234" s="21" t="n">
+        <v>22221</v>
+      </c>
+      <c r="G234" s="22" t="inlineStr">
+        <is>
+          <t>21.7 KB</t>
+        </is>
+      </c>
+      <c r="H234" s="19" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I234" s="20" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J234" s="20" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K234" s="23" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L234" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M234" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:10</t>
+        </is>
+      </c>
+      <c r="N234" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/01_100_Beal_Street_Verifiable_Facts_and_Human_Document_v1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="15" t="inlineStr">
+        <is>
+          <t>FL-319</t>
+        </is>
+      </c>
+      <c r="B235" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C235" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D235" s="16" t="inlineStr">
+        <is>
+          <t>01_100_Beal_Street_Verifiable_Facts_and_Human_Document_v1.pdf</t>
+        </is>
+      </c>
+      <c r="E235" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F235" s="17" t="n">
+        <v>103490</v>
+      </c>
+      <c r="G235" s="12" t="inlineStr">
+        <is>
+          <t>101.1 KB</t>
+        </is>
+      </c>
+      <c r="H235" s="15" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I235" s="16" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J235" s="16" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K235" s="18" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L235" s="15" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M235" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:10</t>
+        </is>
+      </c>
+      <c r="N235" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/01_100_Beal_Street_Verifiable_Facts_and_Human_Document_v1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="19" t="inlineStr">
+        <is>
+          <t>FL-320</t>
+        </is>
+      </c>
+      <c r="B236" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C236" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D236" s="20" t="inlineStr">
+        <is>
+          <t>02_100_Beal_Street_Records_Verification_Checklist_and_Audit_v1.md</t>
+        </is>
+      </c>
+      <c r="E236" s="19" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="F236" s="21" t="n">
+        <v>28047</v>
+      </c>
+      <c r="G236" s="22" t="inlineStr">
+        <is>
+          <t>27.4 KB</t>
+        </is>
+      </c>
+      <c r="H236" s="19" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I236" s="20" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J236" s="20" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K236" s="23" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L236" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M236" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:06</t>
+        </is>
+      </c>
+      <c r="N236" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/02_100_Beal_Street_Records_Verification_Checklist_and_Audit_v1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="15" t="inlineStr">
+        <is>
+          <t>FL-321</t>
+        </is>
+      </c>
+      <c r="B237" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C237" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D237" s="16" t="inlineStr">
+        <is>
+          <t>02_100_Beal_Street_Records_Verification_Checklist_and_Audit_v1.pdf</t>
+        </is>
+      </c>
+      <c r="E237" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F237" s="17" t="n">
+        <v>132623</v>
+      </c>
+      <c r="G237" s="12" t="inlineStr">
+        <is>
+          <t>129.5 KB</t>
+        </is>
+      </c>
+      <c r="H237" s="15" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I237" s="16" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J237" s="16" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K237" s="18" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L237" s="15" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M237" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:08</t>
+        </is>
+      </c>
+      <c r="N237" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/02_100_Beal_Street_Records_Verification_Checklist_and_Audit_v1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="19" t="inlineStr">
+        <is>
+          <t>FL-322</t>
+        </is>
+      </c>
+      <c r="B238" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C238" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D238" s="20" t="inlineStr">
+        <is>
+          <t>03_100_Beal_Street_The_True_Story_and_Evidence_v1.md</t>
+        </is>
+      </c>
+      <c r="E238" s="19" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="F238" s="21" t="n">
+        <v>12031</v>
+      </c>
+      <c r="G238" s="22" t="inlineStr">
+        <is>
+          <t>11.7 KB</t>
+        </is>
+      </c>
+      <c r="H238" s="19" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I238" s="20" t="inlineStr">
+        <is>
+          <t>Primary Municipal Records &amp; Educational Architecture</t>
+        </is>
+      </c>
+      <c r="J238" s="20" t="inlineStr">
+        <is>
+          <t>M.G.L. c. 121B; M.G.L. c. 184A; M.G.L. c. 44, § 7; Plymouth Registry Instruments</t>
+        </is>
+      </c>
+      <c r="K238" s="23" t="inlineStr">
+        <is>
+          <t>Dedicated 2-page educational guide and evidence ledger for family and community members. Page 1 provides a 1-page unspun narrative essay; Page 2 provides the companion Works Cited mapping every point to primary documents with repository file names.</t>
+        </is>
+      </c>
+      <c r="L238" s="19" t="inlineStr">
+        <is>
+          <t>Community Educational Guide &amp; Evidence Ledger (Verified)</t>
+        </is>
+      </c>
+      <c r="M238" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:27</t>
+        </is>
+      </c>
+      <c r="N238" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/03_100_Beal_Street_The_True_Story_and_Evidence_v1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="15" t="inlineStr">
+        <is>
+          <t>FL-323</t>
+        </is>
+      </c>
+      <c r="B239" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C239" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D239" s="16" t="inlineStr">
+        <is>
+          <t>03_100_Beal_Street_The_True_Story_and_Evidence_v1.pdf</t>
+        </is>
+      </c>
+      <c r="E239" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F239" s="17" t="n">
+        <v>74343</v>
+      </c>
+      <c r="G239" s="12" t="inlineStr">
+        <is>
+          <t>72.6 KB</t>
+        </is>
+      </c>
+      <c r="H239" s="15" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="I239" s="16" t="inlineStr">
+        <is>
+          <t>Primary Municipal Records &amp; Educational Architecture</t>
+        </is>
+      </c>
+      <c r="J239" s="16" t="inlineStr">
+        <is>
+          <t>M.G.L. c. 121B; M.G.L. c. 184A; M.G.L. c. 44, § 7; Plymouth Registry Instruments</t>
+        </is>
+      </c>
+      <c r="K239" s="18" t="inlineStr">
+        <is>
+          <t>Dedicated 2-page educational guide and evidence ledger for family and community members. Page 1 provides a 1-page unspun narrative essay; Page 2 provides the companion Works Cited mapping every point to primary documents with repository file names.</t>
+        </is>
+      </c>
+      <c r="L239" s="15" t="inlineStr">
+        <is>
+          <t>Community Educational Guide &amp; Evidence Ledger (Verified)</t>
+        </is>
+      </c>
+      <c r="M239" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:27</t>
+        </is>
+      </c>
+      <c r="N239" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/03_100_Beal_Street_The_True_Story_and_Evidence_v1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="19" t="inlineStr">
+        <is>
+          <t>FL-324</t>
+        </is>
+      </c>
+      <c r="B240" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C240" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D240" s="20" t="inlineStr">
+        <is>
+          <t>04_100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.md</t>
+        </is>
+      </c>
+      <c r="E240" s="19" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="F240" s="21" t="n">
+        <v>31676</v>
+      </c>
+      <c r="G240" s="22" t="inlineStr">
+        <is>
+          <t>30.9 KB</t>
+        </is>
+      </c>
+      <c r="H240" s="19" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="I240" s="20" t="inlineStr">
+        <is>
+          <t>Primary Municipal Records / Mass. Registry of Deeds</t>
+        </is>
+      </c>
+      <c r="J240" s="20" t="inlineStr">
+        <is>
+          <t>Historical M.G.L. c. 184A, § 3; M.G.L. c. 184, § 23; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
+        </is>
+      </c>
+      <c r="K240" s="23" t="inlineStr">
+        <is>
+          <t>Preliminary primary-source research chronology and record index; strictly neutral factual reporting; segregates verified facts, factual inferences, and open legal questions; includes missing documents inventory and disclaimer. Not a title opinion.</t>
+        </is>
+      </c>
+      <c r="L240" s="19" t="inlineStr">
+        <is>
+          <t>Neutral Primary Source Research Index &amp; Inventory (Verified)</t>
+        </is>
+      </c>
+      <c r="M240" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:44</t>
+        </is>
+      </c>
+      <c r="N240" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/04_100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="15" t="inlineStr">
+        <is>
+          <t>FL-325</t>
+        </is>
+      </c>
+      <c r="B241" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C241" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D241" s="16" t="inlineStr">
+        <is>
+          <t>04_100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.pdf</t>
+        </is>
+      </c>
+      <c r="E241" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F241" s="17" t="n">
+        <v>119536</v>
+      </c>
+      <c r="G241" s="12" t="inlineStr">
+        <is>
+          <t>116.7 KB</t>
+        </is>
+      </c>
+      <c r="H241" s="15" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="I241" s="16" t="inlineStr">
+        <is>
+          <t>Primary Municipal Records / Mass. Registry of Deeds</t>
+        </is>
+      </c>
+      <c r="J241" s="16" t="inlineStr">
+        <is>
+          <t>Historical M.G.L. c. 184A, § 3; M.G.L. c. 184, § 23; M.G.L. c. 121B, § 34; Book 09097 Pg 158; Book 51379 Pg 244</t>
+        </is>
+      </c>
+      <c r="K241" s="18" t="inlineStr">
+        <is>
+          <t>Preliminary primary-source research chronology and record index; strictly neutral factual reporting; segregates verified facts, factual inferences, and open legal questions; includes missing documents inventory and disclaimer. Not a title opinion.</t>
+        </is>
+      </c>
+      <c r="L241" s="15" t="inlineStr">
+        <is>
+          <t>Neutral Primary Source Research Index &amp; Inventory (Verified)</t>
+        </is>
+      </c>
+      <c r="M241" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:44</t>
+        </is>
+      </c>
+      <c r="N241" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/01_Executive_and_Human_Documents/04_100_Beal_Street_Town_vs_HHA_Legal_Chronology_and_Minutes_v2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="19" t="inlineStr">
+        <is>
+          <t>FL-326</t>
+        </is>
+      </c>
+      <c r="B242" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C242" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D242" s="20" t="inlineStr">
+        <is>
+          <t>Exhibit_01_1989_Fee_Deed_and_ZBA_Decision_Bk09097_Pg158.pdf</t>
+        </is>
+      </c>
+      <c r="E242" s="19" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F242" s="21" t="n">
+        <v>228302</v>
+      </c>
+      <c r="G242" s="22" t="inlineStr">
+        <is>
+          <t>223.0 KB</t>
+        </is>
+      </c>
+      <c r="H242" s="19" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I242" s="20" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J242" s="20" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K242" s="23" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L242" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M242" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:24</t>
+        </is>
+      </c>
+      <c r="N242" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_01_1989_Fee_Deed_and_ZBA_Decision_Bk09097_Pg158.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="15" t="inlineStr">
+        <is>
+          <t>FL-327</t>
+        </is>
+      </c>
+      <c r="B243" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C243" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D243" s="16" t="inlineStr">
+        <is>
+          <t>Exhibit_02_2001_Gale_Subdivision_Plan_and_2024_ALTA_Survey.pdf</t>
+        </is>
+      </c>
+      <c r="E243" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F243" s="17" t="n">
+        <v>2390635</v>
+      </c>
+      <c r="G243" s="12" t="inlineStr">
+        <is>
+          <t>2.3 MB</t>
+        </is>
+      </c>
+      <c r="H243" s="15" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I243" s="16" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J243" s="16" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K243" s="18" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L243" s="15" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M243" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:24</t>
+        </is>
+      </c>
+      <c r="N243" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_02_2001_Gale_Subdivision_Plan_and_2024_ALTA_Survey.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="19" t="inlineStr">
+        <is>
+          <t>FL-328</t>
+        </is>
+      </c>
+      <c r="B244" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C244" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D244" s="20" t="inlineStr">
+        <is>
+          <t>Exhibit_03_2006_Town_Meeting_Article_38_Certified_Vote.pdf</t>
+        </is>
+      </c>
+      <c r="E244" s="19" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F244" s="21" t="n">
+        <v>217985</v>
+      </c>
+      <c r="G244" s="22" t="inlineStr">
+        <is>
+          <t>212.9 KB</t>
+        </is>
+      </c>
+      <c r="H244" s="19" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I244" s="20" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J244" s="20" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K244" s="23" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L244" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M244" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:24</t>
+        </is>
+      </c>
+      <c r="N244" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_03_2006_Town_Meeting_Article_38_Certified_Vote.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="15" t="inlineStr">
+        <is>
+          <t>FL-329</t>
+        </is>
+      </c>
+      <c r="B245" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C245" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D245" s="16" t="inlineStr">
+        <is>
+          <t>Exhibit_04_2019_Select_Board_Executive_Session_Minutes_Lawsuit_Vote.pdf</t>
+        </is>
+      </c>
+      <c r="E245" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F245" s="17" t="n">
+        <v>50677</v>
+      </c>
+      <c r="G245" s="12" t="inlineStr">
+        <is>
+          <t>49.5 KB</t>
+        </is>
+      </c>
+      <c r="H245" s="15" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I245" s="16" t="inlineStr">
+        <is>
+          <t>Hingham Board of Selectmen (Healey, Power, Johnson)</t>
+        </is>
+      </c>
+      <c r="J245" s="16" t="inlineStr">
+        <is>
+          <t>M.G.L. c. 30A, § 21(a)(3) (Executive Session Litigation)</t>
+        </is>
+      </c>
+      <c r="K245" s="18" t="inlineStr">
+        <is>
+          <t>Executive Session minutes of Feb 26, 2019 recording 3-0 vote to file litigation against HHA to enforce 2001 MOU 9 days before 30-yr reverter expiration.</t>
+        </is>
+      </c>
+      <c r="L245" s="15" t="inlineStr">
+        <is>
+          <t>Official Municipal Minutes (Verified)</t>
+        </is>
+      </c>
+      <c r="M245" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-14 08:38</t>
+        </is>
+      </c>
+      <c r="N245" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_04_2019_Select_Board_Executive_Session_Minutes_Lawsuit_Vote.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="19" t="inlineStr">
+        <is>
+          <t>FL-330</t>
+        </is>
+      </c>
+      <c r="B246" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C246" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D246" s="20" t="inlineStr">
+        <is>
+          <t>Exhibit_05_2019_HHA_Minutes_School_Tract_II_DHCD_Intervention.pdf</t>
+        </is>
+      </c>
+      <c r="E246" s="19" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F246" s="21" t="n">
+        <v>41327</v>
+      </c>
+      <c r="G246" s="22" t="inlineStr">
+        <is>
+          <t>40.4 KB</t>
+        </is>
+      </c>
+      <c r="H246" s="19" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I246" s="20" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J246" s="20" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K246" s="23" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L246" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M246" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:13</t>
+        </is>
+      </c>
+      <c r="N246" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_05_2019_HHA_Minutes_School_Tract_II_DHCD_Intervention.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="15" t="inlineStr">
+        <is>
+          <t>FL-331</t>
+        </is>
+      </c>
+      <c r="B247" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C247" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D247" s="16" t="inlineStr">
+        <is>
+          <t>Exhibit_06_2021_HHA_Minutes_4-0_Rescission_Vote.pdf</t>
+        </is>
+      </c>
+      <c r="E247" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F247" s="17" t="n">
+        <v>101165</v>
+      </c>
+      <c r="G247" s="12" t="inlineStr">
+        <is>
+          <t>98.8 KB</t>
+        </is>
+      </c>
+      <c r="H247" s="15" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I247" s="16" t="inlineStr">
+        <is>
+          <t>Hingham Housing Authority (Dir. James Marathas)</t>
+        </is>
+      </c>
+      <c r="J247" s="16" t="inlineStr">
+        <is>
+          <t>M.G.L. c. 121B, § 34; HHA By-Laws</t>
+        </is>
+      </c>
+      <c r="K247" s="18" t="inlineStr">
+        <is>
+          <t>Official meeting minutes of Sept 7, 2021 recording 4-0 vote formally rescinding the June 5, 2019 transfer motion, keeping land in HHA ownership.</t>
+        </is>
+      </c>
+      <c r="L247" s="15" t="inlineStr">
+        <is>
+          <t>Official Board Minutes (Verified)</t>
+        </is>
+      </c>
+      <c r="M247" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-16 16:46</t>
+        </is>
+      </c>
+      <c r="N247" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_06_2021_HHA_Minutes_4-0_Rescission_Vote.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="19" t="inlineStr">
+        <is>
+          <t>FL-332</t>
+        </is>
+      </c>
+      <c r="B248" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C248" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D248" s="20" t="inlineStr">
+        <is>
+          <t>Exhibit_07_2024_MassDEP_Recorded_ORAD_Bk59527_Pg273.pdf</t>
+        </is>
+      </c>
+      <c r="E248" s="19" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F248" s="21" t="n">
+        <v>468709</v>
+      </c>
+      <c r="G248" s="22" t="inlineStr">
+        <is>
+          <t>457.7 KB</t>
+        </is>
+      </c>
+      <c r="H248" s="19" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I248" s="20" t="inlineStr">
+        <is>
+          <t>Hingham Conservation Commission / MassDEP</t>
+        </is>
+      </c>
+      <c r="J248" s="20" t="inlineStr">
+        <is>
+          <t>Plymouth County Registry of Deeds Book 59527, Page 273 (Doc #78968)</t>
+        </is>
+      </c>
+      <c r="K248" s="23" t="inlineStr">
+        <is>
+          <t>Recorded Order of Resource Area Delineation (ORAD) WPA Form 4B officially approving wetland boundary lines on Dec 10, 2024.</t>
+        </is>
+      </c>
+      <c r="L248" s="19" t="inlineStr">
+        <is>
+          <t>Recorded Order (Verified)</t>
+        </is>
+      </c>
+      <c r="M248" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:26</t>
+        </is>
+      </c>
+      <c r="N248" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_07_2024_MassDEP_Recorded_ORAD_Bk59527_Pg273.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="15" t="inlineStr">
+        <is>
+          <t>FL-333</t>
+        </is>
+      </c>
+      <c r="B249" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C249" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D249" s="16" t="inlineStr">
+        <is>
+          <t>Exhibit_08_2025_HHA_Developer_RFP_155_Pages.pdf</t>
+        </is>
+      </c>
+      <c r="E249" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F249" s="17" t="n">
+        <v>13909202</v>
+      </c>
+      <c r="G249" s="12" t="inlineStr">
+        <is>
+          <t>13.3 MB</t>
+        </is>
+      </c>
+      <c r="H249" s="15" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I249" s="16" t="inlineStr">
+        <is>
+          <t>Hingham Housing Authority (James Marathas, ED)</t>
+        </is>
+      </c>
+      <c r="J249" s="16" t="inlineStr">
+        <is>
+          <t>M.G.L. c. 30B, § 16; M.G.L. c. 121B</t>
+        </is>
+      </c>
+      <c r="K249" s="18" t="inlineStr">
+        <is>
+          <t>Official 155-page Developer RFP package including Bohler engineering study, Lucas wetlands report, Control Point boundary survey, and draft 99-year ground lease.</t>
+        </is>
+      </c>
+      <c r="L249" s="15" t="inlineStr">
+        <is>
+          <t>Authentic Public RFP (Verified)</t>
+        </is>
+      </c>
+      <c r="M249" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:20</t>
+        </is>
+      </c>
+      <c r="N249" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_08_2025_HHA_Developer_RFP_155_Pages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="19" t="inlineStr">
+        <is>
+          <t>FL-334</t>
+        </is>
+      </c>
+      <c r="B250" s="20" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C250" s="20" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D250" s="20" t="inlineStr">
+        <is>
+          <t>Exhibit_09_2025_HHA_Minutes_Peabody_Developer_Award_Vote.pdf</t>
+        </is>
+      </c>
+      <c r="E250" s="19" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F250" s="21" t="n">
+        <v>107708</v>
+      </c>
+      <c r="G250" s="22" t="inlineStr">
+        <is>
+          <t>105.2 KB</t>
+        </is>
+      </c>
+      <c r="H250" s="19" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I250" s="20" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J250" s="20" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K250" s="23" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L250" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M250" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-16 16:46</t>
+        </is>
+      </c>
+      <c r="N250" s="20" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_09_2025_HHA_Minutes_Peabody_Developer_Award_Vote.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="15" t="inlineStr">
+        <is>
+          <t>FL-335</t>
+        </is>
+      </c>
+      <c r="B251" s="16" t="inlineStr">
+        <is>
+          <t>Agent-Created Deliverable</t>
+        </is>
+      </c>
+      <c r="C251" s="16" t="inlineStr">
+        <is>
+          <t>Agent Synthesized Work</t>
+        </is>
+      </c>
+      <c r="D251" s="16" t="inlineStr">
+        <is>
+          <t>Exhibit_10_2026_Town_Meeting_Warrant_Article_12_CAL_Debt_Defeat.pdf</t>
+        </is>
+      </c>
+      <c r="E251" s="15" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F251" s="17" t="n">
+        <v>2958699</v>
+      </c>
+      <c r="G251" s="12" t="inlineStr">
+        <is>
+          <t>2.8 MB</t>
+        </is>
+      </c>
+      <c r="H251" s="15" t="inlineStr">
+        <is>
+          <t>Original Public Record</t>
+        </is>
+      </c>
+      <c r="I251" s="16" t="inlineStr">
+        <is>
+          <t>Town of Hingham / Housing Authority</t>
+        </is>
+      </c>
+      <c r="J251" s="16" t="inlineStr">
+        <is>
+          <t>Massachusetts General Laws</t>
+        </is>
+      </c>
+      <c r="K251" s="18" t="inlineStr">
+        <is>
+          <t>Project documentation and archival record.</t>
+        </is>
+      </c>
+      <c r="L251" s="15" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M251" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:19</t>
+        </is>
+      </c>
+      <c r="N251" s="16" t="inlineStr">
+        <is>
+          <t>agent_created_deliverables/packages/100_Beal_Street_Verifiable_Facts_and_Evidence_Package_v1/02_Primary_Source_Evidence_Exhibits/Exhibit_10_2026_Town_Meeting_Warrant_Article_12_CAL_Debt_Defeat.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:N231"/>
+  <autoFilter ref="A4:N251"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
